--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2180,6 +2180,8295 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126057921</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>550142</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6942582</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126057934</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>550127</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6942669</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126057536</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>550113</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6942389</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126057597</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>550099</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6942637</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>8 ex</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126057564</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>550076</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6942390</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126057563</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>550020</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6942451</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126057582</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>550023</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6942583</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>61 ex</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126057526</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91228</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>550079</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6942497</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126057935</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>550099</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6942670</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126052248</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>550004</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6942504</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom området</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126051522</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>550089</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6942422</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126050880</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>550088</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6942520</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126052983</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>549977</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6942554</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126057545</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91239</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>550011</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6942535</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126057532</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>550020</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6942390</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126057544</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80100</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>550094</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6942584</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126051074</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>550081</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6942505</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126053984</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>549984</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6942510</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126057538</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>550041</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6942496</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126057579</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>550006</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6942636</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126057596</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>550092</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6942597</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>8 ex</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126057591</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>550020</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6942543</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>3 ex</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126057567</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>550001</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6942503</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126057937</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>550147</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6942582</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126052912</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>549977</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6942554</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126052420</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>549984</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6942510</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126057592</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>550038</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6942494</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>28 ex</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126057600</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>550095</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6942646</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>5 ex</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126057569</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>550006</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6942630</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126052332</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98355</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>549984</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6942510</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126057568</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>550093</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6942579</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126057930</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>550112</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6942664</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>50stycken</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126052735</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>549975</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6942519</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126057896</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>550007</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6942646</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126051408</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>550089</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6942422</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126051690</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>550110</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6942386</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126049249</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>550135</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6942628</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126057602</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>550099</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6942666</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>11 ex</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126057565</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>550139</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6942641</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126057915</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>550145</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6942577</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126057898</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>549997</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6942637</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126050777</v>
+      </c>
+      <c r="B56" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>550093</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6942497</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126057525</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91228</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>549977</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6942580</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126057533</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>550026</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6942422</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126049594</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>550141</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6942615</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126048239</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>550147</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6942635</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126051839</v>
+      </c>
+      <c r="B61" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>550088</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6942377</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126052934</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>549977</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6942554</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126052802</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98355</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>549987</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6942530</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126057601</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>550096</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6942661</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>40 ex</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126057576</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>550078</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6942401</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126051507</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98355</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>550089</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6942422</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126051197</v>
+      </c>
+      <c r="B67" t="n">
+        <v>97212</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>550077</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6942476</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126057594</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>550130</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6942565</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>35 ex</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126057537</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>550111</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6942345</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126053048</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>549965</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6942583</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I området</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126051112</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>550093</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6942497</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126057583</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>550098</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6942641</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>31 ex</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126049570</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>550135</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6942628</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126057578</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>550086</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6942580</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>126057549</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91682</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>549978</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6942581</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126051602</v>
+      </c>
+      <c r="B76" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>550089</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6942422</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>126050913</v>
+      </c>
+      <c r="B77" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>550088</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6942520</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126057606</v>
+      </c>
+      <c r="B78" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>550034</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6942421</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126057904</v>
+      </c>
+      <c r="B79" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>549997</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6942637</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126051270</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>550065</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6942463</v>
+      </c>
+      <c r="S80" t="n">
+        <v>18</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>126057559</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>550000</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6942626</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>126057574</v>
+      </c>
+      <c r="B82" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>549990</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6942590</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126057524</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91193</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>550079</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6942497</v>
+      </c>
+      <c r="S83" t="n">
+        <v>15</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126047488</v>
+      </c>
+      <c r="B84" t="n">
+        <v>43933</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>550158</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6942653</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Går djupt ner i hela veden. Björk</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126057531</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>549974</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6942584</v>
+      </c>
+      <c r="S85" t="n">
+        <v>15</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126057535</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>550047</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6942401</v>
+      </c>
+      <c r="S86" t="n">
+        <v>15</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126057575</v>
+      </c>
+      <c r="B87" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>550022</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6942537</v>
+      </c>
+      <c r="S87" t="n">
+        <v>15</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126057556</v>
+      </c>
+      <c r="B88" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>550074</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6942641</v>
+      </c>
+      <c r="S88" t="n">
+        <v>15</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126052154</v>
+      </c>
+      <c r="B89" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>550021</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6942450</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126052873</v>
+      </c>
+      <c r="B90" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>549989</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6942554</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126052827</v>
+      </c>
+      <c r="B91" t="n">
+        <v>97212</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>549987</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6942530</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>126057923</v>
+      </c>
+      <c r="B92" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>550122</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6942671</v>
+      </c>
+      <c r="S92" t="n">
+        <v>15</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126057593</v>
+      </c>
+      <c r="B93" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>550137</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6942555</v>
+      </c>
+      <c r="S93" t="n">
+        <v>15</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>3 ex</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>126057577</v>
+      </c>
+      <c r="B94" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>550101</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6942551</v>
+      </c>
+      <c r="S94" t="n">
+        <v>15</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>126057540</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>550138</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6942638</v>
+      </c>
+      <c r="S95" t="n">
+        <v>15</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>126057581</v>
+      </c>
+      <c r="B96" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>550004</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6942625</v>
+      </c>
+      <c r="S96" t="n">
+        <v>15</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>126050713</v>
+      </c>
+      <c r="B97" t="n">
+        <v>56834</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>550120</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6942506</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -3081,32 +3081,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126052248</v>
+        <v>126057545</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>91239</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3116,13 +3116,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550004</v>
+        <v>550011</v>
       </c>
       <c r="R24" t="n">
-        <v>6942504</v>
+        <v>6942535</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,11 +3152,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom området</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3183,32 +3178,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126051522</v>
+        <v>126057532</v>
       </c>
       <c r="B25" t="n">
-        <v>80099</v>
+        <v>57651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3218,13 +3213,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550089</v>
+        <v>550020</v>
       </c>
       <c r="R25" t="n">
-        <v>6942422</v>
+        <v>6942390</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3254,6 +3249,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3280,10 +3280,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126050880</v>
+        <v>126057544</v>
       </c>
       <c r="B26" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,21 +3291,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,13 +3315,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550088</v>
+        <v>550094</v>
       </c>
       <c r="R26" t="n">
-        <v>6942520</v>
+        <v>6942584</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3377,10 +3377,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126052983</v>
+        <v>126052248</v>
       </c>
       <c r="B27" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3388,21 +3388,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549977</v>
+        <v>550004</v>
       </c>
       <c r="R27" t="n">
-        <v>6942554</v>
+        <v>6942504</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3448,6 +3448,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom området</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3474,10 +3479,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126057545</v>
+        <v>126051522</v>
       </c>
       <c r="B28" t="n">
-        <v>91239</v>
+        <v>80099</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3485,21 +3490,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1205</v>
+        <v>6461</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3509,13 +3514,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550011</v>
+        <v>550089</v>
       </c>
       <c r="R28" t="n">
-        <v>6942535</v>
+        <v>6942422</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3571,32 +3576,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057532</v>
+        <v>126050880</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>80099</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3606,13 +3611,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550020</v>
+        <v>550088</v>
       </c>
       <c r="R29" t="n">
-        <v>6942390</v>
+        <v>6942520</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3642,11 +3647,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3673,32 +3673,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057544</v>
+        <v>126052983</v>
       </c>
       <c r="B30" t="n">
-        <v>80100</v>
+        <v>78726</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3708,13 +3708,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550094</v>
+        <v>549977</v>
       </c>
       <c r="R30" t="n">
-        <v>6942584</v>
+        <v>6942554</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -5074,49 +5074,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126052332</v>
+        <v>126052735</v>
       </c>
       <c r="B44" t="n">
-        <v>98355</v>
+        <v>78727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549984</v>
+        <v>549975</v>
       </c>
       <c r="R44" t="n">
-        <v>6942510</v>
+        <v>6942519</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5175,45 +5171,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057568</v>
+        <v>126057896</v>
       </c>
       <c r="B45" t="n">
-        <v>80071</v>
+        <v>80099</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550093</v>
+        <v>550007</v>
       </c>
       <c r="R45" t="n">
-        <v>6942579</v>
+        <v>6942646</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5272,48 +5268,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057930</v>
+        <v>126052332</v>
       </c>
       <c r="B46" t="n">
-        <v>98334</v>
+        <v>98355</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550112</v>
+        <v>549984</v>
       </c>
       <c r="R46" t="n">
-        <v>6942664</v>
+        <v>6942510</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5343,11 +5343,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>50stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5374,10 +5369,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126052735</v>
+        <v>126057568</v>
       </c>
       <c r="B47" t="n">
-        <v>78727</v>
+        <v>80071</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5385,21 +5380,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5409,13 +5404,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>549975</v>
+        <v>550093</v>
       </c>
       <c r="R47" t="n">
-        <v>6942519</v>
+        <v>6942579</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5471,32 +5466,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057896</v>
+        <v>126057930</v>
       </c>
       <c r="B48" t="n">
-        <v>80099</v>
+        <v>98334</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5506,10 +5501,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550007</v>
+        <v>550112</v>
       </c>
       <c r="R48" t="n">
-        <v>6942646</v>
+        <v>6942664</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5542,6 +5537,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>50stycken</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5980,10 +5980,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057565</v>
+        <v>126057915</v>
       </c>
       <c r="B53" t="n">
-        <v>78727</v>
+        <v>78726</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5991,34 +5991,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550139</v>
+        <v>550145</v>
       </c>
       <c r="R53" t="n">
-        <v>6942641</v>
+        <v>6942577</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6077,32 +6077,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057915</v>
+        <v>126057898</v>
       </c>
       <c r="B54" t="n">
-        <v>78726</v>
+        <v>80099</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550145</v>
+        <v>549997</v>
       </c>
       <c r="R54" t="n">
-        <v>6942577</v>
+        <v>6942637</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6174,45 +6174,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057898</v>
+        <v>126057565</v>
       </c>
       <c r="B55" t="n">
-        <v>80099</v>
+        <v>78727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>549997</v>
+        <v>550139</v>
       </c>
       <c r="R55" t="n">
-        <v>6942637</v>
+        <v>6942641</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6572,37 +6572,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126049594</v>
+        <v>126051839</v>
       </c>
       <c r="B59" t="n">
-        <v>98334</v>
+        <v>56843</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6611,10 +6612,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550141</v>
+        <v>550088</v>
       </c>
       <c r="R59" t="n">
-        <v>6942615</v>
+        <v>6942377</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6673,7 +6674,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126048239</v>
+        <v>126052934</v>
       </c>
       <c r="B60" t="n">
         <v>98334</v>
@@ -6703,7 +6704,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6712,10 +6713,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550147</v>
+        <v>549977</v>
       </c>
       <c r="R60" t="n">
-        <v>6942635</v>
+        <v>6942554</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6774,10 +6775,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126051839</v>
+        <v>126052802</v>
       </c>
       <c r="B61" t="n">
-        <v>56843</v>
+        <v>98355</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6785,27 +6786,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550088</v>
+        <v>549987</v>
       </c>
       <c r="R61" t="n">
-        <v>6942377</v>
+        <v>6942530</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6876,7 +6876,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126052934</v>
+        <v>126057601</v>
       </c>
       <c r="B62" t="n">
         <v>98334</v>
@@ -6904,24 +6904,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>549977</v>
+        <v>550096</v>
       </c>
       <c r="R62" t="n">
-        <v>6942554</v>
+        <v>6942661</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6951,6 +6947,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6977,52 +6978,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126052802</v>
+        <v>126057576</v>
       </c>
       <c r="B63" t="n">
-        <v>98355</v>
+        <v>78726</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>549987</v>
+        <v>550078</v>
       </c>
       <c r="R63" t="n">
-        <v>6942530</v>
+        <v>6942401</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7078,7 +7075,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126057601</v>
+        <v>126049594</v>
       </c>
       <c r="B64" t="n">
         <v>98334</v>
@@ -7106,20 +7103,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550096</v>
+        <v>550141</v>
       </c>
       <c r="R64" t="n">
-        <v>6942661</v>
+        <v>6942615</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7149,11 +7150,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7180,48 +7176,52 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126057576</v>
+        <v>126048239</v>
       </c>
       <c r="B65" t="n">
-        <v>78726</v>
+        <v>98334</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550078</v>
+        <v>550147</v>
       </c>
       <c r="R65" t="n">
-        <v>6942401</v>
+        <v>6942635</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7679,32 +7679,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126053048</v>
+        <v>126051112</v>
       </c>
       <c r="B70" t="n">
-        <v>78968</v>
+        <v>80099</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>549965</v>
+        <v>550093</v>
       </c>
       <c r="R70" t="n">
-        <v>6942583</v>
+        <v>6942497</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7750,11 +7750,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I området</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7781,32 +7776,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126051112</v>
+        <v>126053048</v>
       </c>
       <c r="B71" t="n">
-        <v>80099</v>
+        <v>78968</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7816,10 +7811,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550093</v>
+        <v>549965</v>
       </c>
       <c r="R71" t="n">
-        <v>6942497</v>
+        <v>6942583</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7852,6 +7847,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I området</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7980,10 +7980,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126049570</v>
+        <v>126057578</v>
       </c>
       <c r="B73" t="n">
-        <v>78968</v>
+        <v>78726</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7991,21 +7991,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550135</v>
+        <v>550086</v>
       </c>
       <c r="R73" t="n">
-        <v>6942628</v>
+        <v>6942580</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8051,11 +8051,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8082,32 +8077,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126057578</v>
+        <v>126057549</v>
       </c>
       <c r="B74" t="n">
-        <v>78726</v>
+        <v>91682</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8117,10 +8112,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550086</v>
+        <v>549978</v>
       </c>
       <c r="R74" t="n">
-        <v>6942580</v>
+        <v>6942581</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8179,32 +8174,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126057549</v>
+        <v>126049570</v>
       </c>
       <c r="B75" t="n">
-        <v>91682</v>
+        <v>78968</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8214,13 +8209,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>549978</v>
+        <v>550135</v>
       </c>
       <c r="R75" t="n">
-        <v>6942581</v>
+        <v>6942628</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8250,6 +8245,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9172,48 +9172,52 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126057531</v>
+        <v>126052873</v>
       </c>
       <c r="B85" t="n">
-        <v>57651</v>
+        <v>98334</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>549974</v>
+        <v>549989</v>
       </c>
       <c r="R85" t="n">
-        <v>6942584</v>
+        <v>6942554</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9243,11 +9247,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9274,32 +9273,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126057535</v>
+        <v>126052827</v>
       </c>
       <c r="B86" t="n">
-        <v>57651</v>
+        <v>97212</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9309,13 +9308,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550047</v>
+        <v>549987</v>
       </c>
       <c r="R86" t="n">
-        <v>6942401</v>
+        <v>6942530</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9345,11 +9344,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9376,10 +9370,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126057575</v>
+        <v>126057531</v>
       </c>
       <c r="B87" t="n">
-        <v>78726</v>
+        <v>57651</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9387,21 +9381,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9411,10 +9405,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550022</v>
+        <v>549974</v>
       </c>
       <c r="R87" t="n">
-        <v>6942537</v>
+        <v>6942584</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9447,6 +9441,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9473,32 +9472,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126057556</v>
+        <v>126057535</v>
       </c>
       <c r="B88" t="n">
-        <v>80099</v>
+        <v>57651</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9508,10 +9507,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550074</v>
+        <v>550047</v>
       </c>
       <c r="R88" t="n">
-        <v>6942641</v>
+        <v>6942401</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9544,6 +9543,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9570,10 +9574,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126052154</v>
+        <v>126057575</v>
       </c>
       <c r="B89" t="n">
-        <v>78968</v>
+        <v>78726</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9581,21 +9585,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9605,13 +9609,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550021</v>
+        <v>550022</v>
       </c>
       <c r="R89" t="n">
-        <v>6942450</v>
+        <v>6942537</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9641,11 +9645,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9672,52 +9671,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126052873</v>
+        <v>126057556</v>
       </c>
       <c r="B90" t="n">
-        <v>98334</v>
+        <v>80099</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>549989</v>
+        <v>550074</v>
       </c>
       <c r="R90" t="n">
-        <v>6942554</v>
+        <v>6942641</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9773,32 +9768,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126052827</v>
+        <v>126052154</v>
       </c>
       <c r="B91" t="n">
-        <v>97212</v>
+        <v>78968</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9808,10 +9803,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>549987</v>
+        <v>550021</v>
       </c>
       <c r="R91" t="n">
-        <v>6942530</v>
+        <v>6942450</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9844,6 +9839,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2183,32 +2183,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126057921</v>
+        <v>126057934</v>
       </c>
       <c r="B15" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550142</v>
+        <v>550127</v>
       </c>
       <c r="R15" t="n">
-        <v>6942582</v>
+        <v>6942669</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>30 stycken</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126057934</v>
+        <v>126057536</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,34 +2296,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550127</v>
+        <v>550113</v>
       </c>
       <c r="R16" t="n">
-        <v>6942669</v>
+        <v>6942389</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126057536</v>
+        <v>126057564</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>78731</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550113</v>
+        <v>550076</v>
       </c>
       <c r="R17" t="n">
-        <v>6942389</v>
+        <v>6942390</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2458,11 +2458,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,10 +2484,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057597</v>
+        <v>126057921</v>
       </c>
       <c r="B18" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,14 +2515,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550099</v>
+        <v>550142</v>
       </c>
       <c r="R18" t="n">
-        <v>6942637</v>
+        <v>6942582</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2564,7 +2559,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,32 +2586,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057564</v>
+        <v>126057597</v>
       </c>
       <c r="B19" t="n">
-        <v>78727</v>
+        <v>98338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550076</v>
+        <v>550099</v>
       </c>
       <c r="R19" t="n">
-        <v>6942390</v>
+        <v>6942637</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2662,6 +2657,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,7 +2691,7 @@
         <v>126057563</v>
       </c>
       <c r="B20" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,45 +2785,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057582</v>
+        <v>126057935</v>
       </c>
       <c r="B21" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550023</v>
+        <v>550099</v>
       </c>
       <c r="R21" t="n">
-        <v>6942583</v>
+        <v>6942670</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2856,11 +2856,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>61 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,7 +2885,7 @@
         <v>126057526</v>
       </c>
       <c r="B22" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,45 +2979,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057935</v>
+        <v>126057582</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550099</v>
+        <v>550023</v>
       </c>
       <c r="R23" t="n">
-        <v>6942670</v>
+        <v>6942583</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3055,6 +3050,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>61 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,10 +3081,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126057545</v>
+        <v>126050880</v>
       </c>
       <c r="B24" t="n">
-        <v>91239</v>
+        <v>80103</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3092,21 +3092,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1205</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3116,13 +3116,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550011</v>
+        <v>550088</v>
       </c>
       <c r="R24" t="n">
-        <v>6942535</v>
+        <v>6942520</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3178,32 +3178,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126057532</v>
+        <v>126057545</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>91243</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550020</v>
+        <v>550011</v>
       </c>
       <c r="R25" t="n">
-        <v>6942390</v>
+        <v>6942535</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3249,11 +3249,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3280,32 +3275,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126057544</v>
+        <v>126052983</v>
       </c>
       <c r="B26" t="n">
-        <v>80100</v>
+        <v>78730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,13 +3310,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550094</v>
+        <v>549977</v>
       </c>
       <c r="R26" t="n">
-        <v>6942584</v>
+        <v>6942554</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3380,7 +3375,7 @@
         <v>126052248</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,7 +3477,7 @@
         <v>126051522</v>
       </c>
       <c r="B28" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3576,10 +3571,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126050880</v>
+        <v>126057544</v>
       </c>
       <c r="B29" t="n">
-        <v>80099</v>
+        <v>80104</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3587,21 +3582,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3611,13 +3606,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550088</v>
+        <v>550094</v>
       </c>
       <c r="R29" t="n">
-        <v>6942520</v>
+        <v>6942584</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3673,10 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126052983</v>
+        <v>126057532</v>
       </c>
       <c r="B30" t="n">
-        <v>78726</v>
+        <v>57651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3684,21 +3679,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3708,13 +3703,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549977</v>
+        <v>550020</v>
       </c>
       <c r="R30" t="n">
-        <v>6942554</v>
+        <v>6942390</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3744,6 +3739,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3773,7 +3773,7 @@
         <v>126051074</v>
       </c>
       <c r="B31" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,10 +3871,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126053984</v>
+        <v>126057579</v>
       </c>
       <c r="B32" t="n">
-        <v>78968</v>
+        <v>78730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3882,21 +3882,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549984</v>
+        <v>550006</v>
       </c>
       <c r="R32" t="n">
-        <v>6942510</v>
+        <v>6942636</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3942,11 +3942,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3973,10 +3968,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057538</v>
+        <v>126057937</v>
       </c>
       <c r="B33" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3984,34 +3979,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550041</v>
+        <v>550147</v>
       </c>
       <c r="R33" t="n">
-        <v>6942496</v>
+        <v>6942582</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4048,7 +4043,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4075,10 +4070,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057579</v>
+        <v>126057567</v>
       </c>
       <c r="B34" t="n">
-        <v>78726</v>
+        <v>80075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4086,21 +4081,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4110,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550006</v>
+        <v>550001</v>
       </c>
       <c r="R34" t="n">
-        <v>6942636</v>
+        <v>6942503</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4172,32 +4167,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057596</v>
+        <v>126053984</v>
       </c>
       <c r="B35" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4207,13 +4202,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550092</v>
+        <v>549984</v>
       </c>
       <c r="R35" t="n">
-        <v>6942597</v>
+        <v>6942510</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4247,7 +4242,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,32 +4269,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057591</v>
+        <v>126057538</v>
       </c>
       <c r="B36" t="n">
-        <v>98334</v>
+        <v>57651</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4309,10 +4304,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550020</v>
+        <v>550041</v>
       </c>
       <c r="R36" t="n">
-        <v>6942543</v>
+        <v>6942496</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4349,7 +4344,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4376,32 +4371,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057567</v>
+        <v>126057596</v>
       </c>
       <c r="B37" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4411,10 +4406,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550001</v>
+        <v>550092</v>
       </c>
       <c r="R37" t="n">
-        <v>6942503</v>
+        <v>6942597</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4447,6 +4442,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4473,45 +4473,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057937</v>
+        <v>126057591</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550147</v>
+        <v>550020</v>
       </c>
       <c r="R38" t="n">
-        <v>6942582</v>
+        <v>6942543</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4578,7 +4578,7 @@
         <v>126052912</v>
       </c>
       <c r="B39" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4672,52 +4672,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126052420</v>
+        <v>126057569</v>
       </c>
       <c r="B40" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549984</v>
+        <v>550006</v>
       </c>
       <c r="R40" t="n">
-        <v>6942510</v>
+        <v>6942630</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4776,7 +4772,7 @@
         <v>126057592</v>
       </c>
       <c r="B41" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4875,10 +4871,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126057600</v>
+        <v>126052420</v>
       </c>
       <c r="B42" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4903,20 +4899,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550095</v>
+        <v>549984</v>
       </c>
       <c r="R42" t="n">
-        <v>6942646</v>
+        <v>6942510</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4946,11 +4946,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4977,32 +4972,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126057569</v>
+        <v>126057600</v>
       </c>
       <c r="B43" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5012,10 +5007,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550006</v>
+        <v>550095</v>
       </c>
       <c r="R43" t="n">
-        <v>6942630</v>
+        <v>6942646</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5048,6 +5043,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5074,48 +5074,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126052735</v>
+        <v>126057896</v>
       </c>
       <c r="B44" t="n">
-        <v>78727</v>
+        <v>80103</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549975</v>
+        <v>550007</v>
       </c>
       <c r="R44" t="n">
-        <v>6942519</v>
+        <v>6942646</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5171,45 +5171,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057896</v>
+        <v>126057568</v>
       </c>
       <c r="B45" t="n">
-        <v>80099</v>
+        <v>80075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550007</v>
+        <v>550093</v>
       </c>
       <c r="R45" t="n">
-        <v>6942646</v>
+        <v>6942579</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5271,7 +5271,7 @@
         <v>126052332</v>
       </c>
       <c r="B46" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5369,45 +5369,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057568</v>
+        <v>126057930</v>
       </c>
       <c r="B47" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550093</v>
+        <v>550112</v>
       </c>
       <c r="R47" t="n">
-        <v>6942579</v>
+        <v>6942664</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5440,6 +5440,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>50stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5466,48 +5471,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057930</v>
+        <v>126052735</v>
       </c>
       <c r="B48" t="n">
-        <v>98334</v>
+        <v>78731</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550112</v>
+        <v>549975</v>
       </c>
       <c r="R48" t="n">
-        <v>6942664</v>
+        <v>6942519</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5537,11 +5542,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>50stycken</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5568,50 +5568,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126051408</v>
+        <v>126051690</v>
       </c>
       <c r="B49" t="n">
-        <v>57648</v>
+        <v>80103</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550089</v>
+        <v>550110</v>
       </c>
       <c r="R49" t="n">
-        <v>6942422</v>
+        <v>6942386</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5644,11 +5639,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5675,45 +5665,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126051690</v>
+        <v>126051408</v>
       </c>
       <c r="B50" t="n">
-        <v>80099</v>
+        <v>57648</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550110</v>
+        <v>550089</v>
       </c>
       <c r="R50" t="n">
-        <v>6942386</v>
+        <v>6942422</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5746,6 +5741,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5772,57 +5772,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126049249</v>
+        <v>126057602</v>
       </c>
       <c r="B51" t="n">
-        <v>58020</v>
+        <v>98338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550135</v>
+        <v>550099</v>
       </c>
       <c r="R51" t="n">
-        <v>6942628</v>
+        <v>6942666</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5852,6 +5843,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5878,48 +5874,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126057602</v>
+        <v>126049249</v>
       </c>
       <c r="B52" t="n">
-        <v>98334</v>
+        <v>58020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550099</v>
+        <v>550135</v>
       </c>
       <c r="R52" t="n">
-        <v>6942666</v>
+        <v>6942628</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5949,11 +5954,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5983,7 +5983,7 @@
         <v>126057915</v>
       </c>
       <c r="B53" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>126057898</v>
       </c>
       <c r="B54" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>126057565</v>
       </c>
       <c r="B55" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6271,53 +6271,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126050777</v>
+        <v>126057533</v>
       </c>
       <c r="B56" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550093</v>
+        <v>550026</v>
       </c>
       <c r="R56" t="n">
-        <v>6942497</v>
+        <v>6942422</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6347,6 +6342,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6373,48 +6373,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126057525</v>
+        <v>126050777</v>
       </c>
       <c r="B57" t="n">
-        <v>91228</v>
+        <v>56843</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>549977</v>
+        <v>550093</v>
       </c>
       <c r="R57" t="n">
-        <v>6942580</v>
+        <v>6942497</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6470,10 +6475,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126057533</v>
+        <v>126057525</v>
       </c>
       <c r="B58" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6481,21 +6486,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6505,10 +6510,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550026</v>
+        <v>549977</v>
       </c>
       <c r="R58" t="n">
-        <v>6942422</v>
+        <v>6942580</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6541,11 +6546,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6674,52 +6674,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126052934</v>
+        <v>126057576</v>
       </c>
       <c r="B60" t="n">
-        <v>98334</v>
+        <v>78730</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>549977</v>
+        <v>550078</v>
       </c>
       <c r="R60" t="n">
-        <v>6942554</v>
+        <v>6942401</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6775,52 +6771,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126052802</v>
+        <v>126057601</v>
       </c>
       <c r="B61" t="n">
-        <v>98355</v>
+        <v>98338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>549987</v>
+        <v>550096</v>
       </c>
       <c r="R61" t="n">
-        <v>6942530</v>
+        <v>6942661</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6850,6 +6842,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6876,10 +6873,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126057601</v>
+        <v>126052934</v>
       </c>
       <c r="B62" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6904,20 +6901,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550096</v>
+        <v>549977</v>
       </c>
       <c r="R62" t="n">
-        <v>6942661</v>
+        <v>6942554</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6947,11 +6948,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6978,48 +6974,52 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126057576</v>
+        <v>126052802</v>
       </c>
       <c r="B63" t="n">
-        <v>78726</v>
+        <v>98359</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550078</v>
+        <v>549987</v>
       </c>
       <c r="R63" t="n">
-        <v>6942401</v>
+        <v>6942530</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7075,10 +7075,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126049594</v>
+        <v>126048239</v>
       </c>
       <c r="B64" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7114,10 +7114,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550141</v>
+        <v>550147</v>
       </c>
       <c r="R64" t="n">
-        <v>6942615</v>
+        <v>6942635</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7176,10 +7176,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126048239</v>
+        <v>126049594</v>
       </c>
       <c r="B65" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550147</v>
+        <v>550141</v>
       </c>
       <c r="R65" t="n">
-        <v>6942635</v>
+        <v>6942615</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7277,10 +7277,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126051507</v>
+        <v>126051197</v>
       </c>
       <c r="B66" t="n">
-        <v>98355</v>
+        <v>97216</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7288,38 +7288,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550089</v>
+        <v>550077</v>
       </c>
       <c r="R66" t="n">
-        <v>6942422</v>
+        <v>6942476</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7378,10 +7374,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126051197</v>
+        <v>126051507</v>
       </c>
       <c r="B67" t="n">
-        <v>97212</v>
+        <v>98359</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7389,34 +7385,38 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550077</v>
+        <v>550089</v>
       </c>
       <c r="R67" t="n">
-        <v>6942476</v>
+        <v>6942422</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7478,7 +7478,7 @@
         <v>126057594</v>
       </c>
       <c r="B68" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>126051112</v>
       </c>
       <c r="B70" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>126053048</v>
       </c>
       <c r="B71" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>126057583</v>
       </c>
       <c r="B72" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>126057578</v>
       </c>
       <c r="B73" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>126057549</v>
       </c>
       <c r="B74" t="n">
-        <v>91682</v>
+        <v>91686</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>126049570</v>
       </c>
       <c r="B75" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8276,49 +8276,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126051602</v>
+        <v>126050913</v>
       </c>
       <c r="B76" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550089</v>
+        <v>550088</v>
       </c>
       <c r="R76" t="n">
-        <v>6942422</v>
+        <v>6942520</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8351,6 +8347,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8377,10 +8378,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126050913</v>
+        <v>126057606</v>
       </c>
       <c r="B77" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8412,13 +8413,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550088</v>
+        <v>550034</v>
       </c>
       <c r="R77" t="n">
-        <v>6942520</v>
+        <v>6942421</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8448,11 +8449,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8479,10 +8475,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126057606</v>
+        <v>126057904</v>
       </c>
       <c r="B78" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8490,34 +8486,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550034</v>
+        <v>549997</v>
       </c>
       <c r="R78" t="n">
-        <v>6942421</v>
+        <v>6942637</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8576,48 +8572,52 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126057904</v>
+        <v>126051602</v>
       </c>
       <c r="B79" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>549997</v>
+        <v>550089</v>
       </c>
       <c r="R79" t="n">
-        <v>6942637</v>
+        <v>6942422</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>126051270</v>
       </c>
       <c r="B80" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>126057559</v>
       </c>
       <c r="B81" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>126057574</v>
       </c>
       <c r="B82" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>126057524</v>
       </c>
       <c r="B83" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9172,52 +9172,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126052873</v>
+        <v>126057531</v>
       </c>
       <c r="B85" t="n">
-        <v>98334</v>
+        <v>57651</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>549989</v>
+        <v>549974</v>
       </c>
       <c r="R85" t="n">
-        <v>6942554</v>
+        <v>6942584</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9247,6 +9243,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9273,32 +9274,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126052827</v>
+        <v>126057535</v>
       </c>
       <c r="B86" t="n">
-        <v>97212</v>
+        <v>57651</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9308,13 +9309,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>549987</v>
+        <v>550047</v>
       </c>
       <c r="R86" t="n">
-        <v>6942530</v>
+        <v>6942401</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9344,6 +9345,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9370,10 +9376,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126057531</v>
+        <v>126057575</v>
       </c>
       <c r="B87" t="n">
-        <v>57651</v>
+        <v>78730</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9381,21 +9387,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9405,10 +9411,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>549974</v>
+        <v>550022</v>
       </c>
       <c r="R87" t="n">
-        <v>6942584</v>
+        <v>6942537</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9441,11 +9447,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9472,32 +9473,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126057535</v>
+        <v>126057556</v>
       </c>
       <c r="B88" t="n">
-        <v>57651</v>
+        <v>80103</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9507,10 +9508,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550047</v>
+        <v>550074</v>
       </c>
       <c r="R88" t="n">
-        <v>6942401</v>
+        <v>6942641</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9543,11 +9544,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9574,10 +9570,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126057575</v>
+        <v>126052154</v>
       </c>
       <c r="B89" t="n">
-        <v>78726</v>
+        <v>78972</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9585,21 +9581,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9609,13 +9605,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550022</v>
+        <v>550021</v>
       </c>
       <c r="R89" t="n">
-        <v>6942537</v>
+        <v>6942450</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9645,6 +9641,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9671,48 +9672,52 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126057556</v>
+        <v>126052873</v>
       </c>
       <c r="B90" t="n">
-        <v>80099</v>
+        <v>98338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550074</v>
+        <v>549989</v>
       </c>
       <c r="R90" t="n">
-        <v>6942641</v>
+        <v>6942554</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9768,32 +9773,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126052154</v>
+        <v>126052827</v>
       </c>
       <c r="B91" t="n">
-        <v>78968</v>
+        <v>97216</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9803,10 +9808,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550021</v>
+        <v>549987</v>
       </c>
       <c r="R91" t="n">
-        <v>6942450</v>
+        <v>6942530</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9839,11 +9844,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9870,48 +9870,53 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126057923</v>
+        <v>126050713</v>
       </c>
       <c r="B92" t="n">
-        <v>98334</v>
+        <v>56834</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550122</v>
+        <v>550120</v>
       </c>
       <c r="R92" t="n">
-        <v>6942671</v>
+        <v>6942506</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9941,11 +9946,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9972,32 +9972,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126057593</v>
+        <v>126057540</v>
       </c>
       <c r="B93" t="n">
-        <v>98334</v>
+        <v>57651</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10007,10 +10007,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550137</v>
+        <v>550138</v>
       </c>
       <c r="R93" t="n">
-        <v>6942555</v>
+        <v>6942638</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10074,32 +10074,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126057577</v>
+        <v>126057593</v>
       </c>
       <c r="B94" t="n">
-        <v>78726</v>
+        <v>98338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10109,10 +10109,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550101</v>
+        <v>550137</v>
       </c>
       <c r="R94" t="n">
-        <v>6942551</v>
+        <v>6942555</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10145,6 +10145,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10171,45 +10176,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126057540</v>
+        <v>126057923</v>
       </c>
       <c r="B95" t="n">
-        <v>57651</v>
+        <v>98338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>550138</v>
+        <v>550122</v>
       </c>
       <c r="R95" t="n">
-        <v>6942638</v>
+        <v>6942671</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10246,7 +10251,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall.</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10273,10 +10278,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126057581</v>
+        <v>126057577</v>
       </c>
       <c r="B96" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10308,10 +10313,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>550004</v>
+        <v>550101</v>
       </c>
       <c r="R96" t="n">
-        <v>6942625</v>
+        <v>6942551</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10370,10 +10375,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126050713</v>
+        <v>126057581</v>
       </c>
       <c r="B97" t="n">
-        <v>56834</v>
+        <v>78730</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10381,42 +10386,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>550120</v>
+        <v>550004</v>
       </c>
       <c r="R97" t="n">
-        <v>6942506</v>
+        <v>6942625</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -5568,45 +5568,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126051690</v>
+        <v>126051408</v>
       </c>
       <c r="B49" t="n">
-        <v>80103</v>
+        <v>57648</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550110</v>
+        <v>550089</v>
       </c>
       <c r="R49" t="n">
-        <v>6942386</v>
+        <v>6942422</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5639,6 +5644,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5665,53 +5675,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126051408</v>
+        <v>126057602</v>
       </c>
       <c r="B50" t="n">
-        <v>57648</v>
+        <v>98338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550089</v>
+        <v>550099</v>
       </c>
       <c r="R50" t="n">
-        <v>6942422</v>
+        <v>6942666</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5745,7 +5750,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5772,32 +5777,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126057602</v>
+        <v>126051690</v>
       </c>
       <c r="B51" t="n">
-        <v>98338</v>
+        <v>80103</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5807,13 +5812,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550099</v>
+        <v>550110</v>
       </c>
       <c r="R51" t="n">
-        <v>6942666</v>
+        <v>6942386</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5843,11 +5848,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2387,45 +2387,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126057564</v>
+        <v>126057921</v>
       </c>
       <c r="B17" t="n">
-        <v>78731</v>
+        <v>98339</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550076</v>
+        <v>550142</v>
       </c>
       <c r="R17" t="n">
-        <v>6942390</v>
+        <v>6942582</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2458,6 +2458,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057921</v>
+        <v>126057597</v>
       </c>
       <c r="B18" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2515,14 +2520,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550142</v>
+        <v>550099</v>
       </c>
       <c r="R18" t="n">
-        <v>6942582</v>
+        <v>6942637</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2559,7 +2564,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>30 stycken</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,32 +2591,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057597</v>
+        <v>126057564</v>
       </c>
       <c r="B19" t="n">
-        <v>98338</v>
+        <v>78731</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2621,10 +2626,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550099</v>
+        <v>550076</v>
       </c>
       <c r="R19" t="n">
-        <v>6942637</v>
+        <v>6942390</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2657,11 +2662,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>8 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057935</v>
+        <v>126057526</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,34 +2796,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550099</v>
+        <v>550079</v>
       </c>
       <c r="R21" t="n">
-        <v>6942670</v>
+        <v>6942497</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057526</v>
+        <v>126057935</v>
       </c>
       <c r="B22" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,34 +2893,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550079</v>
+        <v>550099</v>
       </c>
       <c r="R22" t="n">
-        <v>6942497</v>
+        <v>6942670</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2982,7 +2982,7 @@
         <v>126057582</v>
       </c>
       <c r="B23" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126057545</v>
+        <v>126051522</v>
       </c>
       <c r="B25" t="n">
-        <v>91243</v>
+        <v>80103</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3189,21 +3189,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1205</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3213,13 +3213,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550011</v>
+        <v>550089</v>
       </c>
       <c r="R25" t="n">
-        <v>6942535</v>
+        <v>6942422</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3275,32 +3275,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126052983</v>
+        <v>126057544</v>
       </c>
       <c r="B26" t="n">
-        <v>78730</v>
+        <v>80104</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3310,13 +3310,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549977</v>
+        <v>550094</v>
       </c>
       <c r="R26" t="n">
-        <v>6942554</v>
+        <v>6942584</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126052248</v>
+        <v>126057532</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3383,21 +3383,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550004</v>
+        <v>550020</v>
       </c>
       <c r="R27" t="n">
-        <v>6942504</v>
+        <v>6942390</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom området</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3474,10 +3474,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126051522</v>
+        <v>126057545</v>
       </c>
       <c r="B28" t="n">
-        <v>80103</v>
+        <v>91243</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3485,21 +3485,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>1205</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550089</v>
+        <v>550011</v>
       </c>
       <c r="R28" t="n">
-        <v>6942422</v>
+        <v>6942535</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3571,32 +3571,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057544</v>
+        <v>126052983</v>
       </c>
       <c r="B29" t="n">
-        <v>80104</v>
+        <v>78730</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3606,13 +3606,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550094</v>
+        <v>549977</v>
       </c>
       <c r="R29" t="n">
-        <v>6942584</v>
+        <v>6942554</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3668,10 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057532</v>
+        <v>126052248</v>
       </c>
       <c r="B30" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,21 +3679,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550020</v>
+        <v>550004</v>
       </c>
       <c r="R30" t="n">
-        <v>6942390</v>
+        <v>6942504</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Rikligt med garnlav inom området</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3773,7 +3773,7 @@
         <v>126051074</v>
       </c>
       <c r="B31" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,32 +3871,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057579</v>
+        <v>126057596</v>
       </c>
       <c r="B32" t="n">
-        <v>78730</v>
+        <v>98339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550006</v>
+        <v>550092</v>
       </c>
       <c r="R32" t="n">
-        <v>6942636</v>
+        <v>6942597</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3942,6 +3942,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3968,45 +3973,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057937</v>
+        <v>126057591</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550147</v>
+        <v>550020</v>
       </c>
       <c r="R33" t="n">
-        <v>6942582</v>
+        <v>6942543</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4043,7 +4048,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4070,10 +4075,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057567</v>
+        <v>126057538</v>
       </c>
       <c r="B34" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4081,21 +4086,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4105,10 +4110,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550001</v>
+        <v>550041</v>
       </c>
       <c r="R34" t="n">
-        <v>6942503</v>
+        <v>6942496</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4141,6 +4146,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4167,10 +4177,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126053984</v>
+        <v>126057579</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4178,21 +4188,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4202,13 +4212,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549984</v>
+        <v>550006</v>
       </c>
       <c r="R35" t="n">
-        <v>6942510</v>
+        <v>6942636</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4238,11 +4248,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4269,10 +4274,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057538</v>
+        <v>126057937</v>
       </c>
       <c r="B36" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4280,34 +4285,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550041</v>
+        <v>550147</v>
       </c>
       <c r="R36" t="n">
-        <v>6942496</v>
+        <v>6942582</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4344,7 +4349,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4371,32 +4376,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057596</v>
+        <v>126053984</v>
       </c>
       <c r="B37" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4406,13 +4411,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550092</v>
+        <v>549984</v>
       </c>
       <c r="R37" t="n">
-        <v>6942597</v>
+        <v>6942510</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4446,7 +4451,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4473,32 +4478,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057591</v>
+        <v>126057567</v>
       </c>
       <c r="B38" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4508,10 +4513,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550020</v>
+        <v>550001</v>
       </c>
       <c r="R38" t="n">
-        <v>6942543</v>
+        <v>6942503</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4544,11 +4549,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>3 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4575,32 +4575,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126052912</v>
+        <v>126057592</v>
       </c>
       <c r="B39" t="n">
-        <v>80103</v>
+        <v>98339</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549977</v>
+        <v>550038</v>
       </c>
       <c r="R39" t="n">
-        <v>6942554</v>
+        <v>6942494</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4646,6 +4646,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>28 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4672,48 +4677,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057569</v>
+        <v>126052420</v>
       </c>
       <c r="B40" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550006</v>
+        <v>549984</v>
       </c>
       <c r="R40" t="n">
-        <v>6942630</v>
+        <v>6942510</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4769,10 +4778,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126057592</v>
+        <v>126057600</v>
       </c>
       <c r="B41" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4804,10 +4813,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550038</v>
+        <v>550095</v>
       </c>
       <c r="R41" t="n">
-        <v>6942494</v>
+        <v>6942646</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4844,7 +4853,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>28 ex</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4871,49 +4880,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126052420</v>
+        <v>126052912</v>
       </c>
       <c r="B42" t="n">
-        <v>98338</v>
+        <v>80103</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549984</v>
+        <v>549977</v>
       </c>
       <c r="R42" t="n">
-        <v>6942510</v>
+        <v>6942554</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,32 +4977,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126057600</v>
+        <v>126057569</v>
       </c>
       <c r="B43" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5007,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550095</v>
+        <v>550006</v>
       </c>
       <c r="R43" t="n">
-        <v>6942646</v>
+        <v>6942630</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5043,11 +5048,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5074,10 +5074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057896</v>
+        <v>126052332</v>
       </c>
       <c r="B44" t="n">
-        <v>80103</v>
+        <v>98360</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5085,37 +5085,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550007</v>
+        <v>549984</v>
       </c>
       <c r="R44" t="n">
-        <v>6942646</v>
+        <v>6942510</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5171,45 +5175,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057568</v>
+        <v>126057896</v>
       </c>
       <c r="B45" t="n">
-        <v>80075</v>
+        <v>80103</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550093</v>
+        <v>550007</v>
       </c>
       <c r="R45" t="n">
-        <v>6942579</v>
+        <v>6942646</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5268,52 +5272,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126052332</v>
+        <v>126057568</v>
       </c>
       <c r="B46" t="n">
-        <v>98359</v>
+        <v>80075</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549984</v>
+        <v>550093</v>
       </c>
       <c r="R46" t="n">
-        <v>6942510</v>
+        <v>6942579</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>126057930</v>
       </c>
       <c r="B47" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5568,50 +5568,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126051408</v>
+        <v>126051690</v>
       </c>
       <c r="B49" t="n">
-        <v>57648</v>
+        <v>80103</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550089</v>
+        <v>550110</v>
       </c>
       <c r="R49" t="n">
-        <v>6942422</v>
+        <v>6942386</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5644,11 +5639,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5678,7 +5668,7 @@
         <v>126057602</v>
       </c>
       <c r="B50" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5777,10 +5767,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126051690</v>
+        <v>126049249</v>
       </c>
       <c r="B51" t="n">
-        <v>80103</v>
+        <v>58020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5788,34 +5778,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550110</v>
+        <v>550135</v>
       </c>
       <c r="R51" t="n">
-        <v>6942386</v>
+        <v>6942628</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5874,27 +5873,27 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126049249</v>
+        <v>126051408</v>
       </c>
       <c r="B52" t="n">
-        <v>58020</v>
+        <v>57648</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5902,14 +5901,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5918,10 +5913,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550135</v>
+        <v>550089</v>
       </c>
       <c r="R52" t="n">
-        <v>6942628</v>
+        <v>6942422</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5954,6 +5949,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6271,10 +6271,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126057533</v>
+        <v>126057525</v>
       </c>
       <c r="B56" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6282,21 +6282,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6306,10 +6306,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550026</v>
+        <v>549977</v>
       </c>
       <c r="R56" t="n">
-        <v>6942422</v>
+        <v>6942580</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6342,11 +6342,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6475,10 +6470,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126057525</v>
+        <v>126057533</v>
       </c>
       <c r="B58" t="n">
-        <v>91232</v>
+        <v>57651</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6486,21 +6481,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6510,10 +6505,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>549977</v>
+        <v>550026</v>
       </c>
       <c r="R58" t="n">
-        <v>6942580</v>
+        <v>6942422</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6546,6 +6541,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6572,38 +6572,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126051839</v>
+        <v>126048239</v>
       </c>
       <c r="B59" t="n">
-        <v>56843</v>
+        <v>98339</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>56</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6612,10 +6611,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550088</v>
+        <v>550147</v>
       </c>
       <c r="R59" t="n">
-        <v>6942377</v>
+        <v>6942635</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6674,48 +6673,52 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126057576</v>
+        <v>126049594</v>
       </c>
       <c r="B60" t="n">
-        <v>78730</v>
+        <v>98339</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550078</v>
+        <v>550141</v>
       </c>
       <c r="R60" t="n">
-        <v>6942401</v>
+        <v>6942615</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6771,32 +6774,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126057601</v>
+        <v>126057576</v>
       </c>
       <c r="B61" t="n">
-        <v>98338</v>
+        <v>78730</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6806,10 +6809,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550096</v>
+        <v>550078</v>
       </c>
       <c r="R61" t="n">
-        <v>6942661</v>
+        <v>6942401</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6842,11 +6845,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6873,37 +6871,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126052934</v>
+        <v>126051839</v>
       </c>
       <c r="B62" t="n">
-        <v>98338</v>
+        <v>56843</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>29</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6912,10 +6911,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>549977</v>
+        <v>550088</v>
       </c>
       <c r="R62" t="n">
-        <v>6942554</v>
+        <v>6942377</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6977,7 +6976,7 @@
         <v>126052802</v>
       </c>
       <c r="B63" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7075,10 +7074,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126048239</v>
+        <v>126057601</v>
       </c>
       <c r="B64" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7103,24 +7102,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550147</v>
+        <v>550096</v>
       </c>
       <c r="R64" t="n">
-        <v>6942635</v>
+        <v>6942661</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7150,6 +7145,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7176,10 +7176,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126049594</v>
+        <v>126052934</v>
       </c>
       <c r="B65" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550141</v>
+        <v>549977</v>
       </c>
       <c r="R65" t="n">
-        <v>6942615</v>
+        <v>6942554</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7280,7 +7280,7 @@
         <v>126051197</v>
       </c>
       <c r="B66" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>126051507</v>
       </c>
       <c r="B67" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>126057594</v>
       </c>
       <c r="B68" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>126057583</v>
       </c>
       <c r="B72" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>126051602</v>
       </c>
       <c r="B79" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8673,52 +8673,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126051270</v>
+        <v>126057574</v>
       </c>
       <c r="B80" t="n">
-        <v>98338</v>
+        <v>78730</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550065</v>
+        <v>549990</v>
       </c>
       <c r="R80" t="n">
-        <v>6942463</v>
+        <v>6942590</v>
       </c>
       <c r="S80" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8774,10 +8770,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126057559</v>
+        <v>126057524</v>
       </c>
       <c r="B81" t="n">
-        <v>80103</v>
+        <v>91197</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8785,21 +8781,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8809,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550000</v>
+        <v>550079</v>
       </c>
       <c r="R81" t="n">
-        <v>6942626</v>
+        <v>6942497</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8871,48 +8867,53 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126057574</v>
+        <v>126047488</v>
       </c>
       <c r="B82" t="n">
-        <v>78730</v>
+        <v>43933</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>101735</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>549990</v>
+        <v>550158</v>
       </c>
       <c r="R82" t="n">
-        <v>6942590</v>
+        <v>6942653</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8942,6 +8943,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8968,48 +8974,52 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126057524</v>
+        <v>126051270</v>
       </c>
       <c r="B83" t="n">
-        <v>91197</v>
+        <v>98339</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550079</v>
+        <v>550065</v>
       </c>
       <c r="R83" t="n">
-        <v>6942497</v>
+        <v>6942463</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9065,10 +9075,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126047488</v>
+        <v>126057559</v>
       </c>
       <c r="B84" t="n">
-        <v>43933</v>
+        <v>80103</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9076,42 +9086,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>101735</v>
+        <v>6461</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550158</v>
+        <v>550000</v>
       </c>
       <c r="R84" t="n">
-        <v>6942653</v>
+        <v>6942626</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9141,11 +9146,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9172,48 +9172,52 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126057531</v>
+        <v>126052873</v>
       </c>
       <c r="B85" t="n">
-        <v>57651</v>
+        <v>98339</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>549974</v>
+        <v>549989</v>
       </c>
       <c r="R85" t="n">
-        <v>6942584</v>
+        <v>6942554</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9243,11 +9247,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9274,10 +9273,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126057535</v>
+        <v>126057575</v>
       </c>
       <c r="B86" t="n">
-        <v>57651</v>
+        <v>78730</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9285,21 +9284,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9309,10 +9308,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550047</v>
+        <v>550022</v>
       </c>
       <c r="R86" t="n">
-        <v>6942401</v>
+        <v>6942537</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9345,11 +9344,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9376,10 +9370,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126057575</v>
+        <v>126052154</v>
       </c>
       <c r="B87" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9387,21 +9381,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9411,13 +9405,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550022</v>
+        <v>550021</v>
       </c>
       <c r="R87" t="n">
-        <v>6942537</v>
+        <v>6942450</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9447,6 +9441,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9570,10 +9569,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126052154</v>
+        <v>126057531</v>
       </c>
       <c r="B89" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9581,21 +9580,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9605,13 +9604,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550021</v>
+        <v>549974</v>
       </c>
       <c r="R89" t="n">
-        <v>6942450</v>
+        <v>6942584</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9645,7 +9644,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9672,52 +9671,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126052873</v>
+        <v>126057535</v>
       </c>
       <c r="B90" t="n">
-        <v>98338</v>
+        <v>57651</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>549989</v>
+        <v>550047</v>
       </c>
       <c r="R90" t="n">
-        <v>6942554</v>
+        <v>6942401</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9747,6 +9742,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9776,7 +9776,7 @@
         <v>126052827</v>
       </c>
       <c r="B91" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9870,10 +9870,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126050713</v>
+        <v>126057577</v>
       </c>
       <c r="B92" t="n">
-        <v>56834</v>
+        <v>78730</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9881,42 +9881,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550120</v>
+        <v>550101</v>
       </c>
       <c r="R92" t="n">
-        <v>6942506</v>
+        <v>6942551</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9972,10 +9967,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126057540</v>
+        <v>126057581</v>
       </c>
       <c r="B93" t="n">
-        <v>57651</v>
+        <v>78730</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9983,21 +9978,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10007,10 +10002,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550138</v>
+        <v>550004</v>
       </c>
       <c r="R93" t="n">
-        <v>6942638</v>
+        <v>6942625</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10043,11 +10038,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10074,48 +10064,53 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126057593</v>
+        <v>126050713</v>
       </c>
       <c r="B94" t="n">
-        <v>98338</v>
+        <v>56834</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550137</v>
+        <v>550120</v>
       </c>
       <c r="R94" t="n">
-        <v>6942555</v>
+        <v>6942506</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10145,11 +10140,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>3 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10176,45 +10166,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126057923</v>
+        <v>126057540</v>
       </c>
       <c r="B95" t="n">
-        <v>98338</v>
+        <v>57651</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>550122</v>
+        <v>550138</v>
       </c>
       <c r="R95" t="n">
-        <v>6942671</v>
+        <v>6942638</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10251,7 +10241,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10278,32 +10268,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126057577</v>
+        <v>126057593</v>
       </c>
       <c r="B96" t="n">
-        <v>78730</v>
+        <v>98339</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10313,10 +10303,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>550101</v>
+        <v>550137</v>
       </c>
       <c r="R96" t="n">
-        <v>6942551</v>
+        <v>6942555</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10349,6 +10339,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10375,45 +10370,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126057581</v>
+        <v>126057923</v>
       </c>
       <c r="B97" t="n">
-        <v>78730</v>
+        <v>98339</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>550004</v>
+        <v>550122</v>
       </c>
       <c r="R97" t="n">
-        <v>6942625</v>
+        <v>6942671</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10446,6 +10441,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -3081,32 +3081,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126050880</v>
+        <v>126057532</v>
       </c>
       <c r="B24" t="n">
-        <v>80103</v>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3116,13 +3116,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550088</v>
+        <v>550020</v>
       </c>
       <c r="R24" t="n">
-        <v>6942520</v>
+        <v>6942390</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,6 +3152,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3178,10 +3183,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126051522</v>
+        <v>126057545</v>
       </c>
       <c r="B25" t="n">
-        <v>80103</v>
+        <v>91243</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3189,21 +3194,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>1205</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3213,13 +3218,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550089</v>
+        <v>550011</v>
       </c>
       <c r="R25" t="n">
-        <v>6942422</v>
+        <v>6942535</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3275,32 +3280,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126057544</v>
+        <v>126052983</v>
       </c>
       <c r="B26" t="n">
-        <v>80104</v>
+        <v>78730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3310,13 +3315,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550094</v>
+        <v>549977</v>
       </c>
       <c r="R26" t="n">
-        <v>6942584</v>
+        <v>6942554</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3372,10 +3377,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126057532</v>
+        <v>126052248</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3383,21 +3388,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3407,13 +3412,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550020</v>
+        <v>550004</v>
       </c>
       <c r="R27" t="n">
-        <v>6942390</v>
+        <v>6942504</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3447,7 +3452,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Rikligt med garnlav inom området</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3474,10 +3479,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126057545</v>
+        <v>126050880</v>
       </c>
       <c r="B28" t="n">
-        <v>91243</v>
+        <v>80103</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3485,21 +3490,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1205</v>
+        <v>6461</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3509,13 +3514,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550011</v>
+        <v>550088</v>
       </c>
       <c r="R28" t="n">
-        <v>6942535</v>
+        <v>6942520</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3571,32 +3576,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126052983</v>
+        <v>126051522</v>
       </c>
       <c r="B29" t="n">
-        <v>78730</v>
+        <v>80103</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3606,10 +3611,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549977</v>
+        <v>550089</v>
       </c>
       <c r="R29" t="n">
-        <v>6942554</v>
+        <v>6942422</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3668,32 +3673,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126052248</v>
+        <v>126057544</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>80104</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3703,13 +3708,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550004</v>
+        <v>550094</v>
       </c>
       <c r="R30" t="n">
-        <v>6942504</v>
+        <v>6942584</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3739,11 +3744,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom området</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4575,32 +4575,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057592</v>
+        <v>126052912</v>
       </c>
       <c r="B39" t="n">
-        <v>98339</v>
+        <v>80103</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550038</v>
+        <v>549977</v>
       </c>
       <c r="R39" t="n">
-        <v>6942494</v>
+        <v>6942554</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4646,11 +4646,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>28 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4677,52 +4672,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126052420</v>
+        <v>126057569</v>
       </c>
       <c r="B40" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549984</v>
+        <v>550006</v>
       </c>
       <c r="R40" t="n">
-        <v>6942510</v>
+        <v>6942630</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4778,7 +4769,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126057600</v>
+        <v>126057592</v>
       </c>
       <c r="B41" t="n">
         <v>98339</v>
@@ -4813,10 +4804,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550095</v>
+        <v>550038</v>
       </c>
       <c r="R41" t="n">
-        <v>6942646</v>
+        <v>6942494</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4853,7 +4844,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>28 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4880,45 +4871,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126052912</v>
+        <v>126052420</v>
       </c>
       <c r="B42" t="n">
-        <v>80103</v>
+        <v>98339</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549977</v>
+        <v>549984</v>
       </c>
       <c r="R42" t="n">
-        <v>6942554</v>
+        <v>6942510</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4977,32 +4972,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126057569</v>
+        <v>126057600</v>
       </c>
       <c r="B43" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5012,10 +5007,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550006</v>
+        <v>550095</v>
       </c>
       <c r="R43" t="n">
-        <v>6942630</v>
+        <v>6942646</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5048,6 +5043,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5074,10 +5074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126052332</v>
+        <v>126057896</v>
       </c>
       <c r="B44" t="n">
-        <v>98360</v>
+        <v>80103</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5085,41 +5085,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549984</v>
+        <v>550007</v>
       </c>
       <c r="R44" t="n">
-        <v>6942510</v>
+        <v>6942646</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5175,45 +5171,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057896</v>
+        <v>126057568</v>
       </c>
       <c r="B45" t="n">
-        <v>80103</v>
+        <v>80075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550007</v>
+        <v>550093</v>
       </c>
       <c r="R45" t="n">
-        <v>6942646</v>
+        <v>6942579</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5272,48 +5268,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057568</v>
+        <v>126052332</v>
       </c>
       <c r="B46" t="n">
-        <v>80075</v>
+        <v>98360</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550093</v>
+        <v>549984</v>
       </c>
       <c r="R46" t="n">
-        <v>6942579</v>
+        <v>6942510</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5568,10 +5568,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126051690</v>
+        <v>126049249</v>
       </c>
       <c r="B49" t="n">
-        <v>80103</v>
+        <v>58020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5579,34 +5579,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550110</v>
+        <v>550135</v>
       </c>
       <c r="R49" t="n">
-        <v>6942386</v>
+        <v>6942628</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5665,32 +5674,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126057602</v>
+        <v>126051690</v>
       </c>
       <c r="B50" t="n">
-        <v>98339</v>
+        <v>80103</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5700,13 +5709,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550099</v>
+        <v>550110</v>
       </c>
       <c r="R50" t="n">
-        <v>6942666</v>
+        <v>6942386</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5736,11 +5745,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5767,27 +5771,27 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126049249</v>
+        <v>126051408</v>
       </c>
       <c r="B51" t="n">
-        <v>58020</v>
+        <v>57648</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5795,14 +5799,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5811,10 +5811,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550135</v>
+        <v>550089</v>
       </c>
       <c r="R51" t="n">
-        <v>6942628</v>
+        <v>6942422</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5847,6 +5847,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5873,53 +5878,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126051408</v>
+        <v>126057602</v>
       </c>
       <c r="B52" t="n">
-        <v>57648</v>
+        <v>98339</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550089</v>
+        <v>550099</v>
       </c>
       <c r="R52" t="n">
-        <v>6942422</v>
+        <v>6942666</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5980,10 +5980,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057915</v>
+        <v>126057565</v>
       </c>
       <c r="B53" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5991,34 +5991,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550145</v>
+        <v>550139</v>
       </c>
       <c r="R53" t="n">
-        <v>6942577</v>
+        <v>6942641</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6077,32 +6077,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057898</v>
+        <v>126057915</v>
       </c>
       <c r="B54" t="n">
-        <v>80103</v>
+        <v>78730</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>549997</v>
+        <v>550145</v>
       </c>
       <c r="R54" t="n">
-        <v>6942637</v>
+        <v>6942577</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6174,45 +6174,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057565</v>
+        <v>126057898</v>
       </c>
       <c r="B55" t="n">
-        <v>78731</v>
+        <v>80103</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550139</v>
+        <v>549997</v>
       </c>
       <c r="R55" t="n">
-        <v>6942641</v>
+        <v>6942637</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6271,10 +6271,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126057525</v>
+        <v>126057533</v>
       </c>
       <c r="B56" t="n">
-        <v>91232</v>
+        <v>57651</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6282,21 +6282,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6306,10 +6306,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>549977</v>
+        <v>550026</v>
       </c>
       <c r="R56" t="n">
-        <v>6942580</v>
+        <v>6942422</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6342,6 +6342,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6368,53 +6373,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126050777</v>
+        <v>126057525</v>
       </c>
       <c r="B57" t="n">
-        <v>56843</v>
+        <v>91232</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550093</v>
+        <v>549977</v>
       </c>
       <c r="R57" t="n">
-        <v>6942497</v>
+        <v>6942580</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6470,48 +6470,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126057533</v>
+        <v>126050777</v>
       </c>
       <c r="B58" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550026</v>
+        <v>550093</v>
       </c>
       <c r="R58" t="n">
-        <v>6942422</v>
+        <v>6942497</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6541,11 +6546,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7679,32 +7679,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126051112</v>
+        <v>126053048</v>
       </c>
       <c r="B70" t="n">
-        <v>80103</v>
+        <v>78972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550093</v>
+        <v>549965</v>
       </c>
       <c r="R70" t="n">
-        <v>6942497</v>
+        <v>6942583</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7750,6 +7750,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I området</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7776,32 +7781,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126053048</v>
+        <v>126051112</v>
       </c>
       <c r="B71" t="n">
-        <v>78972</v>
+        <v>80103</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7811,10 +7816,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>549965</v>
+        <v>550093</v>
       </c>
       <c r="R71" t="n">
-        <v>6942583</v>
+        <v>6942497</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7847,11 +7852,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I området</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9172,52 +9172,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126052873</v>
+        <v>126057575</v>
       </c>
       <c r="B85" t="n">
-        <v>98339</v>
+        <v>78730</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>549989</v>
+        <v>550022</v>
       </c>
       <c r="R85" t="n">
-        <v>6942554</v>
+        <v>6942537</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9273,10 +9269,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126057575</v>
+        <v>126052154</v>
       </c>
       <c r="B86" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9284,21 +9280,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9308,13 +9304,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550022</v>
+        <v>550021</v>
       </c>
       <c r="R86" t="n">
-        <v>6942537</v>
+        <v>6942450</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9344,6 +9340,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9370,32 +9371,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126052154</v>
+        <v>126057556</v>
       </c>
       <c r="B87" t="n">
-        <v>78972</v>
+        <v>80103</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9405,13 +9406,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550021</v>
+        <v>550074</v>
       </c>
       <c r="R87" t="n">
-        <v>6942450</v>
+        <v>6942641</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9441,11 +9442,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9472,32 +9468,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126057556</v>
+        <v>126057531</v>
       </c>
       <c r="B88" t="n">
-        <v>80103</v>
+        <v>57651</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9507,10 +9503,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550074</v>
+        <v>549974</v>
       </c>
       <c r="R88" t="n">
-        <v>6942641</v>
+        <v>6942584</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9543,6 +9539,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9569,7 +9570,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126057531</v>
+        <v>126057535</v>
       </c>
       <c r="B89" t="n">
         <v>57651</v>
@@ -9604,10 +9605,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>549974</v>
+        <v>550047</v>
       </c>
       <c r="R89" t="n">
-        <v>6942584</v>
+        <v>6942401</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9644,7 +9645,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9671,32 +9672,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126057535</v>
+        <v>126052827</v>
       </c>
       <c r="B90" t="n">
-        <v>57651</v>
+        <v>97217</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9706,13 +9707,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550047</v>
+        <v>549987</v>
       </c>
       <c r="R90" t="n">
-        <v>6942401</v>
+        <v>6942530</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9742,11 +9743,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9773,45 +9769,49 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126052827</v>
+        <v>126052873</v>
       </c>
       <c r="B91" t="n">
-        <v>97217</v>
+        <v>98339</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>549987</v>
+        <v>549989</v>
       </c>
       <c r="R91" t="n">
-        <v>6942530</v>
+        <v>6942554</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -3081,32 +3081,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126057532</v>
+        <v>126050880</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>80103</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3116,13 +3116,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550020</v>
+        <v>550088</v>
       </c>
       <c r="R24" t="n">
-        <v>6942390</v>
+        <v>6942520</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,11 +3152,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3183,10 +3178,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126057545</v>
+        <v>126051522</v>
       </c>
       <c r="B25" t="n">
-        <v>91243</v>
+        <v>80103</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3194,21 +3189,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1205</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3218,13 +3213,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550011</v>
+        <v>550089</v>
       </c>
       <c r="R25" t="n">
-        <v>6942535</v>
+        <v>6942422</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3280,32 +3275,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126052983</v>
+        <v>126057544</v>
       </c>
       <c r="B26" t="n">
-        <v>78730</v>
+        <v>80104</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,13 +3310,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549977</v>
+        <v>550094</v>
       </c>
       <c r="R26" t="n">
-        <v>6942554</v>
+        <v>6942584</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3377,10 +3372,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126052248</v>
+        <v>126057532</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3388,21 +3383,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3412,13 +3407,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550004</v>
+        <v>550020</v>
       </c>
       <c r="R27" t="n">
-        <v>6942504</v>
+        <v>6942390</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3452,7 +3447,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom området</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3479,10 +3474,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126050880</v>
+        <v>126057545</v>
       </c>
       <c r="B28" t="n">
-        <v>80103</v>
+        <v>91243</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3490,21 +3485,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>1205</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3514,13 +3509,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550088</v>
+        <v>550011</v>
       </c>
       <c r="R28" t="n">
-        <v>6942520</v>
+        <v>6942535</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3576,32 +3571,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126051522</v>
+        <v>126052983</v>
       </c>
       <c r="B29" t="n">
-        <v>80103</v>
+        <v>78730</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3611,10 +3606,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550089</v>
+        <v>549977</v>
       </c>
       <c r="R29" t="n">
-        <v>6942422</v>
+        <v>6942554</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3673,32 +3668,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057544</v>
+        <v>126052248</v>
       </c>
       <c r="B30" t="n">
-        <v>80104</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3708,13 +3703,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550094</v>
+        <v>550004</v>
       </c>
       <c r="R30" t="n">
-        <v>6942584</v>
+        <v>6942504</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3744,6 +3739,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom området</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4575,32 +4575,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126052912</v>
+        <v>126057592</v>
       </c>
       <c r="B39" t="n">
-        <v>80103</v>
+        <v>98339</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549977</v>
+        <v>550038</v>
       </c>
       <c r="R39" t="n">
-        <v>6942554</v>
+        <v>6942494</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4646,6 +4646,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>28 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4672,48 +4677,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057569</v>
+        <v>126052420</v>
       </c>
       <c r="B40" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550006</v>
+        <v>549984</v>
       </c>
       <c r="R40" t="n">
-        <v>6942630</v>
+        <v>6942510</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4769,7 +4778,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126057592</v>
+        <v>126057600</v>
       </c>
       <c r="B41" t="n">
         <v>98339</v>
@@ -4804,10 +4813,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550038</v>
+        <v>550095</v>
       </c>
       <c r="R41" t="n">
-        <v>6942494</v>
+        <v>6942646</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4844,7 +4853,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>28 ex</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4871,49 +4880,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126052420</v>
+        <v>126052912</v>
       </c>
       <c r="B42" t="n">
-        <v>98339</v>
+        <v>80103</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549984</v>
+        <v>549977</v>
       </c>
       <c r="R42" t="n">
-        <v>6942510</v>
+        <v>6942554</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,32 +4977,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126057600</v>
+        <v>126057569</v>
       </c>
       <c r="B43" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5007,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550095</v>
+        <v>550006</v>
       </c>
       <c r="R43" t="n">
-        <v>6942646</v>
+        <v>6942630</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5043,11 +5048,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5074,10 +5074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057896</v>
+        <v>126052332</v>
       </c>
       <c r="B44" t="n">
-        <v>80103</v>
+        <v>98360</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5085,37 +5085,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550007</v>
+        <v>549984</v>
       </c>
       <c r="R44" t="n">
-        <v>6942646</v>
+        <v>6942510</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5171,45 +5175,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057568</v>
+        <v>126057896</v>
       </c>
       <c r="B45" t="n">
-        <v>80075</v>
+        <v>80103</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550093</v>
+        <v>550007</v>
       </c>
       <c r="R45" t="n">
-        <v>6942579</v>
+        <v>6942646</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5268,52 +5272,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126052332</v>
+        <v>126057568</v>
       </c>
       <c r="B46" t="n">
-        <v>98360</v>
+        <v>80075</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549984</v>
+        <v>550093</v>
       </c>
       <c r="R46" t="n">
-        <v>6942510</v>
+        <v>6942579</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5980,10 +5980,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057565</v>
+        <v>126057915</v>
       </c>
       <c r="B53" t="n">
-        <v>78731</v>
+        <v>78730</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5991,34 +5991,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550139</v>
+        <v>550145</v>
       </c>
       <c r="R53" t="n">
-        <v>6942641</v>
+        <v>6942577</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6077,32 +6077,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057915</v>
+        <v>126057898</v>
       </c>
       <c r="B54" t="n">
-        <v>78730</v>
+        <v>80103</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550145</v>
+        <v>549997</v>
       </c>
       <c r="R54" t="n">
-        <v>6942577</v>
+        <v>6942637</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6174,45 +6174,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057898</v>
+        <v>126057565</v>
       </c>
       <c r="B55" t="n">
-        <v>80103</v>
+        <v>78731</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>549997</v>
+        <v>550139</v>
       </c>
       <c r="R55" t="n">
-        <v>6942637</v>
+        <v>6942641</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6271,10 +6271,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126057533</v>
+        <v>126057525</v>
       </c>
       <c r="B56" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6282,21 +6282,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6306,10 +6306,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550026</v>
+        <v>549977</v>
       </c>
       <c r="R56" t="n">
-        <v>6942422</v>
+        <v>6942580</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6342,11 +6342,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6373,48 +6368,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126057525</v>
+        <v>126050777</v>
       </c>
       <c r="B57" t="n">
-        <v>91232</v>
+        <v>56843</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>549977</v>
+        <v>550093</v>
       </c>
       <c r="R57" t="n">
-        <v>6942580</v>
+        <v>6942497</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6470,53 +6470,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126050777</v>
+        <v>126057533</v>
       </c>
       <c r="B58" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550093</v>
+        <v>550026</v>
       </c>
       <c r="R58" t="n">
-        <v>6942497</v>
+        <v>6942422</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6546,6 +6541,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8673,32 +8673,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126057574</v>
+        <v>126057559</v>
       </c>
       <c r="B80" t="n">
-        <v>78730</v>
+        <v>80103</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>549990</v>
+        <v>550000</v>
       </c>
       <c r="R80" t="n">
-        <v>6942590</v>
+        <v>6942626</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8770,32 +8770,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126057524</v>
+        <v>126057574</v>
       </c>
       <c r="B81" t="n">
-        <v>91197</v>
+        <v>78730</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550079</v>
+        <v>549990</v>
       </c>
       <c r="R81" t="n">
-        <v>6942497</v>
+        <v>6942590</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8867,10 +8867,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126047488</v>
+        <v>126057524</v>
       </c>
       <c r="B82" t="n">
-        <v>43933</v>
+        <v>91197</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8878,42 +8878,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>101735</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550158</v>
+        <v>550079</v>
       </c>
       <c r="R82" t="n">
-        <v>6942653</v>
+        <v>6942497</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8943,11 +8938,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9075,10 +9065,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126057559</v>
+        <v>126047488</v>
       </c>
       <c r="B84" t="n">
-        <v>80103</v>
+        <v>43933</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9086,37 +9076,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6461</v>
+        <v>101735</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550000</v>
+        <v>550158</v>
       </c>
       <c r="R84" t="n">
-        <v>6942626</v>
+        <v>6942653</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9146,6 +9141,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126057934</v>
+        <v>126057536</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,34 +2194,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550127</v>
+        <v>550113</v>
       </c>
       <c r="R15" t="n">
-        <v>6942669</v>
+        <v>6942389</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,32 +2285,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126057536</v>
+        <v>126057597</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>98341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550113</v>
+        <v>550099</v>
       </c>
       <c r="R16" t="n">
-        <v>6942389</v>
+        <v>6942637</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,7 +2390,7 @@
         <v>126057921</v>
       </c>
       <c r="B17" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,45 +2489,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057597</v>
+        <v>126057934</v>
       </c>
       <c r="B18" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550099</v>
+        <v>550127</v>
       </c>
       <c r="R18" t="n">
-        <v>6942637</v>
+        <v>6942669</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,7 +2594,7 @@
         <v>126057564</v>
       </c>
       <c r="B19" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>126057563</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>126057526</v>
       </c>
       <c r="B21" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>126057935</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>126057582</v>
       </c>
       <c r="B23" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>126050880</v>
       </c>
       <c r="B24" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>126051522</v>
       </c>
       <c r="B25" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>126057544</v>
       </c>
       <c r="B26" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3372,32 +3372,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126057532</v>
+        <v>126057545</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>91245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550020</v>
+        <v>550011</v>
       </c>
       <c r="R27" t="n">
-        <v>6942390</v>
+        <v>6942535</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3443,11 +3443,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3474,32 +3469,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126057545</v>
+        <v>126057532</v>
       </c>
       <c r="B28" t="n">
-        <v>91243</v>
+        <v>57652</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3509,10 +3504,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550011</v>
+        <v>550020</v>
       </c>
       <c r="R28" t="n">
-        <v>6942535</v>
+        <v>6942390</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3545,6 +3540,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3574,7 +3574,7 @@
         <v>126052983</v>
       </c>
       <c r="B29" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>126052248</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>126051074</v>
       </c>
       <c r="B31" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>126057596</v>
       </c>
       <c r="B32" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>126057591</v>
       </c>
       <c r="B33" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4075,10 +4075,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057538</v>
+        <v>126057579</v>
       </c>
       <c r="B34" t="n">
-        <v>57651</v>
+        <v>78731</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4086,21 +4086,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550041</v>
+        <v>550006</v>
       </c>
       <c r="R34" t="n">
-        <v>6942496</v>
+        <v>6942636</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4146,11 +4146,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4177,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057579</v>
+        <v>126057937</v>
       </c>
       <c r="B35" t="n">
-        <v>78730</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4188,34 +4183,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550006</v>
+        <v>550147</v>
       </c>
       <c r="R35" t="n">
-        <v>6942636</v>
+        <v>6942582</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4248,6 +4243,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,10 +4274,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057937</v>
+        <v>126053984</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4305,17 +4305,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550147</v>
+        <v>549984</v>
       </c>
       <c r="R36" t="n">
-        <v>6942582</v>
+        <v>6942510</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126053984</v>
+        <v>126057567</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4411,13 +4411,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>549984</v>
+        <v>550001</v>
       </c>
       <c r="R37" t="n">
-        <v>6942510</v>
+        <v>6942503</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4447,11 +4447,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4478,10 +4473,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057567</v>
+        <v>126057538</v>
       </c>
       <c r="B38" t="n">
-        <v>80075</v>
+        <v>57652</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4489,21 +4484,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4513,10 +4508,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550001</v>
+        <v>550041</v>
       </c>
       <c r="R38" t="n">
-        <v>6942503</v>
+        <v>6942496</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4549,6 +4544,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4575,32 +4575,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057592</v>
+        <v>126052912</v>
       </c>
       <c r="B39" t="n">
-        <v>98339</v>
+        <v>80104</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550038</v>
+        <v>549977</v>
       </c>
       <c r="R39" t="n">
-        <v>6942494</v>
+        <v>6942554</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4646,11 +4646,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>28 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4677,52 +4672,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126052420</v>
+        <v>126057569</v>
       </c>
       <c r="B40" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549984</v>
+        <v>550006</v>
       </c>
       <c r="R40" t="n">
-        <v>6942510</v>
+        <v>6942630</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4781,7 +4772,7 @@
         <v>126057600</v>
       </c>
       <c r="B41" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4880,32 +4871,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126052912</v>
+        <v>126057592</v>
       </c>
       <c r="B42" t="n">
-        <v>80103</v>
+        <v>98341</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4915,13 +4906,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549977</v>
+        <v>550038</v>
       </c>
       <c r="R42" t="n">
-        <v>6942554</v>
+        <v>6942494</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4951,6 +4942,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>28 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4977,48 +4973,52 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126057569</v>
+        <v>126052420</v>
       </c>
       <c r="B43" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550006</v>
+        <v>549984</v>
       </c>
       <c r="R43" t="n">
-        <v>6942630</v>
+        <v>6942510</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5074,10 +5074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126052332</v>
+        <v>126057896</v>
       </c>
       <c r="B44" t="n">
-        <v>98360</v>
+        <v>80104</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5085,41 +5085,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549984</v>
+        <v>550007</v>
       </c>
       <c r="R44" t="n">
-        <v>6942510</v>
+        <v>6942646</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5175,45 +5171,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057896</v>
+        <v>126057568</v>
       </c>
       <c r="B45" t="n">
-        <v>80103</v>
+        <v>80076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550007</v>
+        <v>550093</v>
       </c>
       <c r="R45" t="n">
-        <v>6942646</v>
+        <v>6942579</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5272,45 +5268,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057568</v>
+        <v>126057930</v>
       </c>
       <c r="B46" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550093</v>
+        <v>550112</v>
       </c>
       <c r="R46" t="n">
-        <v>6942579</v>
+        <v>6942664</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5343,6 +5339,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>50stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5369,48 +5370,52 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057930</v>
+        <v>126052332</v>
       </c>
       <c r="B47" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550112</v>
+        <v>549984</v>
       </c>
       <c r="R47" t="n">
-        <v>6942664</v>
+        <v>6942510</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5440,11 +5445,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>50stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5474,7 +5474,7 @@
         <v>126052735</v>
       </c>
       <c r="B48" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5568,57 +5568,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126049249</v>
+        <v>126057602</v>
       </c>
       <c r="B49" t="n">
-        <v>58020</v>
+        <v>98341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550135</v>
+        <v>550099</v>
       </c>
       <c r="R49" t="n">
-        <v>6942628</v>
+        <v>6942666</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5648,6 +5639,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5674,45 +5670,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126051690</v>
+        <v>126051408</v>
       </c>
       <c r="B50" t="n">
-        <v>80103</v>
+        <v>57649</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550110</v>
+        <v>550089</v>
       </c>
       <c r="R50" t="n">
-        <v>6942386</v>
+        <v>6942422</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5745,6 +5746,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5771,27 +5777,27 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126051408</v>
+        <v>126049249</v>
       </c>
       <c r="B51" t="n">
-        <v>57648</v>
+        <v>58021</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5799,10 +5805,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5811,10 +5821,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550089</v>
+        <v>550135</v>
       </c>
       <c r="R51" t="n">
-        <v>6942422</v>
+        <v>6942628</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5847,11 +5857,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5878,32 +5883,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126057602</v>
+        <v>126051690</v>
       </c>
       <c r="B52" t="n">
-        <v>98339</v>
+        <v>80104</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5913,13 +5918,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550099</v>
+        <v>550110</v>
       </c>
       <c r="R52" t="n">
-        <v>6942666</v>
+        <v>6942386</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5949,11 +5954,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5980,10 +5980,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057915</v>
+        <v>126057565</v>
       </c>
       <c r="B53" t="n">
-        <v>78730</v>
+        <v>78732</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5991,34 +5991,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550145</v>
+        <v>550139</v>
       </c>
       <c r="R53" t="n">
-        <v>6942577</v>
+        <v>6942641</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6077,32 +6077,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057898</v>
+        <v>126057915</v>
       </c>
       <c r="B54" t="n">
-        <v>80103</v>
+        <v>78731</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>549997</v>
+        <v>550145</v>
       </c>
       <c r="R54" t="n">
-        <v>6942637</v>
+        <v>6942577</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6174,45 +6174,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057565</v>
+        <v>126057898</v>
       </c>
       <c r="B55" t="n">
-        <v>78731</v>
+        <v>80104</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550139</v>
+        <v>549997</v>
       </c>
       <c r="R55" t="n">
-        <v>6942641</v>
+        <v>6942637</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6274,7 +6274,7 @@
         <v>126057525</v>
       </c>
       <c r="B56" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6368,53 +6368,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126050777</v>
+        <v>126057533</v>
       </c>
       <c r="B57" t="n">
-        <v>56843</v>
+        <v>57652</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550093</v>
+        <v>550026</v>
       </c>
       <c r="R57" t="n">
-        <v>6942497</v>
+        <v>6942422</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6444,6 +6439,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6470,48 +6470,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126057533</v>
+        <v>126050777</v>
       </c>
       <c r="B58" t="n">
-        <v>57651</v>
+        <v>56844</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550026</v>
+        <v>550093</v>
       </c>
       <c r="R58" t="n">
-        <v>6942422</v>
+        <v>6942497</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6541,11 +6546,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6572,52 +6572,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126048239</v>
+        <v>126057576</v>
       </c>
       <c r="B59" t="n">
-        <v>98339</v>
+        <v>78731</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550147</v>
+        <v>550078</v>
       </c>
       <c r="R59" t="n">
-        <v>6942635</v>
+        <v>6942401</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6673,37 +6669,38 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126049594</v>
+        <v>126051839</v>
       </c>
       <c r="B60" t="n">
-        <v>98339</v>
+        <v>56844</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6712,10 +6709,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550141</v>
+        <v>550088</v>
       </c>
       <c r="R60" t="n">
-        <v>6942615</v>
+        <v>6942377</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6774,32 +6771,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126057576</v>
+        <v>126057601</v>
       </c>
       <c r="B61" t="n">
-        <v>78730</v>
+        <v>98341</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6809,10 +6806,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550078</v>
+        <v>550096</v>
       </c>
       <c r="R61" t="n">
-        <v>6942401</v>
+        <v>6942661</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6845,6 +6842,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6871,38 +6873,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126051839</v>
+        <v>126052934</v>
       </c>
       <c r="B62" t="n">
-        <v>56843</v>
+        <v>98341</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6911,10 +6912,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550088</v>
+        <v>549977</v>
       </c>
       <c r="R62" t="n">
-        <v>6942377</v>
+        <v>6942554</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6973,37 +6974,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126052802</v>
+        <v>126048239</v>
       </c>
       <c r="B63" t="n">
-        <v>98360</v>
+        <v>98341</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7012,10 +7013,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>549987</v>
+        <v>550147</v>
       </c>
       <c r="R63" t="n">
-        <v>6942530</v>
+        <v>6942635</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7074,10 +7075,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126057601</v>
+        <v>126049594</v>
       </c>
       <c r="B64" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7102,20 +7103,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550096</v>
+        <v>550141</v>
       </c>
       <c r="R64" t="n">
-        <v>6942661</v>
+        <v>6942615</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7145,11 +7150,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7176,37 +7176,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126052934</v>
+        <v>126052802</v>
       </c>
       <c r="B65" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>549977</v>
+        <v>549987</v>
       </c>
       <c r="R65" t="n">
-        <v>6942554</v>
+        <v>6942530</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7280,7 +7280,7 @@
         <v>126051197</v>
       </c>
       <c r="B66" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>126051507</v>
       </c>
       <c r="B67" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>126057594</v>
       </c>
       <c r="B68" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>126057537</v>
       </c>
       <c r="B69" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>126053048</v>
       </c>
       <c r="B70" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>126051112</v>
       </c>
       <c r="B71" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>126057583</v>
       </c>
       <c r="B72" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7980,10 +7980,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126057578</v>
+        <v>126049570</v>
       </c>
       <c r="B73" t="n">
-        <v>78730</v>
+        <v>78973</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7991,21 +7991,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550086</v>
+        <v>550135</v>
       </c>
       <c r="R73" t="n">
-        <v>6942580</v>
+        <v>6942628</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8051,6 +8051,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8077,32 +8082,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126057549</v>
+        <v>126057578</v>
       </c>
       <c r="B74" t="n">
-        <v>91686</v>
+        <v>78731</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8112,10 +8117,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>549978</v>
+        <v>550086</v>
       </c>
       <c r="R74" t="n">
-        <v>6942581</v>
+        <v>6942580</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8174,32 +8179,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126049570</v>
+        <v>126057549</v>
       </c>
       <c r="B75" t="n">
-        <v>78972</v>
+        <v>91688</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8209,13 +8214,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550135</v>
+        <v>549978</v>
       </c>
       <c r="R75" t="n">
-        <v>6942628</v>
+        <v>6942581</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8245,11 +8250,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8279,7 +8279,7 @@
         <v>126050913</v>
       </c>
       <c r="B76" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>126057606</v>
       </c>
       <c r="B77" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>126057904</v>
       </c>
       <c r="B78" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>126051602</v>
       </c>
       <c r="B79" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8673,32 +8673,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126057559</v>
+        <v>126057574</v>
       </c>
       <c r="B80" t="n">
-        <v>80103</v>
+        <v>78731</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550000</v>
+        <v>549990</v>
       </c>
       <c r="R80" t="n">
-        <v>6942626</v>
+        <v>6942590</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8770,32 +8770,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126057574</v>
+        <v>126057524</v>
       </c>
       <c r="B81" t="n">
-        <v>78730</v>
+        <v>91199</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>549990</v>
+        <v>550079</v>
       </c>
       <c r="R81" t="n">
-        <v>6942590</v>
+        <v>6942497</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8867,48 +8867,52 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126057524</v>
+        <v>126051270</v>
       </c>
       <c r="B82" t="n">
-        <v>91197</v>
+        <v>98341</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550079</v>
+        <v>550065</v>
       </c>
       <c r="R82" t="n">
-        <v>6942497</v>
+        <v>6942463</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8964,37 +8968,38 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126051270</v>
+        <v>126047488</v>
       </c>
       <c r="B83" t="n">
-        <v>98339</v>
+        <v>43934</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>43</t>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9003,13 +9008,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550065</v>
+        <v>550158</v>
       </c>
       <c r="R83" t="n">
-        <v>6942463</v>
+        <v>6942653</v>
       </c>
       <c r="S83" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9039,6 +9044,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9065,10 +9075,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126047488</v>
+        <v>126057559</v>
       </c>
       <c r="B84" t="n">
-        <v>43933</v>
+        <v>80104</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9076,42 +9086,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>101735</v>
+        <v>6461</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550158</v>
+        <v>550000</v>
       </c>
       <c r="R84" t="n">
-        <v>6942653</v>
+        <v>6942626</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9141,11 +9146,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9172,48 +9172,52 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126057575</v>
+        <v>126052873</v>
       </c>
       <c r="B85" t="n">
-        <v>78730</v>
+        <v>98341</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550022</v>
+        <v>549989</v>
       </c>
       <c r="R85" t="n">
-        <v>6942537</v>
+        <v>6942554</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9269,32 +9273,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126052154</v>
+        <v>126052827</v>
       </c>
       <c r="B86" t="n">
-        <v>78972</v>
+        <v>97219</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9304,10 +9308,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550021</v>
+        <v>549987</v>
       </c>
       <c r="R86" t="n">
-        <v>6942450</v>
+        <v>6942530</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9340,11 +9344,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9374,7 +9373,7 @@
         <v>126057556</v>
       </c>
       <c r="B87" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9471,7 +9470,7 @@
         <v>126057531</v>
       </c>
       <c r="B88" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9573,7 +9572,7 @@
         <v>126057535</v>
       </c>
       <c r="B89" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9672,32 +9671,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126052827</v>
+        <v>126057575</v>
       </c>
       <c r="B90" t="n">
-        <v>97217</v>
+        <v>78731</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9707,13 +9706,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>549987</v>
+        <v>550022</v>
       </c>
       <c r="R90" t="n">
-        <v>6942530</v>
+        <v>6942537</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9769,49 +9768,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126052873</v>
+        <v>126052154</v>
       </c>
       <c r="B91" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>549989</v>
+        <v>550021</v>
       </c>
       <c r="R91" t="n">
-        <v>6942554</v>
+        <v>6942450</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9844,6 +9839,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9873,7 +9873,7 @@
         <v>126057577</v>
       </c>
       <c r="B92" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>126057581</v>
       </c>
       <c r="B93" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10064,10 +10064,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126050713</v>
+        <v>126057540</v>
       </c>
       <c r="B94" t="n">
-        <v>56834</v>
+        <v>57652</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10075,16 +10075,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -10093,24 +10093,19 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550120</v>
+        <v>550138</v>
       </c>
       <c r="R94" t="n">
-        <v>6942506</v>
+        <v>6942638</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10140,6 +10135,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10166,10 +10166,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126057540</v>
+        <v>126050713</v>
       </c>
       <c r="B95" t="n">
-        <v>57651</v>
+        <v>56835</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10177,16 +10177,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10195,19 +10195,24 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>550138</v>
+        <v>550120</v>
       </c>
       <c r="R95" t="n">
-        <v>6942638</v>
+        <v>6942506</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10237,11 +10242,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10268,10 +10268,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126057593</v>
+        <v>126057923</v>
       </c>
       <c r="B96" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10299,14 +10299,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>550137</v>
+        <v>550122</v>
       </c>
       <c r="R96" t="n">
-        <v>6942555</v>
+        <v>6942671</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10370,10 +10370,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126057923</v>
+        <v>126057593</v>
       </c>
       <c r="B97" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10401,14 +10401,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>550122</v>
+        <v>550137</v>
       </c>
       <c r="R97" t="n">
-        <v>6942671</v>
+        <v>6942555</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2285,32 +2285,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126057597</v>
+        <v>126057564</v>
       </c>
       <c r="B16" t="n">
-        <v>98341</v>
+        <v>78732</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550099</v>
+        <v>550076</v>
       </c>
       <c r="R16" t="n">
-        <v>6942637</v>
+        <v>6942390</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2356,11 +2356,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>8 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,32 +2382,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126057921</v>
+        <v>126057934</v>
       </c>
       <c r="B17" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2422,10 +2417,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550142</v>
+        <v>550127</v>
       </c>
       <c r="R17" t="n">
-        <v>6942582</v>
+        <v>6942669</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2462,7 +2457,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>30 stycken</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,45 +2484,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057934</v>
+        <v>126057597</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>98341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550127</v>
+        <v>550099</v>
       </c>
       <c r="R18" t="n">
-        <v>6942669</v>
+        <v>6942637</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2564,7 +2559,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,45 +2586,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057564</v>
+        <v>126057921</v>
       </c>
       <c r="B19" t="n">
-        <v>78732</v>
+        <v>98341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550076</v>
+        <v>550142</v>
       </c>
       <c r="R19" t="n">
-        <v>6942390</v>
+        <v>6942582</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2662,6 +2657,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3372,32 +3372,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126057545</v>
+        <v>126052983</v>
       </c>
       <c r="B27" t="n">
-        <v>91245</v>
+        <v>78731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1205</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550011</v>
+        <v>549977</v>
       </c>
       <c r="R27" t="n">
-        <v>6942535</v>
+        <v>6942554</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3469,10 +3469,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126057532</v>
+        <v>126052248</v>
       </c>
       <c r="B28" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3480,21 +3480,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3504,13 +3504,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550020</v>
+        <v>550004</v>
       </c>
       <c r="R28" t="n">
-        <v>6942390</v>
+        <v>6942504</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Rikligt med garnlav inom området</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3571,32 +3571,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126052983</v>
+        <v>126057545</v>
       </c>
       <c r="B29" t="n">
-        <v>78731</v>
+        <v>91245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>1205</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3606,13 +3606,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549977</v>
+        <v>550011</v>
       </c>
       <c r="R29" t="n">
-        <v>6942554</v>
+        <v>6942535</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3668,10 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126052248</v>
+        <v>126057532</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,21 +3679,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550004</v>
+        <v>550020</v>
       </c>
       <c r="R30" t="n">
-        <v>6942504</v>
+        <v>6942390</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom området</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5074,45 +5074,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057896</v>
+        <v>126057568</v>
       </c>
       <c r="B44" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550007</v>
+        <v>550093</v>
       </c>
       <c r="R44" t="n">
-        <v>6942646</v>
+        <v>6942579</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5171,45 +5171,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057568</v>
+        <v>126057930</v>
       </c>
       <c r="B45" t="n">
-        <v>80076</v>
+        <v>98341</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550093</v>
+        <v>550112</v>
       </c>
       <c r="R45" t="n">
-        <v>6942579</v>
+        <v>6942664</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5242,6 +5242,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>50stycken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5268,48 +5273,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057930</v>
+        <v>126052332</v>
       </c>
       <c r="B46" t="n">
-        <v>98341</v>
+        <v>98362</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550112</v>
+        <v>549984</v>
       </c>
       <c r="R46" t="n">
-        <v>6942664</v>
+        <v>6942510</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5339,11 +5348,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>50stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5370,49 +5374,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126052332</v>
+        <v>126052735</v>
       </c>
       <c r="B47" t="n">
-        <v>98362</v>
+        <v>78732</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>549984</v>
+        <v>549975</v>
       </c>
       <c r="R47" t="n">
-        <v>6942510</v>
+        <v>6942519</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5471,48 +5471,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126052735</v>
+        <v>126057896</v>
       </c>
       <c r="B48" t="n">
-        <v>78732</v>
+        <v>80104</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>549975</v>
+        <v>550007</v>
       </c>
       <c r="R48" t="n">
-        <v>6942519</v>
+        <v>6942646</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5980,10 +5980,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057565</v>
+        <v>126057915</v>
       </c>
       <c r="B53" t="n">
-        <v>78732</v>
+        <v>78731</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5991,34 +5991,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550139</v>
+        <v>550145</v>
       </c>
       <c r="R53" t="n">
-        <v>6942641</v>
+        <v>6942577</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6077,32 +6077,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057915</v>
+        <v>126057898</v>
       </c>
       <c r="B54" t="n">
-        <v>78731</v>
+        <v>80104</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550145</v>
+        <v>549997</v>
       </c>
       <c r="R54" t="n">
-        <v>6942577</v>
+        <v>6942637</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6174,45 +6174,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057898</v>
+        <v>126057565</v>
       </c>
       <c r="B55" t="n">
-        <v>80104</v>
+        <v>78732</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>549997</v>
+        <v>550139</v>
       </c>
       <c r="R55" t="n">
-        <v>6942637</v>
+        <v>6942641</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6669,38 +6669,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126051839</v>
+        <v>126048239</v>
       </c>
       <c r="B60" t="n">
-        <v>56844</v>
+        <v>98341</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>56</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6709,10 +6708,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550088</v>
+        <v>550147</v>
       </c>
       <c r="R60" t="n">
-        <v>6942377</v>
+        <v>6942635</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6771,7 +6770,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126057601</v>
+        <v>126049594</v>
       </c>
       <c r="B61" t="n">
         <v>98341</v>
@@ -6799,20 +6798,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550096</v>
+        <v>550141</v>
       </c>
       <c r="R61" t="n">
-        <v>6942661</v>
+        <v>6942615</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6842,11 +6845,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6873,37 +6871,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126052934</v>
+        <v>126051839</v>
       </c>
       <c r="B62" t="n">
-        <v>98341</v>
+        <v>56844</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>29</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6912,10 +6911,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>549977</v>
+        <v>550088</v>
       </c>
       <c r="R62" t="n">
-        <v>6942554</v>
+        <v>6942377</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6974,37 +6973,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126048239</v>
+        <v>126052802</v>
       </c>
       <c r="B63" t="n">
-        <v>98341</v>
+        <v>98362</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7013,10 +7012,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550147</v>
+        <v>549987</v>
       </c>
       <c r="R63" t="n">
-        <v>6942635</v>
+        <v>6942530</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7075,7 +7074,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126049594</v>
+        <v>126057601</v>
       </c>
       <c r="B64" t="n">
         <v>98341</v>
@@ -7103,24 +7102,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550141</v>
+        <v>550096</v>
       </c>
       <c r="R64" t="n">
-        <v>6942615</v>
+        <v>6942661</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7150,6 +7145,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7176,37 +7176,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126052802</v>
+        <v>126052934</v>
       </c>
       <c r="B65" t="n">
-        <v>98362</v>
+        <v>98341</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>549987</v>
+        <v>549977</v>
       </c>
       <c r="R65" t="n">
-        <v>6942530</v>
+        <v>6942554</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7781,32 +7781,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126051112</v>
+        <v>126057583</v>
       </c>
       <c r="B71" t="n">
-        <v>80104</v>
+        <v>98341</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7816,13 +7816,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550093</v>
+        <v>550098</v>
       </c>
       <c r="R71" t="n">
-        <v>6942497</v>
+        <v>6942641</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7852,6 +7852,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>31 ex</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7878,32 +7883,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126057583</v>
+        <v>126051112</v>
       </c>
       <c r="B72" t="n">
-        <v>98341</v>
+        <v>80104</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7913,13 +7918,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550098</v>
+        <v>550093</v>
       </c>
       <c r="R72" t="n">
-        <v>6942641</v>
+        <v>6942497</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7949,11 +7954,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>31 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126057536</v>
+        <v>126057934</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,34 +2194,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550113</v>
+        <v>550127</v>
       </c>
       <c r="R15" t="n">
-        <v>6942389</v>
+        <v>6942669</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126057564</v>
+        <v>126057536</v>
       </c>
       <c r="B16" t="n">
-        <v>78732</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,21 +2296,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550076</v>
+        <v>550113</v>
       </c>
       <c r="R16" t="n">
-        <v>6942390</v>
+        <v>6942389</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2356,6 +2356,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,32 +2387,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126057934</v>
+        <v>126057921</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2417,10 +2422,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550127</v>
+        <v>550142</v>
       </c>
       <c r="R17" t="n">
-        <v>6942669</v>
+        <v>6942582</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2457,7 +2462,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,7 +2492,7 @@
         <v>126057597</v>
       </c>
       <c r="B18" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,45 +2591,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057921</v>
+        <v>126057564</v>
       </c>
       <c r="B19" t="n">
-        <v>98341</v>
+        <v>78732</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550142</v>
+        <v>550076</v>
       </c>
       <c r="R19" t="n">
-        <v>6942582</v>
+        <v>6942390</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2657,11 +2662,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,32 +2785,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057526</v>
+        <v>126057582</v>
       </c>
       <c r="B21" t="n">
-        <v>91234</v>
+        <v>98343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550079</v>
+        <v>550023</v>
       </c>
       <c r="R21" t="n">
-        <v>6942497</v>
+        <v>6942583</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2856,6 +2856,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>61 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,32 +2984,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057582</v>
+        <v>126057526</v>
       </c>
       <c r="B23" t="n">
-        <v>98341</v>
+        <v>91236</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3014,10 +3019,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550023</v>
+        <v>550079</v>
       </c>
       <c r="R23" t="n">
-        <v>6942583</v>
+        <v>6942497</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3050,11 +3055,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>61 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,32 +3081,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126050880</v>
+        <v>126052983</v>
       </c>
       <c r="B24" t="n">
-        <v>80104</v>
+        <v>78731</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550088</v>
+        <v>549977</v>
       </c>
       <c r="R24" t="n">
-        <v>6942520</v>
+        <v>6942554</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126051522</v>
+        <v>126050880</v>
       </c>
       <c r="B25" t="n">
         <v>80104</v>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550089</v>
+        <v>550088</v>
       </c>
       <c r="R25" t="n">
-        <v>6942422</v>
+        <v>6942520</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3372,32 +3372,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126052983</v>
+        <v>126051522</v>
       </c>
       <c r="B27" t="n">
-        <v>78731</v>
+        <v>80104</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549977</v>
+        <v>550089</v>
       </c>
       <c r="R27" t="n">
-        <v>6942554</v>
+        <v>6942422</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126052248</v>
+        <v>126057545</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>91247</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3504,13 +3504,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550004</v>
+        <v>550011</v>
       </c>
       <c r="R28" t="n">
-        <v>6942504</v>
+        <v>6942535</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3540,11 +3540,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom området</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3571,32 +3566,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057545</v>
+        <v>126057532</v>
       </c>
       <c r="B29" t="n">
-        <v>91245</v>
+        <v>57652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3606,10 +3601,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550011</v>
+        <v>550020</v>
       </c>
       <c r="R29" t="n">
-        <v>6942535</v>
+        <v>6942390</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3642,6 +3637,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3668,10 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057532</v>
+        <v>126052248</v>
       </c>
       <c r="B30" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,21 +3679,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550020</v>
+        <v>550004</v>
       </c>
       <c r="R30" t="n">
-        <v>6942390</v>
+        <v>6942504</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Rikligt med garnlav inom området</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3773,7 +3773,7 @@
         <v>126051074</v>
       </c>
       <c r="B31" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,45 +3871,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057596</v>
+        <v>126057937</v>
       </c>
       <c r="B32" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550092</v>
+        <v>550147</v>
       </c>
       <c r="R32" t="n">
-        <v>6942597</v>
+        <v>6942582</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3973,32 +3973,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057591</v>
+        <v>126057579</v>
       </c>
       <c r="B33" t="n">
-        <v>98341</v>
+        <v>78731</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550020</v>
+        <v>550006</v>
       </c>
       <c r="R33" t="n">
-        <v>6942543</v>
+        <v>6942636</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4044,11 +4044,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>3 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4075,10 +4070,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057579</v>
+        <v>126057567</v>
       </c>
       <c r="B34" t="n">
-        <v>78731</v>
+        <v>80076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4086,21 +4081,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4110,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550006</v>
+        <v>550001</v>
       </c>
       <c r="R34" t="n">
-        <v>6942636</v>
+        <v>6942503</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4172,10 +4167,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057937</v>
+        <v>126057538</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,34 +4178,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550147</v>
+        <v>550041</v>
       </c>
       <c r="R35" t="n">
-        <v>6942582</v>
+        <v>6942496</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4247,7 +4242,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4376,32 +4371,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057567</v>
+        <v>126057596</v>
       </c>
       <c r="B37" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4411,10 +4406,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550001</v>
+        <v>550092</v>
       </c>
       <c r="R37" t="n">
-        <v>6942503</v>
+        <v>6942597</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4447,6 +4442,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4473,32 +4473,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057538</v>
+        <v>126057591</v>
       </c>
       <c r="B38" t="n">
-        <v>57652</v>
+        <v>98343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550041</v>
+        <v>550020</v>
       </c>
       <c r="R38" t="n">
-        <v>6942496</v>
+        <v>6942543</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4575,32 +4575,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126052912</v>
+        <v>126057569</v>
       </c>
       <c r="B39" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549977</v>
+        <v>550006</v>
       </c>
       <c r="R39" t="n">
-        <v>6942554</v>
+        <v>6942630</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4672,32 +4672,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057569</v>
+        <v>126052912</v>
       </c>
       <c r="B40" t="n">
-        <v>80076</v>
+        <v>80104</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4707,13 +4707,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550006</v>
+        <v>549977</v>
       </c>
       <c r="R40" t="n">
-        <v>6942630</v>
+        <v>6942554</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126057600</v>
+        <v>126057592</v>
       </c>
       <c r="B41" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550095</v>
+        <v>550038</v>
       </c>
       <c r="R41" t="n">
-        <v>6942646</v>
+        <v>6942494</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>28 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4871,10 +4871,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126057592</v>
+        <v>126052420</v>
       </c>
       <c r="B42" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4899,20 +4899,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550038</v>
+        <v>549984</v>
       </c>
       <c r="R42" t="n">
-        <v>6942494</v>
+        <v>6942510</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4942,11 +4946,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>28 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4973,10 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126052420</v>
+        <v>126057600</v>
       </c>
       <c r="B43" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5001,24 +5000,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>549984</v>
+        <v>550095</v>
       </c>
       <c r="R43" t="n">
-        <v>6942510</v>
+        <v>6942646</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5048,6 +5043,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5171,32 +5171,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057930</v>
+        <v>126057896</v>
       </c>
       <c r="B45" t="n">
-        <v>98341</v>
+        <v>80104</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5206,10 +5206,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550112</v>
+        <v>550007</v>
       </c>
       <c r="R45" t="n">
-        <v>6942664</v>
+        <v>6942646</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5242,11 +5242,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>50stycken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5273,52 +5268,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126052332</v>
+        <v>126057930</v>
       </c>
       <c r="B46" t="n">
-        <v>98362</v>
+        <v>98343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549984</v>
+        <v>550112</v>
       </c>
       <c r="R46" t="n">
-        <v>6942510</v>
+        <v>6942664</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5348,6 +5339,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>50stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5374,45 +5370,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126052735</v>
+        <v>126052332</v>
       </c>
       <c r="B47" t="n">
-        <v>78732</v>
+        <v>98364</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>549975</v>
+        <v>549984</v>
       </c>
       <c r="R47" t="n">
-        <v>6942519</v>
+        <v>6942510</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5471,48 +5471,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057896</v>
+        <v>126052735</v>
       </c>
       <c r="B48" t="n">
-        <v>80104</v>
+        <v>78732</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550007</v>
+        <v>549975</v>
       </c>
       <c r="R48" t="n">
-        <v>6942646</v>
+        <v>6942519</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5568,48 +5568,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126057602</v>
+        <v>126051408</v>
       </c>
       <c r="B49" t="n">
-        <v>98341</v>
+        <v>57649</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550099</v>
+        <v>550089</v>
       </c>
       <c r="R49" t="n">
-        <v>6942666</v>
+        <v>6942422</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5643,7 +5648,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5670,50 +5675,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126051408</v>
+        <v>126051690</v>
       </c>
       <c r="B50" t="n">
-        <v>57649</v>
+        <v>80104</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550089</v>
+        <v>550110</v>
       </c>
       <c r="R50" t="n">
-        <v>6942422</v>
+        <v>6942386</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5746,11 +5746,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5777,57 +5772,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126049249</v>
+        <v>126057602</v>
       </c>
       <c r="B51" t="n">
-        <v>58021</v>
+        <v>98343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550135</v>
+        <v>550099</v>
       </c>
       <c r="R51" t="n">
-        <v>6942628</v>
+        <v>6942666</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5857,6 +5843,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5883,10 +5874,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126051690</v>
+        <v>126049249</v>
       </c>
       <c r="B52" t="n">
-        <v>80104</v>
+        <v>58021</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5894,34 +5885,43 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550110</v>
+        <v>550135</v>
       </c>
       <c r="R52" t="n">
-        <v>6942386</v>
+        <v>6942628</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5980,32 +5980,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057915</v>
+        <v>126057898</v>
       </c>
       <c r="B53" t="n">
-        <v>78731</v>
+        <v>80104</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550145</v>
+        <v>549997</v>
       </c>
       <c r="R53" t="n">
-        <v>6942577</v>
+        <v>6942637</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6077,32 +6077,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057898</v>
+        <v>126057915</v>
       </c>
       <c r="B54" t="n">
-        <v>80104</v>
+        <v>78731</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>549997</v>
+        <v>550145</v>
       </c>
       <c r="R54" t="n">
-        <v>6942637</v>
+        <v>6942577</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6274,7 +6274,7 @@
         <v>126057525</v>
       </c>
       <c r="B56" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6669,37 +6669,38 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126048239</v>
+        <v>126051839</v>
       </c>
       <c r="B60" t="n">
-        <v>98341</v>
+        <v>56844</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>56</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6708,10 +6709,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550147</v>
+        <v>550088</v>
       </c>
       <c r="R60" t="n">
-        <v>6942635</v>
+        <v>6942377</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6770,10 +6771,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126049594</v>
+        <v>126057601</v>
       </c>
       <c r="B61" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6798,24 +6799,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550141</v>
+        <v>550096</v>
       </c>
       <c r="R61" t="n">
-        <v>6942615</v>
+        <v>6942661</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6845,6 +6842,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6871,38 +6873,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126051839</v>
+        <v>126052934</v>
       </c>
       <c r="B62" t="n">
-        <v>56844</v>
+        <v>98343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6911,10 +6912,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550088</v>
+        <v>549977</v>
       </c>
       <c r="R62" t="n">
-        <v>6942377</v>
+        <v>6942554</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6976,7 +6977,7 @@
         <v>126052802</v>
       </c>
       <c r="B63" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7074,10 +7075,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126057601</v>
+        <v>126048239</v>
       </c>
       <c r="B64" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7102,20 +7103,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550096</v>
+        <v>550147</v>
       </c>
       <c r="R64" t="n">
-        <v>6942661</v>
+        <v>6942635</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7145,11 +7150,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7176,10 +7176,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126052934</v>
+        <v>126049594</v>
       </c>
       <c r="B65" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>549977</v>
+        <v>550141</v>
       </c>
       <c r="R65" t="n">
-        <v>6942554</v>
+        <v>6942615</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7280,7 +7280,7 @@
         <v>126051197</v>
       </c>
       <c r="B66" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>126051507</v>
       </c>
       <c r="B67" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>126057594</v>
       </c>
       <c r="B68" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7679,32 +7679,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126053048</v>
+        <v>126057583</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7714,13 +7714,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>549965</v>
+        <v>550098</v>
       </c>
       <c r="R70" t="n">
-        <v>6942583</v>
+        <v>6942641</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav I området</t>
+          <t>31 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7781,32 +7781,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126057583</v>
+        <v>126053048</v>
       </c>
       <c r="B71" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7816,13 +7816,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550098</v>
+        <v>549965</v>
       </c>
       <c r="R71" t="n">
-        <v>6942641</v>
+        <v>6942583</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>31 ex</t>
+          <t>Rikligt med garnlav I området</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126049570</v>
+        <v>126057549</v>
       </c>
       <c r="B73" t="n">
-        <v>78973</v>
+        <v>91690</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550135</v>
+        <v>549978</v>
       </c>
       <c r="R73" t="n">
-        <v>6942628</v>
+        <v>6942581</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8051,11 +8051,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8179,32 +8174,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126057549</v>
+        <v>126049570</v>
       </c>
       <c r="B75" t="n">
-        <v>91688</v>
+        <v>78973</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8214,13 +8209,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>549978</v>
+        <v>550135</v>
       </c>
       <c r="R75" t="n">
-        <v>6942581</v>
+        <v>6942628</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8250,6 +8245,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8276,10 +8276,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126050913</v>
+        <v>126057904</v>
       </c>
       <c r="B76" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8287,37 +8287,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550088</v>
+        <v>549997</v>
       </c>
       <c r="R76" t="n">
-        <v>6942520</v>
+        <v>6942637</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8347,11 +8347,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8378,7 +8373,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126057606</v>
+        <v>126050913</v>
       </c>
       <c r="B77" t="n">
         <v>78973</v>
@@ -8413,13 +8408,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550034</v>
+        <v>550088</v>
       </c>
       <c r="R77" t="n">
-        <v>6942421</v>
+        <v>6942520</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8449,6 +8444,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8475,10 +8475,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126057904</v>
+        <v>126057606</v>
       </c>
       <c r="B78" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8486,34 +8486,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>549997</v>
+        <v>550034</v>
       </c>
       <c r="R78" t="n">
-        <v>6942637</v>
+        <v>6942421</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8575,7 +8575,7 @@
         <v>126051602</v>
       </c>
       <c r="B79" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126057524</v>
+        <v>126057559</v>
       </c>
       <c r="B81" t="n">
-        <v>91199</v>
+        <v>80104</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8781,21 +8781,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550079</v>
+        <v>550000</v>
       </c>
       <c r="R81" t="n">
-        <v>6942497</v>
+        <v>6942626</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8867,37 +8867,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126051270</v>
+        <v>126047488</v>
       </c>
       <c r="B82" t="n">
-        <v>98341</v>
+        <v>43934</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>43</t>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -8906,13 +8907,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550065</v>
+        <v>550158</v>
       </c>
       <c r="R82" t="n">
-        <v>6942463</v>
+        <v>6942653</v>
       </c>
       <c r="S82" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8942,6 +8943,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8968,10 +8974,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126047488</v>
+        <v>126057524</v>
       </c>
       <c r="B83" t="n">
-        <v>43934</v>
+        <v>91201</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8979,42 +8985,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>101735</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550158</v>
+        <v>550079</v>
       </c>
       <c r="R83" t="n">
-        <v>6942653</v>
+        <v>6942497</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9044,11 +9045,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9075,48 +9071,52 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126057559</v>
+        <v>126051270</v>
       </c>
       <c r="B84" t="n">
-        <v>80104</v>
+        <v>98343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550000</v>
+        <v>550065</v>
       </c>
       <c r="R84" t="n">
-        <v>6942626</v>
+        <v>6942463</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9172,52 +9172,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126052873</v>
+        <v>126057531</v>
       </c>
       <c r="B85" t="n">
-        <v>98341</v>
+        <v>57652</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>549989</v>
+        <v>549974</v>
       </c>
       <c r="R85" t="n">
-        <v>6942554</v>
+        <v>6942584</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9247,6 +9243,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9273,32 +9274,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126052827</v>
+        <v>126057535</v>
       </c>
       <c r="B86" t="n">
-        <v>97219</v>
+        <v>57652</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9308,13 +9309,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>549987</v>
+        <v>550047</v>
       </c>
       <c r="R86" t="n">
-        <v>6942530</v>
+        <v>6942401</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9344,6 +9345,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9467,10 +9473,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126057531</v>
+        <v>126057575</v>
       </c>
       <c r="B88" t="n">
-        <v>57652</v>
+        <v>78731</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9478,21 +9484,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9502,10 +9508,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>549974</v>
+        <v>550022</v>
       </c>
       <c r="R88" t="n">
-        <v>6942584</v>
+        <v>6942537</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9538,11 +9544,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9569,10 +9570,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126057535</v>
+        <v>126052154</v>
       </c>
       <c r="B89" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9580,21 +9581,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9604,13 +9605,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550047</v>
+        <v>550021</v>
       </c>
       <c r="R89" t="n">
-        <v>6942401</v>
+        <v>6942450</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9644,7 +9645,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9671,48 +9672,52 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126057575</v>
+        <v>126052873</v>
       </c>
       <c r="B90" t="n">
-        <v>78731</v>
+        <v>98343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550022</v>
+        <v>549989</v>
       </c>
       <c r="R90" t="n">
-        <v>6942537</v>
+        <v>6942554</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9768,32 +9773,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126052154</v>
+        <v>126052827</v>
       </c>
       <c r="B91" t="n">
-        <v>78973</v>
+        <v>97221</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9803,10 +9808,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550021</v>
+        <v>549987</v>
       </c>
       <c r="R91" t="n">
-        <v>6942450</v>
+        <v>6942530</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9839,11 +9844,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9870,10 +9870,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126057577</v>
+        <v>126057540</v>
       </c>
       <c r="B92" t="n">
-        <v>78731</v>
+        <v>57652</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9881,21 +9881,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9905,10 +9905,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550101</v>
+        <v>550138</v>
       </c>
       <c r="R92" t="n">
-        <v>6942551</v>
+        <v>6942638</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -9941,6 +9941,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9967,10 +9972,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126057581</v>
+        <v>126050713</v>
       </c>
       <c r="B93" t="n">
-        <v>78731</v>
+        <v>56835</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9978,37 +9983,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550004</v>
+        <v>550120</v>
       </c>
       <c r="R93" t="n">
-        <v>6942625</v>
+        <v>6942506</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10064,10 +10074,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126057540</v>
+        <v>126057577</v>
       </c>
       <c r="B94" t="n">
-        <v>57652</v>
+        <v>78731</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10075,21 +10085,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10099,10 +10109,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550138</v>
+        <v>550101</v>
       </c>
       <c r="R94" t="n">
-        <v>6942638</v>
+        <v>6942551</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10135,11 +10145,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10166,10 +10171,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126050713</v>
+        <v>126057581</v>
       </c>
       <c r="B95" t="n">
-        <v>56835</v>
+        <v>78731</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10177,42 +10182,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>550120</v>
+        <v>550004</v>
       </c>
       <c r="R95" t="n">
-        <v>6942506</v>
+        <v>6942625</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10268,10 +10268,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126057923</v>
+        <v>126057593</v>
       </c>
       <c r="B96" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10299,14 +10299,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>550122</v>
+        <v>550137</v>
       </c>
       <c r="R96" t="n">
-        <v>6942671</v>
+        <v>6942555</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10370,10 +10370,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126057593</v>
+        <v>126057923</v>
       </c>
       <c r="B97" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10401,14 +10401,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>550137</v>
+        <v>550122</v>
       </c>
       <c r="R97" t="n">
-        <v>6942555</v>
+        <v>6942671</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2785,32 +2785,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057582</v>
+        <v>126057526</v>
       </c>
       <c r="B21" t="n">
-        <v>98343</v>
+        <v>91236</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550023</v>
+        <v>550079</v>
       </c>
       <c r="R21" t="n">
-        <v>6942583</v>
+        <v>6942497</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2856,11 +2856,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>61 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2887,45 +2882,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057935</v>
+        <v>126057582</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550099</v>
+        <v>550023</v>
       </c>
       <c r="R22" t="n">
-        <v>6942670</v>
+        <v>6942583</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2958,6 +2953,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>61 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057526</v>
+        <v>126057935</v>
       </c>
       <c r="B23" t="n">
-        <v>91236</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2995,34 +2995,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550079</v>
+        <v>550099</v>
       </c>
       <c r="R23" t="n">
-        <v>6942497</v>
+        <v>6942670</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3469,32 +3469,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126057545</v>
+        <v>126052248</v>
       </c>
       <c r="B28" t="n">
-        <v>91247</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3504,13 +3504,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550011</v>
+        <v>550004</v>
       </c>
       <c r="R28" t="n">
-        <v>6942535</v>
+        <v>6942504</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3540,6 +3540,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom området</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3566,32 +3571,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057532</v>
+        <v>126057545</v>
       </c>
       <c r="B29" t="n">
-        <v>57652</v>
+        <v>91247</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3601,10 +3606,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550020</v>
+        <v>550011</v>
       </c>
       <c r="R29" t="n">
-        <v>6942390</v>
+        <v>6942535</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3637,11 +3642,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3668,10 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126052248</v>
+        <v>126057532</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,21 +3679,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550004</v>
+        <v>550020</v>
       </c>
       <c r="R30" t="n">
-        <v>6942504</v>
+        <v>6942390</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom området</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5370,49 +5370,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126052332</v>
+        <v>126052735</v>
       </c>
       <c r="B47" t="n">
-        <v>98364</v>
+        <v>78732</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>549984</v>
+        <v>549975</v>
       </c>
       <c r="R47" t="n">
-        <v>6942510</v>
+        <v>6942519</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5471,45 +5467,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126052735</v>
+        <v>126052332</v>
       </c>
       <c r="B48" t="n">
-        <v>78732</v>
+        <v>98364</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>549975</v>
+        <v>549984</v>
       </c>
       <c r="R48" t="n">
-        <v>6942519</v>
+        <v>6942510</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5568,53 +5568,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126051408</v>
+        <v>126057602</v>
       </c>
       <c r="B49" t="n">
-        <v>57649</v>
+        <v>98343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550089</v>
+        <v>550099</v>
       </c>
       <c r="R49" t="n">
-        <v>6942422</v>
+        <v>6942666</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5648,7 +5643,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5772,48 +5767,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126057602</v>
+        <v>126051408</v>
       </c>
       <c r="B51" t="n">
-        <v>98343</v>
+        <v>57649</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550099</v>
+        <v>550089</v>
       </c>
       <c r="R51" t="n">
-        <v>6942666</v>
+        <v>6942422</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6271,10 +6271,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126057525</v>
+        <v>126057533</v>
       </c>
       <c r="B56" t="n">
-        <v>91236</v>
+        <v>57652</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6282,21 +6282,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6306,10 +6306,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>549977</v>
+        <v>550026</v>
       </c>
       <c r="R56" t="n">
-        <v>6942580</v>
+        <v>6942422</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6342,6 +6342,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6368,48 +6373,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126057533</v>
+        <v>126050777</v>
       </c>
       <c r="B57" t="n">
-        <v>57652</v>
+        <v>56844</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550026</v>
+        <v>550093</v>
       </c>
       <c r="R57" t="n">
-        <v>6942422</v>
+        <v>6942497</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6439,11 +6449,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6470,53 +6475,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126050777</v>
+        <v>126057525</v>
       </c>
       <c r="B58" t="n">
-        <v>56844</v>
+        <v>91236</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550093</v>
+        <v>549977</v>
       </c>
       <c r="R58" t="n">
-        <v>6942497</v>
+        <v>6942580</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6572,48 +6572,52 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126057576</v>
+        <v>126052802</v>
       </c>
       <c r="B59" t="n">
-        <v>78731</v>
+        <v>98364</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550078</v>
+        <v>549987</v>
       </c>
       <c r="R59" t="n">
-        <v>6942401</v>
+        <v>6942530</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6669,38 +6673,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126051839</v>
+        <v>126048239</v>
       </c>
       <c r="B60" t="n">
-        <v>56844</v>
+        <v>98343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>56</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6709,10 +6712,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550088</v>
+        <v>550147</v>
       </c>
       <c r="R60" t="n">
-        <v>6942377</v>
+        <v>6942635</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6771,7 +6774,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126057601</v>
+        <v>126049594</v>
       </c>
       <c r="B61" t="n">
         <v>98343</v>
@@ -6799,20 +6802,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550096</v>
+        <v>550141</v>
       </c>
       <c r="R61" t="n">
-        <v>6942661</v>
+        <v>6942615</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6842,11 +6849,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6873,7 +6875,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126052934</v>
+        <v>126057601</v>
       </c>
       <c r="B62" t="n">
         <v>98343</v>
@@ -6901,24 +6903,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>549977</v>
+        <v>550096</v>
       </c>
       <c r="R62" t="n">
-        <v>6942554</v>
+        <v>6942661</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6948,6 +6946,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6974,37 +6977,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126052802</v>
+        <v>126052934</v>
       </c>
       <c r="B63" t="n">
-        <v>98364</v>
+        <v>98343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7013,10 +7016,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>549987</v>
+        <v>549977</v>
       </c>
       <c r="R63" t="n">
-        <v>6942530</v>
+        <v>6942554</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7075,52 +7078,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126048239</v>
+        <v>126057576</v>
       </c>
       <c r="B64" t="n">
-        <v>98343</v>
+        <v>78731</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550147</v>
+        <v>550078</v>
       </c>
       <c r="R64" t="n">
-        <v>6942635</v>
+        <v>6942401</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7176,37 +7175,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126049594</v>
+        <v>126051839</v>
       </c>
       <c r="B65" t="n">
-        <v>98343</v>
+        <v>56844</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550141</v>
+        <v>550088</v>
       </c>
       <c r="R65" t="n">
-        <v>6942615</v>
+        <v>6942377</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8867,10 +8867,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126047488</v>
+        <v>126057524</v>
       </c>
       <c r="B82" t="n">
-        <v>43934</v>
+        <v>91201</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8878,42 +8878,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>101735</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550158</v>
+        <v>550079</v>
       </c>
       <c r="R82" t="n">
-        <v>6942653</v>
+        <v>6942497</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8943,11 +8938,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8974,10 +8964,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126057524</v>
+        <v>126047488</v>
       </c>
       <c r="B83" t="n">
-        <v>91201</v>
+        <v>43934</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8985,37 +8975,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>101735</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550079</v>
+        <v>550158</v>
       </c>
       <c r="R83" t="n">
-        <v>6942497</v>
+        <v>6942653</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9045,6 +9040,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9172,32 +9172,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126057531</v>
+        <v>126057556</v>
       </c>
       <c r="B85" t="n">
-        <v>57652</v>
+        <v>80104</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9207,10 +9207,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>549974</v>
+        <v>550074</v>
       </c>
       <c r="R85" t="n">
-        <v>6942584</v>
+        <v>6942641</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9243,11 +9243,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9274,10 +9269,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126057535</v>
+        <v>126057575</v>
       </c>
       <c r="B86" t="n">
-        <v>57652</v>
+        <v>78731</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9285,21 +9280,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9309,10 +9304,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550047</v>
+        <v>550022</v>
       </c>
       <c r="R86" t="n">
-        <v>6942401</v>
+        <v>6942537</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9345,11 +9340,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9376,32 +9366,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126057556</v>
+        <v>126052154</v>
       </c>
       <c r="B87" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9411,13 +9401,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550074</v>
+        <v>550021</v>
       </c>
       <c r="R87" t="n">
-        <v>6942641</v>
+        <v>6942450</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9447,6 +9437,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9473,48 +9468,52 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126057575</v>
+        <v>126052873</v>
       </c>
       <c r="B88" t="n">
-        <v>78731</v>
+        <v>98343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550022</v>
+        <v>549989</v>
       </c>
       <c r="R88" t="n">
-        <v>6942537</v>
+        <v>6942554</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9570,32 +9569,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126052154</v>
+        <v>126052827</v>
       </c>
       <c r="B89" t="n">
-        <v>78973</v>
+        <v>97221</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9605,10 +9604,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550021</v>
+        <v>549987</v>
       </c>
       <c r="R89" t="n">
-        <v>6942450</v>
+        <v>6942530</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9641,11 +9640,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9672,52 +9666,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126052873</v>
+        <v>126057531</v>
       </c>
       <c r="B90" t="n">
-        <v>98343</v>
+        <v>57652</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>549989</v>
+        <v>549974</v>
       </c>
       <c r="R90" t="n">
-        <v>6942554</v>
+        <v>6942584</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9747,6 +9737,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9773,32 +9768,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126052827</v>
+        <v>126057535</v>
       </c>
       <c r="B91" t="n">
-        <v>97221</v>
+        <v>57652</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9808,13 +9803,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>549987</v>
+        <v>550047</v>
       </c>
       <c r="R91" t="n">
-        <v>6942530</v>
+        <v>6942401</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9844,6 +9839,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2390,7 +2390,7 @@
         <v>126057921</v>
       </c>
       <c r="B17" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>126057597</v>
       </c>
       <c r="B18" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057526</v>
+        <v>126057935</v>
       </c>
       <c r="B21" t="n">
-        <v>91236</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,34 +2796,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550079</v>
+        <v>550099</v>
       </c>
       <c r="R21" t="n">
-        <v>6942497</v>
+        <v>6942670</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2882,32 +2882,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057582</v>
+        <v>126057526</v>
       </c>
       <c r="B22" t="n">
-        <v>98343</v>
+        <v>91238</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550023</v>
+        <v>550079</v>
       </c>
       <c r="R22" t="n">
-        <v>6942583</v>
+        <v>6942497</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2953,11 +2953,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>61 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2984,45 +2979,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057935</v>
+        <v>126057582</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550099</v>
+        <v>550023</v>
       </c>
       <c r="R23" t="n">
-        <v>6942670</v>
+        <v>6942583</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3055,6 +3050,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>61 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,32 +3081,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126052983</v>
+        <v>126057545</v>
       </c>
       <c r="B24" t="n">
-        <v>78731</v>
+        <v>91249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>1205</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3116,13 +3116,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549977</v>
+        <v>550011</v>
       </c>
       <c r="R24" t="n">
-        <v>6942554</v>
+        <v>6942535</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3275,32 +3275,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126057544</v>
+        <v>126052983</v>
       </c>
       <c r="B26" t="n">
-        <v>80105</v>
+        <v>78731</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3310,13 +3310,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550094</v>
+        <v>549977</v>
       </c>
       <c r="R26" t="n">
-        <v>6942584</v>
+        <v>6942554</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3372,32 +3372,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126051522</v>
+        <v>126052248</v>
       </c>
       <c r="B27" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550089</v>
+        <v>550004</v>
       </c>
       <c r="R27" t="n">
-        <v>6942422</v>
+        <v>6942504</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3443,6 +3443,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom området</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3469,32 +3474,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126052248</v>
+        <v>126051522</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>80104</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3504,10 +3509,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550004</v>
+        <v>550089</v>
       </c>
       <c r="R28" t="n">
-        <v>6942504</v>
+        <v>6942422</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,11 +3545,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom området</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057545</v>
+        <v>126057544</v>
       </c>
       <c r="B29" t="n">
-        <v>91247</v>
+        <v>80105</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3582,21 +3582,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550011</v>
+        <v>550094</v>
       </c>
       <c r="R29" t="n">
-        <v>6942535</v>
+        <v>6942584</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3773,7 +3773,7 @@
         <v>126051074</v>
       </c>
       <c r="B31" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,10 +3871,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057937</v>
+        <v>126057579</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3882,34 +3882,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550147</v>
+        <v>550006</v>
       </c>
       <c r="R32" t="n">
-        <v>6942582</v>
+        <v>6942636</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3942,11 +3942,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3973,10 +3968,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057579</v>
+        <v>126057937</v>
       </c>
       <c r="B33" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3984,34 +3979,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550006</v>
+        <v>550147</v>
       </c>
       <c r="R33" t="n">
-        <v>6942636</v>
+        <v>6942582</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4044,6 +4039,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4167,10 +4167,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057538</v>
+        <v>126053984</v>
       </c>
       <c r="B35" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4178,21 +4178,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4202,13 +4202,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550041</v>
+        <v>549984</v>
       </c>
       <c r="R35" t="n">
-        <v>6942496</v>
+        <v>6942510</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4269,10 +4269,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126053984</v>
+        <v>126057538</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4304,13 +4304,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549984</v>
+        <v>550041</v>
       </c>
       <c r="R36" t="n">
-        <v>6942510</v>
+        <v>6942496</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4374,7 +4374,7 @@
         <v>126057596</v>
       </c>
       <c r="B37" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>126057591</v>
       </c>
       <c r="B38" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4575,32 +4575,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057569</v>
+        <v>126052912</v>
       </c>
       <c r="B39" t="n">
-        <v>80076</v>
+        <v>80104</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550006</v>
+        <v>549977</v>
       </c>
       <c r="R39" t="n">
-        <v>6942630</v>
+        <v>6942554</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4672,32 +4672,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126052912</v>
+        <v>126057569</v>
       </c>
       <c r="B40" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4707,13 +4707,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549977</v>
+        <v>550006</v>
       </c>
       <c r="R40" t="n">
-        <v>6942554</v>
+        <v>6942630</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>126057592</v>
       </c>
       <c r="B41" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>126052420</v>
       </c>
       <c r="B42" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>126057600</v>
       </c>
       <c r="B43" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5074,45 +5074,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057568</v>
+        <v>126057896</v>
       </c>
       <c r="B44" t="n">
-        <v>80076</v>
+        <v>80104</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550093</v>
+        <v>550007</v>
       </c>
       <c r="R44" t="n">
-        <v>6942579</v>
+        <v>6942646</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5171,45 +5171,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057896</v>
+        <v>126057568</v>
       </c>
       <c r="B45" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550007</v>
+        <v>550093</v>
       </c>
       <c r="R45" t="n">
-        <v>6942646</v>
+        <v>6942579</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5271,7 +5271,7 @@
         <v>126057930</v>
       </c>
       <c r="B46" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>126052332</v>
       </c>
       <c r="B48" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5568,48 +5568,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126057602</v>
+        <v>126049249</v>
       </c>
       <c r="B49" t="n">
-        <v>98343</v>
+        <v>58021</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550099</v>
+        <v>550135</v>
       </c>
       <c r="R49" t="n">
-        <v>6942666</v>
+        <v>6942628</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5639,11 +5648,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5874,57 +5878,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126049249</v>
+        <v>126057602</v>
       </c>
       <c r="B52" t="n">
-        <v>58021</v>
+        <v>98345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550135</v>
+        <v>550099</v>
       </c>
       <c r="R52" t="n">
-        <v>6942628</v>
+        <v>6942666</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5954,6 +5949,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5980,32 +5980,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057898</v>
+        <v>126057915</v>
       </c>
       <c r="B53" t="n">
-        <v>80104</v>
+        <v>78731</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>549997</v>
+        <v>550145</v>
       </c>
       <c r="R53" t="n">
-        <v>6942637</v>
+        <v>6942577</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6077,32 +6077,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057915</v>
+        <v>126057898</v>
       </c>
       <c r="B54" t="n">
-        <v>78731</v>
+        <v>80104</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550145</v>
+        <v>549997</v>
       </c>
       <c r="R54" t="n">
-        <v>6942577</v>
+        <v>6942637</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6271,10 +6271,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126057533</v>
+        <v>126057525</v>
       </c>
       <c r="B56" t="n">
-        <v>57652</v>
+        <v>91238</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6282,21 +6282,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6306,10 +6306,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550026</v>
+        <v>549977</v>
       </c>
       <c r="R56" t="n">
-        <v>6942422</v>
+        <v>6942580</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6342,11 +6342,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6475,10 +6470,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126057525</v>
+        <v>126057533</v>
       </c>
       <c r="B58" t="n">
-        <v>91236</v>
+        <v>57652</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6486,21 +6481,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6510,10 +6505,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>549977</v>
+        <v>550026</v>
       </c>
       <c r="R58" t="n">
-        <v>6942580</v>
+        <v>6942422</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6546,6 +6541,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6572,37 +6572,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126052802</v>
+        <v>126049594</v>
       </c>
       <c r="B59" t="n">
-        <v>98364</v>
+        <v>98345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6611,10 +6611,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>549987</v>
+        <v>550141</v>
       </c>
       <c r="R59" t="n">
-        <v>6942530</v>
+        <v>6942615</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6676,7 +6676,7 @@
         <v>126048239</v>
       </c>
       <c r="B60" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6774,37 +6774,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126049594</v>
+        <v>126051839</v>
       </c>
       <c r="B61" t="n">
-        <v>98343</v>
+        <v>56844</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6813,10 +6814,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550141</v>
+        <v>550088</v>
       </c>
       <c r="R61" t="n">
-        <v>6942615</v>
+        <v>6942377</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6875,32 +6876,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126057601</v>
+        <v>126057576</v>
       </c>
       <c r="B62" t="n">
-        <v>98343</v>
+        <v>78731</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6910,10 +6911,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550096</v>
+        <v>550078</v>
       </c>
       <c r="R62" t="n">
-        <v>6942661</v>
+        <v>6942401</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6946,11 +6947,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6977,10 +6973,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126052934</v>
+        <v>126057601</v>
       </c>
       <c r="B63" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7005,24 +7001,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>549977</v>
+        <v>550096</v>
       </c>
       <c r="R63" t="n">
-        <v>6942554</v>
+        <v>6942661</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7052,6 +7044,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7078,48 +7075,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126057576</v>
+        <v>126052934</v>
       </c>
       <c r="B64" t="n">
-        <v>78731</v>
+        <v>98345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550078</v>
+        <v>549977</v>
       </c>
       <c r="R64" t="n">
-        <v>6942401</v>
+        <v>6942554</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7175,10 +7176,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126051839</v>
+        <v>126052802</v>
       </c>
       <c r="B65" t="n">
-        <v>56844</v>
+        <v>98366</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7186,27 +7187,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550088</v>
+        <v>549987</v>
       </c>
       <c r="R65" t="n">
-        <v>6942377</v>
+        <v>6942530</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7280,7 +7280,7 @@
         <v>126051197</v>
       </c>
       <c r="B66" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>126051507</v>
       </c>
       <c r="B67" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>126057594</v>
       </c>
       <c r="B68" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>126057583</v>
       </c>
       <c r="B70" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7781,32 +7781,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126053048</v>
+        <v>126051112</v>
       </c>
       <c r="B71" t="n">
-        <v>78973</v>
+        <v>80104</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7816,10 +7816,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>549965</v>
+        <v>550093</v>
       </c>
       <c r="R71" t="n">
-        <v>6942583</v>
+        <v>6942497</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7852,11 +7852,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I området</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7883,32 +7878,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126051112</v>
+        <v>126053048</v>
       </c>
       <c r="B72" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7918,10 +7913,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550093</v>
+        <v>549965</v>
       </c>
       <c r="R72" t="n">
-        <v>6942497</v>
+        <v>6942583</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7954,6 +7949,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I området</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126057549</v>
+        <v>126057578</v>
       </c>
       <c r="B73" t="n">
-        <v>91690</v>
+        <v>78731</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>549978</v>
+        <v>550086</v>
       </c>
       <c r="R73" t="n">
-        <v>6942581</v>
+        <v>6942580</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8077,10 +8077,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126057578</v>
+        <v>126049570</v>
       </c>
       <c r="B74" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8112,13 +8112,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550086</v>
+        <v>550135</v>
       </c>
       <c r="R74" t="n">
-        <v>6942580</v>
+        <v>6942628</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8148,6 +8148,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8174,32 +8179,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126049570</v>
+        <v>126057549</v>
       </c>
       <c r="B75" t="n">
-        <v>78973</v>
+        <v>91692</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8209,13 +8214,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550135</v>
+        <v>549978</v>
       </c>
       <c r="R75" t="n">
-        <v>6942628</v>
+        <v>6942581</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8245,11 +8250,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8276,10 +8276,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126057904</v>
+        <v>126050913</v>
       </c>
       <c r="B76" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8287,37 +8287,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>549997</v>
+        <v>550088</v>
       </c>
       <c r="R76" t="n">
-        <v>6942637</v>
+        <v>6942520</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8347,6 +8347,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8373,7 +8378,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126050913</v>
+        <v>126057606</v>
       </c>
       <c r="B77" t="n">
         <v>78973</v>
@@ -8408,13 +8413,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550088</v>
+        <v>550034</v>
       </c>
       <c r="R77" t="n">
-        <v>6942520</v>
+        <v>6942421</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8444,11 +8449,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8475,10 +8475,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126057606</v>
+        <v>126057904</v>
       </c>
       <c r="B78" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8486,34 +8486,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550034</v>
+        <v>549997</v>
       </c>
       <c r="R78" t="n">
-        <v>6942421</v>
+        <v>6942637</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8575,7 +8575,7 @@
         <v>126051602</v>
       </c>
       <c r="B79" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8673,48 +8673,53 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126057574</v>
+        <v>126047488</v>
       </c>
       <c r="B80" t="n">
-        <v>78731</v>
+        <v>43934</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>101735</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>549990</v>
+        <v>550158</v>
       </c>
       <c r="R80" t="n">
-        <v>6942590</v>
+        <v>6942653</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8744,6 +8749,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8867,32 +8877,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126057524</v>
+        <v>126057574</v>
       </c>
       <c r="B82" t="n">
-        <v>91201</v>
+        <v>78731</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8902,10 +8912,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550079</v>
+        <v>549990</v>
       </c>
       <c r="R82" t="n">
-        <v>6942497</v>
+        <v>6942590</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8964,10 +8974,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126047488</v>
+        <v>126057524</v>
       </c>
       <c r="B83" t="n">
-        <v>43934</v>
+        <v>91203</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8975,42 +8985,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>101735</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550158</v>
+        <v>550079</v>
       </c>
       <c r="R83" t="n">
-        <v>6942653</v>
+        <v>6942497</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9040,11 +9045,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9074,7 +9074,7 @@
         <v>126051270</v>
       </c>
       <c r="B84" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9172,32 +9172,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126057556</v>
+        <v>126057531</v>
       </c>
       <c r="B85" t="n">
-        <v>80104</v>
+        <v>57652</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9207,10 +9207,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550074</v>
+        <v>549974</v>
       </c>
       <c r="R85" t="n">
-        <v>6942641</v>
+        <v>6942584</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9243,6 +9243,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9269,10 +9274,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126057575</v>
+        <v>126057535</v>
       </c>
       <c r="B86" t="n">
-        <v>78731</v>
+        <v>57652</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9280,21 +9285,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9304,10 +9309,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550022</v>
+        <v>550047</v>
       </c>
       <c r="R86" t="n">
-        <v>6942537</v>
+        <v>6942401</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9340,6 +9345,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9366,32 +9376,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126052154</v>
+        <v>126052827</v>
       </c>
       <c r="B87" t="n">
-        <v>78973</v>
+        <v>97223</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9401,10 +9411,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550021</v>
+        <v>549987</v>
       </c>
       <c r="R87" t="n">
-        <v>6942450</v>
+        <v>6942530</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9437,11 +9447,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9471,7 +9476,7 @@
         <v>126052873</v>
       </c>
       <c r="B88" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9569,32 +9574,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126052827</v>
+        <v>126057575</v>
       </c>
       <c r="B89" t="n">
-        <v>97221</v>
+        <v>78731</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9604,13 +9609,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>549987</v>
+        <v>550022</v>
       </c>
       <c r="R89" t="n">
-        <v>6942530</v>
+        <v>6942537</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9666,32 +9671,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126057531</v>
+        <v>126057556</v>
       </c>
       <c r="B90" t="n">
-        <v>57652</v>
+        <v>80104</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9701,10 +9706,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>549974</v>
+        <v>550074</v>
       </c>
       <c r="R90" t="n">
-        <v>6942584</v>
+        <v>6942641</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9737,11 +9742,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9768,10 +9768,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126057535</v>
+        <v>126052154</v>
       </c>
       <c r="B91" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9779,21 +9779,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550047</v>
+        <v>550021</v>
       </c>
       <c r="R91" t="n">
-        <v>6942401</v>
+        <v>6942450</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10074,32 +10074,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126057577</v>
+        <v>126057593</v>
       </c>
       <c r="B94" t="n">
-        <v>78731</v>
+        <v>98345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10109,10 +10109,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550101</v>
+        <v>550137</v>
       </c>
       <c r="R94" t="n">
-        <v>6942551</v>
+        <v>6942555</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10145,6 +10145,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10171,45 +10176,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126057581</v>
+        <v>126057923</v>
       </c>
       <c r="B95" t="n">
-        <v>78731</v>
+        <v>98345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>550004</v>
+        <v>550122</v>
       </c>
       <c r="R95" t="n">
-        <v>6942625</v>
+        <v>6942671</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10242,6 +10247,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10268,32 +10278,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126057593</v>
+        <v>126057577</v>
       </c>
       <c r="B96" t="n">
-        <v>98343</v>
+        <v>78731</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10303,10 +10313,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>550137</v>
+        <v>550101</v>
       </c>
       <c r="R96" t="n">
-        <v>6942555</v>
+        <v>6942551</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10339,11 +10349,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>3 ex</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10370,45 +10375,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126057923</v>
+        <v>126057581</v>
       </c>
       <c r="B97" t="n">
-        <v>98343</v>
+        <v>78731</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>550122</v>
+        <v>550004</v>
       </c>
       <c r="R97" t="n">
-        <v>6942671</v>
+        <v>6942625</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10441,11 +10446,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -4575,32 +4575,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126052912</v>
+        <v>126057592</v>
       </c>
       <c r="B39" t="n">
-        <v>80104</v>
+        <v>98345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549977</v>
+        <v>550038</v>
       </c>
       <c r="R39" t="n">
-        <v>6942554</v>
+        <v>6942494</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4646,6 +4646,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>28 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4672,48 +4677,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057569</v>
+        <v>126052420</v>
       </c>
       <c r="B40" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550006</v>
+        <v>549984</v>
       </c>
       <c r="R40" t="n">
-        <v>6942630</v>
+        <v>6942510</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4769,7 +4778,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126057592</v>
+        <v>126057600</v>
       </c>
       <c r="B41" t="n">
         <v>98345</v>
@@ -4804,10 +4813,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550038</v>
+        <v>550095</v>
       </c>
       <c r="R41" t="n">
-        <v>6942494</v>
+        <v>6942646</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4844,7 +4853,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>28 ex</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4871,49 +4880,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126052420</v>
+        <v>126052912</v>
       </c>
       <c r="B42" t="n">
-        <v>98345</v>
+        <v>80104</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549984</v>
+        <v>549977</v>
       </c>
       <c r="R42" t="n">
-        <v>6942510</v>
+        <v>6942554</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,32 +4977,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126057600</v>
+        <v>126057569</v>
       </c>
       <c r="B43" t="n">
-        <v>98345</v>
+        <v>80076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5007,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550095</v>
+        <v>550006</v>
       </c>
       <c r="R43" t="n">
-        <v>6942646</v>
+        <v>6942630</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5043,11 +5048,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6271,10 +6271,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126057525</v>
+        <v>126057533</v>
       </c>
       <c r="B56" t="n">
-        <v>91238</v>
+        <v>57652</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6282,21 +6282,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6306,10 +6306,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>549977</v>
+        <v>550026</v>
       </c>
       <c r="R56" t="n">
-        <v>6942580</v>
+        <v>6942422</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6342,6 +6342,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6470,10 +6475,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126057533</v>
+        <v>126057525</v>
       </c>
       <c r="B58" t="n">
-        <v>57652</v>
+        <v>91238</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6481,21 +6486,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6505,10 +6510,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550026</v>
+        <v>549977</v>
       </c>
       <c r="R58" t="n">
-        <v>6942422</v>
+        <v>6942580</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6541,11 +6546,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6774,53 +6774,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126051839</v>
+        <v>126057576</v>
       </c>
       <c r="B61" t="n">
-        <v>56844</v>
+        <v>78731</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550088</v>
+        <v>550078</v>
       </c>
       <c r="R61" t="n">
-        <v>6942377</v>
+        <v>6942401</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6876,48 +6871,52 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126057576</v>
+        <v>126052802</v>
       </c>
       <c r="B62" t="n">
-        <v>78731</v>
+        <v>98366</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550078</v>
+        <v>549987</v>
       </c>
       <c r="R62" t="n">
-        <v>6942401</v>
+        <v>6942530</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6973,48 +6972,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126057601</v>
+        <v>126051839</v>
       </c>
       <c r="B63" t="n">
-        <v>98345</v>
+        <v>56844</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550096</v>
+        <v>550088</v>
       </c>
       <c r="R63" t="n">
-        <v>6942661</v>
+        <v>6942377</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7044,11 +7048,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7075,7 +7074,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126052934</v>
+        <v>126057601</v>
       </c>
       <c r="B64" t="n">
         <v>98345</v>
@@ -7103,24 +7102,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>549977</v>
+        <v>550096</v>
       </c>
       <c r="R64" t="n">
-        <v>6942554</v>
+        <v>6942661</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7150,6 +7145,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7176,37 +7176,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126052802</v>
+        <v>126052934</v>
       </c>
       <c r="B65" t="n">
-        <v>98366</v>
+        <v>98345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>549987</v>
+        <v>549977</v>
       </c>
       <c r="R65" t="n">
-        <v>6942530</v>
+        <v>6942554</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7277,32 +7277,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126051197</v>
+        <v>126057594</v>
       </c>
       <c r="B66" t="n">
-        <v>97223</v>
+        <v>98345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7312,13 +7312,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550077</v>
+        <v>550130</v>
       </c>
       <c r="R66" t="n">
-        <v>6942476</v>
+        <v>6942565</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7348,6 +7348,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7374,10 +7379,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126051507</v>
+        <v>126051197</v>
       </c>
       <c r="B67" t="n">
-        <v>98366</v>
+        <v>97223</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7385,38 +7390,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550089</v>
+        <v>550077</v>
       </c>
       <c r="R67" t="n">
-        <v>6942422</v>
+        <v>6942476</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7475,48 +7476,52 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126057594</v>
+        <v>126051507</v>
       </c>
       <c r="B68" t="n">
-        <v>98345</v>
+        <v>98366</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550130</v>
+        <v>550089</v>
       </c>
       <c r="R68" t="n">
-        <v>6942565</v>
+        <v>6942422</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7546,11 +7551,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7980,10 +7980,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126057578</v>
+        <v>126049570</v>
       </c>
       <c r="B73" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7991,21 +7991,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550086</v>
+        <v>550135</v>
       </c>
       <c r="R73" t="n">
-        <v>6942580</v>
+        <v>6942628</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8051,6 +8051,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8077,10 +8082,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126049570</v>
+        <v>126057578</v>
       </c>
       <c r="B74" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8088,21 +8093,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8112,13 +8117,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550135</v>
+        <v>550086</v>
       </c>
       <c r="R74" t="n">
-        <v>6942628</v>
+        <v>6942580</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8148,11 +8153,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8673,10 +8673,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126047488</v>
+        <v>126057559</v>
       </c>
       <c r="B80" t="n">
-        <v>43934</v>
+        <v>80104</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8684,42 +8684,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>101735</v>
+        <v>6461</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550158</v>
+        <v>550000</v>
       </c>
       <c r="R80" t="n">
-        <v>6942653</v>
+        <v>6942626</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8749,11 +8744,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8780,32 +8770,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126057559</v>
+        <v>126057574</v>
       </c>
       <c r="B81" t="n">
-        <v>80104</v>
+        <v>78731</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8815,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550000</v>
+        <v>549990</v>
       </c>
       <c r="R81" t="n">
-        <v>6942626</v>
+        <v>6942590</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8877,32 +8867,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126057574</v>
+        <v>126057524</v>
       </c>
       <c r="B82" t="n">
-        <v>78731</v>
+        <v>91203</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8912,10 +8902,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>549990</v>
+        <v>550079</v>
       </c>
       <c r="R82" t="n">
-        <v>6942590</v>
+        <v>6942497</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8974,48 +8964,52 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126057524</v>
+        <v>126051270</v>
       </c>
       <c r="B83" t="n">
-        <v>91203</v>
+        <v>98345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550079</v>
+        <v>550065</v>
       </c>
       <c r="R83" t="n">
-        <v>6942497</v>
+        <v>6942463</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9071,37 +9065,38 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126051270</v>
+        <v>126047488</v>
       </c>
       <c r="B84" t="n">
-        <v>98345</v>
+        <v>43934</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>43</t>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9110,13 +9105,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550065</v>
+        <v>550158</v>
       </c>
       <c r="R84" t="n">
-        <v>6942463</v>
+        <v>6942653</v>
       </c>
       <c r="S84" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9146,6 +9141,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2183,32 +2183,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126057934</v>
+        <v>126057921</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550127</v>
+        <v>550142</v>
       </c>
       <c r="R15" t="n">
-        <v>6942669</v>
+        <v>6942582</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,32 +2285,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126057536</v>
+        <v>126057597</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>98349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550113</v>
+        <v>550099</v>
       </c>
       <c r="R16" t="n">
-        <v>6942389</v>
+        <v>6942637</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,45 +2387,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126057921</v>
+        <v>126057564</v>
       </c>
       <c r="B17" t="n">
-        <v>98345</v>
+        <v>78736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550142</v>
+        <v>550076</v>
       </c>
       <c r="R17" t="n">
-        <v>6942582</v>
+        <v>6942390</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2458,11 +2458,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,45 +2484,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057597</v>
+        <v>126057934</v>
       </c>
       <c r="B18" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550099</v>
+        <v>550127</v>
       </c>
       <c r="R18" t="n">
-        <v>6942637</v>
+        <v>6942669</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2564,7 +2559,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,10 +2586,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057564</v>
+        <v>126057536</v>
       </c>
       <c r="B19" t="n">
-        <v>78732</v>
+        <v>57656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,21 +2597,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550076</v>
+        <v>550113</v>
       </c>
       <c r="R19" t="n">
-        <v>6942390</v>
+        <v>6942389</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2662,6 +2657,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,7 +2691,7 @@
         <v>126057563</v>
       </c>
       <c r="B20" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,45 +2785,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057935</v>
+        <v>126057582</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550099</v>
+        <v>550023</v>
       </c>
       <c r="R21" t="n">
-        <v>6942670</v>
+        <v>6942583</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2856,6 +2856,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>61 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,10 +2887,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057526</v>
+        <v>126057935</v>
       </c>
       <c r="B22" t="n">
-        <v>91238</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,34 +2898,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550079</v>
+        <v>550099</v>
       </c>
       <c r="R22" t="n">
-        <v>6942497</v>
+        <v>6942670</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2979,32 +2984,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057582</v>
+        <v>126057526</v>
       </c>
       <c r="B23" t="n">
-        <v>98345</v>
+        <v>91242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3014,10 +3019,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550023</v>
+        <v>550079</v>
       </c>
       <c r="R23" t="n">
-        <v>6942583</v>
+        <v>6942497</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3050,11 +3055,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>61 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3084,7 +3084,7 @@
         <v>126057545</v>
       </c>
       <c r="B24" t="n">
-        <v>91249</v>
+        <v>91253</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>126050880</v>
       </c>
       <c r="B25" t="n">
-        <v>80104</v>
+        <v>80108</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>126052983</v>
       </c>
       <c r="B26" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>126052248</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>126051522</v>
       </c>
       <c r="B28" t="n">
-        <v>80104</v>
+        <v>80108</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>126057544</v>
       </c>
       <c r="B29" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>126057532</v>
       </c>
       <c r="B30" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>126051074</v>
       </c>
       <c r="B31" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>126057579</v>
       </c>
       <c r="B32" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,10 +3968,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057937</v>
+        <v>126057567</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>80080</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3979,34 +3979,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550147</v>
+        <v>550001</v>
       </c>
       <c r="R33" t="n">
-        <v>6942582</v>
+        <v>6942503</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4039,11 +4039,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4070,10 +4065,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057567</v>
+        <v>126053984</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4081,21 +4076,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4105,13 +4100,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550001</v>
+        <v>549984</v>
       </c>
       <c r="R34" t="n">
-        <v>6942503</v>
+        <v>6942510</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4141,6 +4136,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4167,10 +4167,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126053984</v>
+        <v>126057538</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4178,21 +4178,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4202,13 +4202,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549984</v>
+        <v>550041</v>
       </c>
       <c r="R35" t="n">
-        <v>6942510</v>
+        <v>6942496</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4269,10 +4269,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057538</v>
+        <v>126057937</v>
       </c>
       <c r="B36" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4280,34 +4280,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550041</v>
+        <v>550147</v>
       </c>
       <c r="R36" t="n">
-        <v>6942496</v>
+        <v>6942582</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4374,7 +4374,7 @@
         <v>126057596</v>
       </c>
       <c r="B37" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>126057591</v>
       </c>
       <c r="B38" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4575,32 +4575,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057592</v>
+        <v>126052912</v>
       </c>
       <c r="B39" t="n">
-        <v>98345</v>
+        <v>80108</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550038</v>
+        <v>549977</v>
       </c>
       <c r="R39" t="n">
-        <v>6942494</v>
+        <v>6942554</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4646,11 +4646,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>28 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4677,52 +4672,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126052420</v>
+        <v>126057569</v>
       </c>
       <c r="B40" t="n">
-        <v>98345</v>
+        <v>80080</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549984</v>
+        <v>550006</v>
       </c>
       <c r="R40" t="n">
-        <v>6942510</v>
+        <v>6942630</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4778,10 +4769,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126057600</v>
+        <v>126057592</v>
       </c>
       <c r="B41" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4813,10 +4804,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550095</v>
+        <v>550038</v>
       </c>
       <c r="R41" t="n">
-        <v>6942646</v>
+        <v>6942494</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4853,7 +4844,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>28 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4880,45 +4871,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126052912</v>
+        <v>126052420</v>
       </c>
       <c r="B42" t="n">
-        <v>80104</v>
+        <v>98349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549977</v>
+        <v>549984</v>
       </c>
       <c r="R42" t="n">
-        <v>6942554</v>
+        <v>6942510</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4977,32 +4972,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126057569</v>
+        <v>126057600</v>
       </c>
       <c r="B43" t="n">
-        <v>80076</v>
+        <v>98349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5012,10 +5007,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550006</v>
+        <v>550095</v>
       </c>
       <c r="R43" t="n">
-        <v>6942630</v>
+        <v>6942646</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5048,6 +5043,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5077,7 +5077,7 @@
         <v>126057896</v>
       </c>
       <c r="B44" t="n">
-        <v>80104</v>
+        <v>80108</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>126057568</v>
       </c>
       <c r="B45" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5268,48 +5268,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057930</v>
+        <v>126052735</v>
       </c>
       <c r="B46" t="n">
-        <v>98345</v>
+        <v>78736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550112</v>
+        <v>549975</v>
       </c>
       <c r="R46" t="n">
-        <v>6942664</v>
+        <v>6942519</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5339,11 +5339,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>50stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5370,45 +5365,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126052735</v>
+        <v>126052332</v>
       </c>
       <c r="B47" t="n">
-        <v>78732</v>
+        <v>98370</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>549975</v>
+        <v>549984</v>
       </c>
       <c r="R47" t="n">
-        <v>6942519</v>
+        <v>6942510</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5467,52 +5466,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126052332</v>
+        <v>126057930</v>
       </c>
       <c r="B48" t="n">
-        <v>98366</v>
+        <v>98349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>549984</v>
+        <v>550112</v>
       </c>
       <c r="R48" t="n">
-        <v>6942510</v>
+        <v>6942664</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5542,6 +5537,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>50stycken</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5568,10 +5568,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126049249</v>
+        <v>126051690</v>
       </c>
       <c r="B49" t="n">
-        <v>58021</v>
+        <v>80108</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5579,43 +5579,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>6461</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550135</v>
+        <v>550110</v>
       </c>
       <c r="R49" t="n">
-        <v>6942628</v>
+        <v>6942386</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5674,10 +5665,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126051690</v>
+        <v>126049249</v>
       </c>
       <c r="B50" t="n">
-        <v>80104</v>
+        <v>58025</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5685,34 +5676,43 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550110</v>
+        <v>550135</v>
       </c>
       <c r="R50" t="n">
-        <v>6942386</v>
+        <v>6942628</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5771,53 +5771,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126051408</v>
+        <v>126057602</v>
       </c>
       <c r="B51" t="n">
-        <v>57649</v>
+        <v>98349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550089</v>
+        <v>550099</v>
       </c>
       <c r="R51" t="n">
-        <v>6942422</v>
+        <v>6942666</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5851,7 +5846,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5878,48 +5873,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126057602</v>
+        <v>126051408</v>
       </c>
       <c r="B52" t="n">
-        <v>98345</v>
+        <v>57653</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550099</v>
+        <v>550089</v>
       </c>
       <c r="R52" t="n">
-        <v>6942666</v>
+        <v>6942422</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5983,7 +5983,7 @@
         <v>126057915</v>
       </c>
       <c r="B53" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>126057898</v>
       </c>
       <c r="B54" t="n">
-        <v>80104</v>
+        <v>80108</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>126057565</v>
       </c>
       <c r="B55" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>126057533</v>
       </c>
       <c r="B56" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6373,53 +6373,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126050777</v>
+        <v>126057525</v>
       </c>
       <c r="B57" t="n">
-        <v>56844</v>
+        <v>91242</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550093</v>
+        <v>549977</v>
       </c>
       <c r="R57" t="n">
-        <v>6942497</v>
+        <v>6942580</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6475,48 +6470,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126057525</v>
+        <v>126050777</v>
       </c>
       <c r="B58" t="n">
-        <v>91238</v>
+        <v>56848</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>549977</v>
+        <v>550093</v>
       </c>
       <c r="R58" t="n">
-        <v>6942580</v>
+        <v>6942497</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6572,52 +6572,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126049594</v>
+        <v>126057576</v>
       </c>
       <c r="B59" t="n">
-        <v>98345</v>
+        <v>78735</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550141</v>
+        <v>550078</v>
       </c>
       <c r="R59" t="n">
-        <v>6942615</v>
+        <v>6942401</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6673,37 +6669,38 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126048239</v>
+        <v>126051839</v>
       </c>
       <c r="B60" t="n">
-        <v>98345</v>
+        <v>56848</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>56</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6712,10 +6709,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550147</v>
+        <v>550088</v>
       </c>
       <c r="R60" t="n">
-        <v>6942635</v>
+        <v>6942377</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6774,48 +6771,52 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126057576</v>
+        <v>126049594</v>
       </c>
       <c r="B61" t="n">
-        <v>78731</v>
+        <v>98349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550078</v>
+        <v>550141</v>
       </c>
       <c r="R61" t="n">
-        <v>6942401</v>
+        <v>6942615</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6871,37 +6872,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126052802</v>
+        <v>126048239</v>
       </c>
       <c r="B62" t="n">
-        <v>98366</v>
+        <v>98349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6910,10 +6911,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>549987</v>
+        <v>550147</v>
       </c>
       <c r="R62" t="n">
-        <v>6942530</v>
+        <v>6942635</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6972,53 +6973,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126051839</v>
+        <v>126057601</v>
       </c>
       <c r="B63" t="n">
-        <v>56844</v>
+        <v>98349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550088</v>
+        <v>550096</v>
       </c>
       <c r="R63" t="n">
-        <v>6942377</v>
+        <v>6942661</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7048,6 +7044,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7074,10 +7075,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126057601</v>
+        <v>126052934</v>
       </c>
       <c r="B64" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7102,20 +7103,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550096</v>
+        <v>549977</v>
       </c>
       <c r="R64" t="n">
-        <v>6942661</v>
+        <v>6942554</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7145,11 +7150,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7176,37 +7176,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126052934</v>
+        <v>126052802</v>
       </c>
       <c r="B65" t="n">
-        <v>98345</v>
+        <v>98370</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>549977</v>
+        <v>549987</v>
       </c>
       <c r="R65" t="n">
-        <v>6942554</v>
+        <v>6942530</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7280,7 +7280,7 @@
         <v>126057594</v>
       </c>
       <c r="B66" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>126051197</v>
       </c>
       <c r="B67" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>126051507</v>
       </c>
       <c r="B68" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>126057537</v>
       </c>
       <c r="B69" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7679,32 +7679,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126057583</v>
+        <v>126053048</v>
       </c>
       <c r="B70" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7714,13 +7714,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550098</v>
+        <v>549965</v>
       </c>
       <c r="R70" t="n">
-        <v>6942641</v>
+        <v>6942583</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>31 ex</t>
+          <t>Rikligt med garnlav I området</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7784,7 +7784,7 @@
         <v>126051112</v>
       </c>
       <c r="B71" t="n">
-        <v>80104</v>
+        <v>80108</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7878,32 +7878,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126053048</v>
+        <v>126057583</v>
       </c>
       <c r="B72" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7913,13 +7913,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>549965</v>
+        <v>550098</v>
       </c>
       <c r="R72" t="n">
-        <v>6942583</v>
+        <v>6942641</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav I området</t>
+          <t>31 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126049570</v>
+        <v>126057549</v>
       </c>
       <c r="B73" t="n">
-        <v>78973</v>
+        <v>91696</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550135</v>
+        <v>549978</v>
       </c>
       <c r="R73" t="n">
-        <v>6942628</v>
+        <v>6942581</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8051,11 +8051,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8085,7 +8080,7 @@
         <v>126057578</v>
       </c>
       <c r="B74" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8179,32 +8174,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126057549</v>
+        <v>126049570</v>
       </c>
       <c r="B75" t="n">
-        <v>91692</v>
+        <v>78977</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8214,13 +8209,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>549978</v>
+        <v>550135</v>
       </c>
       <c r="R75" t="n">
-        <v>6942581</v>
+        <v>6942628</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8250,6 +8245,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8276,45 +8276,49 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126050913</v>
+        <v>126051602</v>
       </c>
       <c r="B76" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550088</v>
+        <v>550089</v>
       </c>
       <c r="R76" t="n">
-        <v>6942520</v>
+        <v>6942422</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8347,11 +8351,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8378,10 +8377,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126057606</v>
+        <v>126050913</v>
       </c>
       <c r="B77" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8413,13 +8412,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550034</v>
+        <v>550088</v>
       </c>
       <c r="R77" t="n">
-        <v>6942421</v>
+        <v>6942520</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8449,6 +8448,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8475,10 +8479,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126057904</v>
+        <v>126057606</v>
       </c>
       <c r="B78" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8486,34 +8490,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>549997</v>
+        <v>550034</v>
       </c>
       <c r="R78" t="n">
-        <v>6942637</v>
+        <v>6942421</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8572,52 +8576,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126051602</v>
+        <v>126057904</v>
       </c>
       <c r="B79" t="n">
-        <v>98345</v>
+        <v>80080</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550089</v>
+        <v>549997</v>
       </c>
       <c r="R79" t="n">
-        <v>6942422</v>
+        <v>6942637</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8673,10 +8673,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126057559</v>
+        <v>126047488</v>
       </c>
       <c r="B80" t="n">
-        <v>80104</v>
+        <v>43934</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8684,37 +8684,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6461</v>
+        <v>101735</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550000</v>
+        <v>550158</v>
       </c>
       <c r="R80" t="n">
-        <v>6942626</v>
+        <v>6942653</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8744,6 +8749,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8770,32 +8780,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126057574</v>
+        <v>126057524</v>
       </c>
       <c r="B81" t="n">
-        <v>78731</v>
+        <v>91207</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8815,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>549990</v>
+        <v>550079</v>
       </c>
       <c r="R81" t="n">
-        <v>6942590</v>
+        <v>6942497</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8867,10 +8877,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126057524</v>
+        <v>126057559</v>
       </c>
       <c r="B82" t="n">
-        <v>91203</v>
+        <v>80108</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8878,21 +8888,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8902,10 +8912,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550079</v>
+        <v>550000</v>
       </c>
       <c r="R82" t="n">
-        <v>6942497</v>
+        <v>6942626</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8964,52 +8974,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126051270</v>
+        <v>126057574</v>
       </c>
       <c r="B83" t="n">
-        <v>98345</v>
+        <v>78735</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550065</v>
+        <v>549990</v>
       </c>
       <c r="R83" t="n">
-        <v>6942463</v>
+        <v>6942590</v>
       </c>
       <c r="S83" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9065,38 +9071,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126047488</v>
+        <v>126051270</v>
       </c>
       <c r="B84" t="n">
-        <v>43934</v>
+        <v>98349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>43</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9105,13 +9110,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550158</v>
+        <v>550065</v>
       </c>
       <c r="R84" t="n">
-        <v>6942653</v>
+        <v>6942463</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9141,11 +9146,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9172,48 +9172,52 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126057531</v>
+        <v>126052873</v>
       </c>
       <c r="B85" t="n">
-        <v>57652</v>
+        <v>98349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>549974</v>
+        <v>549989</v>
       </c>
       <c r="R85" t="n">
-        <v>6942584</v>
+        <v>6942554</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9243,11 +9247,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9274,32 +9273,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126057535</v>
+        <v>126052827</v>
       </c>
       <c r="B86" t="n">
-        <v>57652</v>
+        <v>97227</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9309,13 +9308,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550047</v>
+        <v>549987</v>
       </c>
       <c r="R86" t="n">
-        <v>6942401</v>
+        <v>6942530</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9345,11 +9344,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9376,10 +9370,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126052827</v>
+        <v>126057556</v>
       </c>
       <c r="B87" t="n">
-        <v>97223</v>
+        <v>80108</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9387,21 +9381,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9411,13 +9405,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>549987</v>
+        <v>550074</v>
       </c>
       <c r="R87" t="n">
-        <v>6942530</v>
+        <v>6942641</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9473,49 +9467,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126052873</v>
+        <v>126052154</v>
       </c>
       <c r="B88" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>549989</v>
+        <v>550021</v>
       </c>
       <c r="R88" t="n">
-        <v>6942554</v>
+        <v>6942450</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9548,6 +9538,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9577,7 +9572,7 @@
         <v>126057575</v>
       </c>
       <c r="B89" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9671,32 +9666,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126057556</v>
+        <v>126057531</v>
       </c>
       <c r="B90" t="n">
-        <v>80104</v>
+        <v>57656</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9706,10 +9701,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550074</v>
+        <v>549974</v>
       </c>
       <c r="R90" t="n">
-        <v>6942641</v>
+        <v>6942584</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9742,6 +9737,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9768,10 +9768,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126052154</v>
+        <v>126057535</v>
       </c>
       <c r="B91" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9779,21 +9779,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550021</v>
+        <v>550047</v>
       </c>
       <c r="R91" t="n">
-        <v>6942450</v>
+        <v>6942401</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9873,7 +9873,7 @@
         <v>126057540</v>
       </c>
       <c r="B92" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>126050713</v>
       </c>
       <c r="B93" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10074,32 +10074,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126057593</v>
+        <v>126057577</v>
       </c>
       <c r="B94" t="n">
-        <v>98345</v>
+        <v>78735</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10109,10 +10109,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550137</v>
+        <v>550101</v>
       </c>
       <c r="R94" t="n">
-        <v>6942555</v>
+        <v>6942551</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10145,11 +10145,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>3 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10176,45 +10171,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126057923</v>
+        <v>126057581</v>
       </c>
       <c r="B95" t="n">
-        <v>98345</v>
+        <v>78735</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>550122</v>
+        <v>550004</v>
       </c>
       <c r="R95" t="n">
-        <v>6942671</v>
+        <v>6942625</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10247,11 +10242,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10278,32 +10268,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126057577</v>
+        <v>126057593</v>
       </c>
       <c r="B96" t="n">
-        <v>78731</v>
+        <v>98349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10313,10 +10303,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>550101</v>
+        <v>550137</v>
       </c>
       <c r="R96" t="n">
-        <v>6942551</v>
+        <v>6942555</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10349,6 +10339,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10375,45 +10370,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126057581</v>
+        <v>126057923</v>
       </c>
       <c r="B97" t="n">
-        <v>78731</v>
+        <v>98349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>550004</v>
+        <v>550122</v>
       </c>
       <c r="R97" t="n">
-        <v>6942625</v>
+        <v>6942671</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10446,6 +10441,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -5074,32 +5074,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057896</v>
+        <v>126057930</v>
       </c>
       <c r="B44" t="n">
-        <v>80108</v>
+        <v>98349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550007</v>
+        <v>550112</v>
       </c>
       <c r="R44" t="n">
-        <v>6942646</v>
+        <v>6942664</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5145,6 +5145,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>50stycken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5171,45 +5176,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057568</v>
+        <v>126057896</v>
       </c>
       <c r="B45" t="n">
-        <v>80080</v>
+        <v>80108</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550093</v>
+        <v>550007</v>
       </c>
       <c r="R45" t="n">
-        <v>6942579</v>
+        <v>6942646</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5268,10 +5273,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126052735</v>
+        <v>126057568</v>
       </c>
       <c r="B46" t="n">
-        <v>78736</v>
+        <v>80080</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5279,21 +5284,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5303,13 +5308,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549975</v>
+        <v>550093</v>
       </c>
       <c r="R46" t="n">
-        <v>6942519</v>
+        <v>6942579</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5365,49 +5370,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126052332</v>
+        <v>126052735</v>
       </c>
       <c r="B47" t="n">
-        <v>98370</v>
+        <v>78736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>549984</v>
+        <v>549975</v>
       </c>
       <c r="R47" t="n">
-        <v>6942510</v>
+        <v>6942519</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5466,48 +5467,52 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057930</v>
+        <v>126052332</v>
       </c>
       <c r="B48" t="n">
-        <v>98349</v>
+        <v>98370</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550112</v>
+        <v>549984</v>
       </c>
       <c r="R48" t="n">
-        <v>6942664</v>
+        <v>6942510</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5537,11 +5542,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>50stycken</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5665,27 +5665,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126049249</v>
+        <v>126051408</v>
       </c>
       <c r="B50" t="n">
-        <v>58025</v>
+        <v>57653</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5693,14 +5693,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5709,10 +5705,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550135</v>
+        <v>550089</v>
       </c>
       <c r="R50" t="n">
-        <v>6942628</v>
+        <v>6942422</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5745,6 +5741,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5771,48 +5772,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126057602</v>
+        <v>126049249</v>
       </c>
       <c r="B51" t="n">
-        <v>98349</v>
+        <v>58025</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550099</v>
+        <v>550135</v>
       </c>
       <c r="R51" t="n">
-        <v>6942666</v>
+        <v>6942628</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5842,11 +5852,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5873,53 +5878,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126051408</v>
+        <v>126057602</v>
       </c>
       <c r="B52" t="n">
-        <v>57653</v>
+        <v>98349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550089</v>
+        <v>550099</v>
       </c>
       <c r="R52" t="n">
-        <v>6942422</v>
+        <v>6942666</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6271,10 +6271,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126057533</v>
+        <v>126057525</v>
       </c>
       <c r="B56" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6282,21 +6282,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6306,10 +6306,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550026</v>
+        <v>549977</v>
       </c>
       <c r="R56" t="n">
-        <v>6942422</v>
+        <v>6942580</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6342,11 +6342,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6373,10 +6368,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126057525</v>
+        <v>126057533</v>
       </c>
       <c r="B57" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6384,21 +6379,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6408,10 +6403,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>549977</v>
+        <v>550026</v>
       </c>
       <c r="R57" t="n">
-        <v>6942580</v>
+        <v>6942422</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6444,6 +6439,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6771,7 +6771,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126049594</v>
+        <v>126057601</v>
       </c>
       <c r="B61" t="n">
         <v>98349</v>
@@ -6799,24 +6799,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550141</v>
+        <v>550096</v>
       </c>
       <c r="R61" t="n">
-        <v>6942615</v>
+        <v>6942661</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6846,6 +6842,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6872,7 +6873,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126048239</v>
+        <v>126052934</v>
       </c>
       <c r="B62" t="n">
         <v>98349</v>
@@ -6902,7 +6903,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6911,10 +6912,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550147</v>
+        <v>549977</v>
       </c>
       <c r="R62" t="n">
-        <v>6942635</v>
+        <v>6942554</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6973,48 +6974,52 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126057601</v>
+        <v>126052802</v>
       </c>
       <c r="B63" t="n">
-        <v>98349</v>
+        <v>98370</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550096</v>
+        <v>549987</v>
       </c>
       <c r="R63" t="n">
-        <v>6942661</v>
+        <v>6942530</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7044,11 +7049,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7075,7 +7075,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126052934</v>
+        <v>126049594</v>
       </c>
       <c r="B64" t="n">
         <v>98349</v>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7114,10 +7114,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>549977</v>
+        <v>550141</v>
       </c>
       <c r="R64" t="n">
-        <v>6942554</v>
+        <v>6942615</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7176,37 +7176,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126052802</v>
+        <v>126048239</v>
       </c>
       <c r="B65" t="n">
-        <v>98370</v>
+        <v>98349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>549987</v>
+        <v>550147</v>
       </c>
       <c r="R65" t="n">
-        <v>6942530</v>
+        <v>6942635</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7980,32 +7980,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126057549</v>
+        <v>126049570</v>
       </c>
       <c r="B73" t="n">
-        <v>91696</v>
+        <v>78977</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>549978</v>
+        <v>550135</v>
       </c>
       <c r="R73" t="n">
-        <v>6942581</v>
+        <v>6942628</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8051,6 +8051,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8077,32 +8082,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126057578</v>
+        <v>126057549</v>
       </c>
       <c r="B74" t="n">
-        <v>78735</v>
+        <v>91696</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8112,10 +8117,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550086</v>
+        <v>549978</v>
       </c>
       <c r="R74" t="n">
-        <v>6942580</v>
+        <v>6942581</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8174,10 +8179,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126049570</v>
+        <v>126057578</v>
       </c>
       <c r="B75" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8185,21 +8190,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8209,13 +8214,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550135</v>
+        <v>550086</v>
       </c>
       <c r="R75" t="n">
-        <v>6942628</v>
+        <v>6942580</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8245,11 +8250,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8276,49 +8276,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126051602</v>
+        <v>126050913</v>
       </c>
       <c r="B76" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550089</v>
+        <v>550088</v>
       </c>
       <c r="R76" t="n">
-        <v>6942422</v>
+        <v>6942520</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8351,6 +8347,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8377,7 +8378,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126050913</v>
+        <v>126057606</v>
       </c>
       <c r="B77" t="n">
         <v>78977</v>
@@ -8412,13 +8413,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550088</v>
+        <v>550034</v>
       </c>
       <c r="R77" t="n">
-        <v>6942520</v>
+        <v>6942421</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8448,11 +8449,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8479,10 +8475,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126057606</v>
+        <v>126057904</v>
       </c>
       <c r="B78" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8490,34 +8486,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550034</v>
+        <v>549997</v>
       </c>
       <c r="R78" t="n">
-        <v>6942421</v>
+        <v>6942637</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8576,48 +8572,52 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126057904</v>
+        <v>126051602</v>
       </c>
       <c r="B79" t="n">
-        <v>80080</v>
+        <v>98349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>549997</v>
+        <v>550089</v>
       </c>
       <c r="R79" t="n">
-        <v>6942637</v>
+        <v>6942422</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8780,10 +8780,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126057524</v>
+        <v>126057559</v>
       </c>
       <c r="B81" t="n">
-        <v>91207</v>
+        <v>80108</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8791,21 +8791,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8815,10 +8815,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550079</v>
+        <v>550000</v>
       </c>
       <c r="R81" t="n">
-        <v>6942497</v>
+        <v>6942626</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8877,32 +8877,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126057559</v>
+        <v>126057574</v>
       </c>
       <c r="B82" t="n">
-        <v>80108</v>
+        <v>78735</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550000</v>
+        <v>549990</v>
       </c>
       <c r="R82" t="n">
-        <v>6942626</v>
+        <v>6942590</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8974,32 +8974,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126057574</v>
+        <v>126057524</v>
       </c>
       <c r="B83" t="n">
-        <v>78735</v>
+        <v>91207</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9009,10 +9009,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>549990</v>
+        <v>550079</v>
       </c>
       <c r="R83" t="n">
-        <v>6942590</v>
+        <v>6942497</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9972,10 +9972,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126050713</v>
+        <v>126057577</v>
       </c>
       <c r="B93" t="n">
-        <v>56839</v>
+        <v>78735</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9983,42 +9983,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550120</v>
+        <v>550101</v>
       </c>
       <c r="R93" t="n">
-        <v>6942506</v>
+        <v>6942551</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10074,7 +10069,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126057577</v>
+        <v>126057581</v>
       </c>
       <c r="B94" t="n">
         <v>78735</v>
@@ -10109,10 +10104,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550101</v>
+        <v>550004</v>
       </c>
       <c r="R94" t="n">
-        <v>6942551</v>
+        <v>6942625</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10171,10 +10166,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126057581</v>
+        <v>126050713</v>
       </c>
       <c r="B95" t="n">
-        <v>78735</v>
+        <v>56839</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10182,37 +10177,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>550004</v>
+        <v>550120</v>
       </c>
       <c r="R95" t="n">
-        <v>6942625</v>
+        <v>6942506</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2183,32 +2183,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126057921</v>
+        <v>126057934</v>
       </c>
       <c r="B15" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550142</v>
+        <v>550127</v>
       </c>
       <c r="R15" t="n">
-        <v>6942582</v>
+        <v>6942669</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>30 stycken</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,32 +2285,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126057597</v>
+        <v>126057536</v>
       </c>
       <c r="B16" t="n">
-        <v>98349</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550099</v>
+        <v>550113</v>
       </c>
       <c r="R16" t="n">
-        <v>6942637</v>
+        <v>6942389</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,45 +2387,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126057564</v>
+        <v>126057921</v>
       </c>
       <c r="B17" t="n">
-        <v>78736</v>
+        <v>98352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550076</v>
+        <v>550142</v>
       </c>
       <c r="R17" t="n">
-        <v>6942390</v>
+        <v>6942582</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2458,6 +2458,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,45 +2489,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057934</v>
+        <v>126057597</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550127</v>
+        <v>550099</v>
       </c>
       <c r="R18" t="n">
-        <v>6942669</v>
+        <v>6942637</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2559,7 +2564,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057536</v>
+        <v>126057564</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>78736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2597,21 +2602,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2621,10 +2626,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550113</v>
+        <v>550076</v>
       </c>
       <c r="R19" t="n">
-        <v>6942389</v>
+        <v>6942390</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2657,11 +2662,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,32 +2785,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057582</v>
+        <v>126057526</v>
       </c>
       <c r="B21" t="n">
-        <v>98349</v>
+        <v>91242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550023</v>
+        <v>550079</v>
       </c>
       <c r="R21" t="n">
-        <v>6942583</v>
+        <v>6942497</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2856,11 +2856,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>61 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,32 +2979,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057526</v>
+        <v>126057582</v>
       </c>
       <c r="B23" t="n">
-        <v>91242</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3019,10 +3014,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550079</v>
+        <v>550023</v>
       </c>
       <c r="R23" t="n">
-        <v>6942497</v>
+        <v>6942583</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3055,6 +3050,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>61 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,32 +3081,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126057545</v>
+        <v>126052983</v>
       </c>
       <c r="B24" t="n">
-        <v>91253</v>
+        <v>78735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1205</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3116,13 +3116,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550011</v>
+        <v>549977</v>
       </c>
       <c r="R24" t="n">
-        <v>6942535</v>
+        <v>6942554</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3275,32 +3275,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126052983</v>
+        <v>126057544</v>
       </c>
       <c r="B26" t="n">
-        <v>78735</v>
+        <v>80109</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3310,13 +3310,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549977</v>
+        <v>550094</v>
       </c>
       <c r="R26" t="n">
-        <v>6942554</v>
+        <v>6942584</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3571,10 +3571,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057544</v>
+        <v>126057545</v>
       </c>
       <c r="B29" t="n">
-        <v>80109</v>
+        <v>91253</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3582,21 +3582,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550094</v>
+        <v>550011</v>
       </c>
       <c r="R29" t="n">
-        <v>6942584</v>
+        <v>6942535</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3773,7 +3773,7 @@
         <v>126051074</v>
       </c>
       <c r="B31" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,10 +3871,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057579</v>
+        <v>126057538</v>
       </c>
       <c r="B32" t="n">
-        <v>78735</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3882,21 +3882,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550006</v>
+        <v>550041</v>
       </c>
       <c r="R32" t="n">
-        <v>6942636</v>
+        <v>6942496</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3942,6 +3942,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3968,10 +3973,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057567</v>
+        <v>126057937</v>
       </c>
       <c r="B33" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3979,34 +3984,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550001</v>
+        <v>550147</v>
       </c>
       <c r="R33" t="n">
-        <v>6942503</v>
+        <v>6942582</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4039,6 +4044,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4065,10 +4075,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126053984</v>
+        <v>126057579</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4076,21 +4086,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4100,13 +4110,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549984</v>
+        <v>550006</v>
       </c>
       <c r="R34" t="n">
-        <v>6942510</v>
+        <v>6942636</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4136,11 +4146,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4167,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057538</v>
+        <v>126053984</v>
       </c>
       <c r="B35" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4178,21 +4183,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4202,13 +4207,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550041</v>
+        <v>549984</v>
       </c>
       <c r="R35" t="n">
-        <v>6942496</v>
+        <v>6942510</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4242,7 +4247,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4269,10 +4274,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057937</v>
+        <v>126057567</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4280,34 +4285,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550147</v>
+        <v>550001</v>
       </c>
       <c r="R36" t="n">
-        <v>6942582</v>
+        <v>6942503</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4340,11 +4345,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4374,7 +4374,7 @@
         <v>126057596</v>
       </c>
       <c r="B37" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>126057591</v>
       </c>
       <c r="B38" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4575,32 +4575,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126052912</v>
+        <v>126057569</v>
       </c>
       <c r="B39" t="n">
-        <v>80108</v>
+        <v>80080</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549977</v>
+        <v>550006</v>
       </c>
       <c r="R39" t="n">
-        <v>6942554</v>
+        <v>6942630</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4672,32 +4672,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057569</v>
+        <v>126052912</v>
       </c>
       <c r="B40" t="n">
-        <v>80080</v>
+        <v>80108</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4707,13 +4707,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550006</v>
+        <v>549977</v>
       </c>
       <c r="R40" t="n">
-        <v>6942630</v>
+        <v>6942554</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>126057592</v>
       </c>
       <c r="B41" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>126052420</v>
       </c>
       <c r="B42" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>126057600</v>
       </c>
       <c r="B43" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5074,48 +5074,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057930</v>
+        <v>126052735</v>
       </c>
       <c r="B44" t="n">
-        <v>98349</v>
+        <v>78736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550112</v>
+        <v>549975</v>
       </c>
       <c r="R44" t="n">
-        <v>6942664</v>
+        <v>6942519</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5145,11 +5145,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>50stycken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5176,45 +5171,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057896</v>
+        <v>126057568</v>
       </c>
       <c r="B45" t="n">
-        <v>80108</v>
+        <v>80080</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550007</v>
+        <v>550093</v>
       </c>
       <c r="R45" t="n">
-        <v>6942646</v>
+        <v>6942579</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5273,45 +5268,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057568</v>
+        <v>126057896</v>
       </c>
       <c r="B46" t="n">
-        <v>80080</v>
+        <v>80108</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550093</v>
+        <v>550007</v>
       </c>
       <c r="R46" t="n">
-        <v>6942579</v>
+        <v>6942646</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5370,48 +5365,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126052735</v>
+        <v>126057930</v>
       </c>
       <c r="B47" t="n">
-        <v>78736</v>
+        <v>98352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>549975</v>
+        <v>550112</v>
       </c>
       <c r="R47" t="n">
-        <v>6942519</v>
+        <v>6942664</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5441,6 +5436,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>50stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5470,7 +5470,7 @@
         <v>126052332</v>
       </c>
       <c r="B48" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5568,10 +5568,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126051690</v>
+        <v>126049249</v>
       </c>
       <c r="B49" t="n">
-        <v>80108</v>
+        <v>58025</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5579,34 +5579,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550110</v>
+        <v>550135</v>
       </c>
       <c r="R49" t="n">
-        <v>6942386</v>
+        <v>6942628</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5665,50 +5674,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126051408</v>
+        <v>126051690</v>
       </c>
       <c r="B50" t="n">
-        <v>57653</v>
+        <v>80108</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550089</v>
+        <v>550110</v>
       </c>
       <c r="R50" t="n">
-        <v>6942422</v>
+        <v>6942386</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5741,11 +5745,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5772,27 +5771,27 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126049249</v>
+        <v>126051408</v>
       </c>
       <c r="B51" t="n">
-        <v>58025</v>
+        <v>57653</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5800,14 +5799,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5816,10 +5811,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550135</v>
+        <v>550089</v>
       </c>
       <c r="R51" t="n">
-        <v>6942628</v>
+        <v>6942422</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5852,6 +5847,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5881,7 +5881,7 @@
         <v>126057602</v>
       </c>
       <c r="B52" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5980,32 +5980,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057915</v>
+        <v>126057898</v>
       </c>
       <c r="B53" t="n">
-        <v>78735</v>
+        <v>80108</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550145</v>
+        <v>549997</v>
       </c>
       <c r="R53" t="n">
-        <v>6942577</v>
+        <v>6942637</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6077,32 +6077,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057898</v>
+        <v>126057915</v>
       </c>
       <c r="B54" t="n">
-        <v>80108</v>
+        <v>78735</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>549997</v>
+        <v>550145</v>
       </c>
       <c r="R54" t="n">
-        <v>6942637</v>
+        <v>6942577</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6368,48 +6368,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126057533</v>
+        <v>126050777</v>
       </c>
       <c r="B57" t="n">
-        <v>57656</v>
+        <v>56848</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550026</v>
+        <v>550093</v>
       </c>
       <c r="R57" t="n">
-        <v>6942422</v>
+        <v>6942497</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6439,11 +6444,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6470,53 +6470,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126050777</v>
+        <v>126057533</v>
       </c>
       <c r="B58" t="n">
-        <v>56848</v>
+        <v>57656</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550093</v>
+        <v>550026</v>
       </c>
       <c r="R58" t="n">
-        <v>6942497</v>
+        <v>6942422</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6546,6 +6541,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6572,48 +6572,52 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126057576</v>
+        <v>126048239</v>
       </c>
       <c r="B59" t="n">
-        <v>78735</v>
+        <v>98352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550078</v>
+        <v>550147</v>
       </c>
       <c r="R59" t="n">
-        <v>6942401</v>
+        <v>6942635</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6669,38 +6673,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126051839</v>
+        <v>126049594</v>
       </c>
       <c r="B60" t="n">
-        <v>56848</v>
+        <v>98352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6709,10 +6712,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550088</v>
+        <v>550141</v>
       </c>
       <c r="R60" t="n">
-        <v>6942377</v>
+        <v>6942615</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6771,48 +6774,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126057601</v>
+        <v>126051839</v>
       </c>
       <c r="B61" t="n">
-        <v>98349</v>
+        <v>56848</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550096</v>
+        <v>550088</v>
       </c>
       <c r="R61" t="n">
-        <v>6942661</v>
+        <v>6942377</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6842,11 +6850,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6873,52 +6876,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126052934</v>
+        <v>126057576</v>
       </c>
       <c r="B62" t="n">
-        <v>98349</v>
+        <v>78735</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>549977</v>
+        <v>550078</v>
       </c>
       <c r="R62" t="n">
-        <v>6942554</v>
+        <v>6942401</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6974,52 +6973,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126052802</v>
+        <v>126057601</v>
       </c>
       <c r="B63" t="n">
-        <v>98370</v>
+        <v>98352</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>549987</v>
+        <v>550096</v>
       </c>
       <c r="R63" t="n">
-        <v>6942530</v>
+        <v>6942661</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7049,6 +7044,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7075,10 +7075,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126049594</v>
+        <v>126052934</v>
       </c>
       <c r="B64" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7114,10 +7114,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550141</v>
+        <v>549977</v>
       </c>
       <c r="R64" t="n">
-        <v>6942615</v>
+        <v>6942554</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7176,37 +7176,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126048239</v>
+        <v>126052802</v>
       </c>
       <c r="B65" t="n">
-        <v>98349</v>
+        <v>98373</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550147</v>
+        <v>549987</v>
       </c>
       <c r="R65" t="n">
-        <v>6942635</v>
+        <v>6942530</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7280,7 +7280,7 @@
         <v>126057594</v>
       </c>
       <c r="B66" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>126051197</v>
       </c>
       <c r="B67" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>126051507</v>
       </c>
       <c r="B68" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7679,32 +7679,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126053048</v>
+        <v>126057583</v>
       </c>
       <c r="B70" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7714,13 +7714,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>549965</v>
+        <v>550098</v>
       </c>
       <c r="R70" t="n">
-        <v>6942583</v>
+        <v>6942641</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav I området</t>
+          <t>31 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7781,32 +7781,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126051112</v>
+        <v>126053048</v>
       </c>
       <c r="B71" t="n">
-        <v>80108</v>
+        <v>78977</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7816,10 +7816,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550093</v>
+        <v>549965</v>
       </c>
       <c r="R71" t="n">
-        <v>6942497</v>
+        <v>6942583</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7852,6 +7852,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I området</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7878,32 +7883,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126057583</v>
+        <v>126051112</v>
       </c>
       <c r="B72" t="n">
-        <v>98349</v>
+        <v>80108</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7913,13 +7918,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550098</v>
+        <v>550093</v>
       </c>
       <c r="R72" t="n">
-        <v>6942641</v>
+        <v>6942497</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7949,11 +7954,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>31 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126049570</v>
+        <v>126057549</v>
       </c>
       <c r="B73" t="n">
-        <v>78977</v>
+        <v>91696</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550135</v>
+        <v>549978</v>
       </c>
       <c r="R73" t="n">
-        <v>6942628</v>
+        <v>6942581</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8051,11 +8051,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8082,32 +8077,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126057549</v>
+        <v>126057578</v>
       </c>
       <c r="B74" t="n">
-        <v>91696</v>
+        <v>78735</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8117,10 +8112,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>549978</v>
+        <v>550086</v>
       </c>
       <c r="R74" t="n">
-        <v>6942581</v>
+        <v>6942580</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8179,10 +8174,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126057578</v>
+        <v>126049570</v>
       </c>
       <c r="B75" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8190,21 +8185,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8214,13 +8209,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550086</v>
+        <v>550135</v>
       </c>
       <c r="R75" t="n">
-        <v>6942580</v>
+        <v>6942628</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8250,6 +8245,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8276,7 +8276,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126050913</v>
+        <v>126057606</v>
       </c>
       <c r="B76" t="n">
         <v>78977</v>
@@ -8311,13 +8311,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550088</v>
+        <v>550034</v>
       </c>
       <c r="R76" t="n">
-        <v>6942520</v>
+        <v>6942421</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8347,11 +8347,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8378,10 +8373,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126057606</v>
+        <v>126057904</v>
       </c>
       <c r="B77" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8389,34 +8384,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550034</v>
+        <v>549997</v>
       </c>
       <c r="R77" t="n">
-        <v>6942421</v>
+        <v>6942637</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8475,10 +8470,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126057904</v>
+        <v>126050913</v>
       </c>
       <c r="B78" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8486,37 +8481,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>549997</v>
+        <v>550088</v>
       </c>
       <c r="R78" t="n">
-        <v>6942637</v>
+        <v>6942520</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8546,6 +8541,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8575,7 +8575,7 @@
         <v>126051602</v>
       </c>
       <c r="B79" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8780,32 +8780,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126057559</v>
+        <v>126057574</v>
       </c>
       <c r="B81" t="n">
-        <v>80108</v>
+        <v>78735</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8815,10 +8815,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550000</v>
+        <v>549990</v>
       </c>
       <c r="R81" t="n">
-        <v>6942626</v>
+        <v>6942590</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8877,32 +8877,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126057574</v>
+        <v>126057559</v>
       </c>
       <c r="B82" t="n">
-        <v>78735</v>
+        <v>80108</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8912,10 +8912,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>549990</v>
+        <v>550000</v>
       </c>
       <c r="R82" t="n">
-        <v>6942590</v>
+        <v>6942626</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9074,7 +9074,7 @@
         <v>126051270</v>
       </c>
       <c r="B84" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9172,52 +9172,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126052873</v>
+        <v>126057556</v>
       </c>
       <c r="B85" t="n">
-        <v>98349</v>
+        <v>80108</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>549989</v>
+        <v>550074</v>
       </c>
       <c r="R85" t="n">
-        <v>6942554</v>
+        <v>6942641</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9273,32 +9269,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126052827</v>
+        <v>126052154</v>
       </c>
       <c r="B86" t="n">
-        <v>97227</v>
+        <v>78977</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9308,10 +9304,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>549987</v>
+        <v>550021</v>
       </c>
       <c r="R86" t="n">
-        <v>6942530</v>
+        <v>6942450</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9344,6 +9340,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9370,32 +9371,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126057556</v>
+        <v>126057575</v>
       </c>
       <c r="B87" t="n">
-        <v>80108</v>
+        <v>78735</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9405,10 +9406,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550074</v>
+        <v>550022</v>
       </c>
       <c r="R87" t="n">
-        <v>6942641</v>
+        <v>6942537</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9467,10 +9468,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126052154</v>
+        <v>126057531</v>
       </c>
       <c r="B88" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9478,21 +9479,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9502,13 +9503,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550021</v>
+        <v>549974</v>
       </c>
       <c r="R88" t="n">
-        <v>6942450</v>
+        <v>6942584</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9542,7 +9543,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9569,10 +9570,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126057575</v>
+        <v>126057535</v>
       </c>
       <c r="B89" t="n">
-        <v>78735</v>
+        <v>57656</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9580,21 +9581,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9604,10 +9605,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550022</v>
+        <v>550047</v>
       </c>
       <c r="R89" t="n">
-        <v>6942537</v>
+        <v>6942401</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9640,6 +9641,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9666,48 +9672,52 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126057531</v>
+        <v>126052873</v>
       </c>
       <c r="B90" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>549974</v>
+        <v>549989</v>
       </c>
       <c r="R90" t="n">
-        <v>6942584</v>
+        <v>6942554</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9737,11 +9747,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9768,32 +9773,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126057535</v>
+        <v>126052827</v>
       </c>
       <c r="B91" t="n">
-        <v>57656</v>
+        <v>97230</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9803,13 +9808,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550047</v>
+        <v>549987</v>
       </c>
       <c r="R91" t="n">
-        <v>6942401</v>
+        <v>6942530</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9839,11 +9844,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9870,10 +9870,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126057540</v>
+        <v>126057577</v>
       </c>
       <c r="B92" t="n">
-        <v>57656</v>
+        <v>78735</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9881,21 +9881,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9905,10 +9905,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550138</v>
+        <v>550101</v>
       </c>
       <c r="R92" t="n">
-        <v>6942638</v>
+        <v>6942551</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -9941,11 +9941,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9972,7 +9967,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126057577</v>
+        <v>126057581</v>
       </c>
       <c r="B93" t="n">
         <v>78735</v>
@@ -10007,10 +10002,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550101</v>
+        <v>550004</v>
       </c>
       <c r="R93" t="n">
-        <v>6942551</v>
+        <v>6942625</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10069,32 +10064,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126057581</v>
+        <v>126057593</v>
       </c>
       <c r="B94" t="n">
-        <v>78735</v>
+        <v>98352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10104,10 +10099,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550004</v>
+        <v>550137</v>
       </c>
       <c r="R94" t="n">
-        <v>6942625</v>
+        <v>6942555</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10140,6 +10135,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10166,53 +10166,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126050713</v>
+        <v>126057923</v>
       </c>
       <c r="B95" t="n">
-        <v>56839</v>
+        <v>98352</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>550120</v>
+        <v>550122</v>
       </c>
       <c r="R95" t="n">
-        <v>6942506</v>
+        <v>6942671</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10242,6 +10237,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10268,32 +10268,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126057593</v>
+        <v>126057540</v>
       </c>
       <c r="B96" t="n">
-        <v>98349</v>
+        <v>57656</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10303,10 +10303,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>550137</v>
+        <v>550138</v>
       </c>
       <c r="R96" t="n">
-        <v>6942555</v>
+        <v>6942638</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10370,48 +10370,53 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126057923</v>
+        <v>126050713</v>
       </c>
       <c r="B97" t="n">
-        <v>98349</v>
+        <v>56839</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>550122</v>
+        <v>550120</v>
       </c>
       <c r="R97" t="n">
-        <v>6942671</v>
+        <v>6942506</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10441,11 +10446,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057526</v>
+        <v>126057935</v>
       </c>
       <c r="B21" t="n">
-        <v>91242</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,34 +2796,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550079</v>
+        <v>550099</v>
       </c>
       <c r="R21" t="n">
-        <v>6942497</v>
+        <v>6942670</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057935</v>
+        <v>126057526</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>91242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,34 +2893,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550099</v>
+        <v>550079</v>
       </c>
       <c r="R22" t="n">
-        <v>6942670</v>
+        <v>6942497</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3871,10 +3871,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057538</v>
+        <v>126057937</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3882,34 +3882,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550041</v>
+        <v>550147</v>
       </c>
       <c r="R32" t="n">
-        <v>6942496</v>
+        <v>6942582</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3973,10 +3973,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057937</v>
+        <v>126057579</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3984,34 +3984,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550147</v>
+        <v>550006</v>
       </c>
       <c r="R33" t="n">
-        <v>6942582</v>
+        <v>6942636</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4044,11 +4044,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4075,10 +4070,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057579</v>
+        <v>126053984</v>
       </c>
       <c r="B34" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4086,21 +4081,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4110,13 +4105,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550006</v>
+        <v>549984</v>
       </c>
       <c r="R34" t="n">
-        <v>6942636</v>
+        <v>6942510</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4146,6 +4141,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126053984</v>
+        <v>126057567</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,21 +4183,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549984</v>
+        <v>550001</v>
       </c>
       <c r="R35" t="n">
-        <v>6942510</v>
+        <v>6942503</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4243,11 +4243,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4274,10 +4269,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057567</v>
+        <v>126057538</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>57656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4285,21 +4280,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4309,10 +4304,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550001</v>
+        <v>550041</v>
       </c>
       <c r="R36" t="n">
-        <v>6942503</v>
+        <v>6942496</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4345,6 +4340,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5771,53 +5771,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126051408</v>
+        <v>126057602</v>
       </c>
       <c r="B51" t="n">
-        <v>57653</v>
+        <v>98352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550089</v>
+        <v>550099</v>
       </c>
       <c r="R51" t="n">
-        <v>6942422</v>
+        <v>6942666</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5851,7 +5846,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5878,48 +5873,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126057602</v>
+        <v>126051408</v>
       </c>
       <c r="B52" t="n">
-        <v>98352</v>
+        <v>57653</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550099</v>
+        <v>550089</v>
       </c>
       <c r="R52" t="n">
-        <v>6942666</v>
+        <v>6942422</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2387,45 +2387,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126057921</v>
+        <v>126057564</v>
       </c>
       <c r="B17" t="n">
-        <v>98352</v>
+        <v>78736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550142</v>
+        <v>550076</v>
       </c>
       <c r="R17" t="n">
-        <v>6942582</v>
+        <v>6942390</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2458,11 +2458,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,7 +2484,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057597</v>
+        <v>126057921</v>
       </c>
       <c r="B18" t="n">
         <v>98352</v>
@@ -2520,14 +2515,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550099</v>
+        <v>550142</v>
       </c>
       <c r="R18" t="n">
-        <v>6942637</v>
+        <v>6942582</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2564,7 +2559,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,32 +2586,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057564</v>
+        <v>126057597</v>
       </c>
       <c r="B19" t="n">
-        <v>78736</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550076</v>
+        <v>550099</v>
       </c>
       <c r="R19" t="n">
-        <v>6942390</v>
+        <v>6942637</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2662,6 +2657,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3081,10 +3081,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126052983</v>
+        <v>126057532</v>
       </c>
       <c r="B24" t="n">
-        <v>78735</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3092,21 +3092,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3116,13 +3116,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549977</v>
+        <v>550020</v>
       </c>
       <c r="R24" t="n">
-        <v>6942554</v>
+        <v>6942390</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,6 +3152,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,32 +3280,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126057544</v>
+        <v>126052983</v>
       </c>
       <c r="B26" t="n">
-        <v>80109</v>
+        <v>78735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3310,13 +3315,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550094</v>
+        <v>549977</v>
       </c>
       <c r="R26" t="n">
-        <v>6942584</v>
+        <v>6942554</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3571,10 +3576,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057545</v>
+        <v>126057544</v>
       </c>
       <c r="B29" t="n">
-        <v>91253</v>
+        <v>80109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3582,21 +3587,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3606,10 +3611,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550011</v>
+        <v>550094</v>
       </c>
       <c r="R29" t="n">
-        <v>6942535</v>
+        <v>6942584</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3668,32 +3673,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057532</v>
+        <v>126057545</v>
       </c>
       <c r="B30" t="n">
-        <v>57656</v>
+        <v>91253</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3703,10 +3708,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550020</v>
+        <v>550011</v>
       </c>
       <c r="R30" t="n">
-        <v>6942390</v>
+        <v>6942535</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3739,11 +3744,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3871,10 +3871,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057937</v>
+        <v>126057579</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3882,34 +3882,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550147</v>
+        <v>550006</v>
       </c>
       <c r="R32" t="n">
-        <v>6942582</v>
+        <v>6942636</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3942,11 +3942,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3973,10 +3968,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057579</v>
+        <v>126057937</v>
       </c>
       <c r="B33" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3984,34 +3979,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550006</v>
+        <v>550147</v>
       </c>
       <c r="R33" t="n">
-        <v>6942636</v>
+        <v>6942582</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4044,6 +4039,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4070,10 +4070,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126053984</v>
+        <v>126057567</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4105,13 +4105,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549984</v>
+        <v>550001</v>
       </c>
       <c r="R34" t="n">
-        <v>6942510</v>
+        <v>6942503</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4141,11 +4141,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4172,10 +4167,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057567</v>
+        <v>126053984</v>
       </c>
       <c r="B35" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,21 +4178,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4207,13 +4202,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550001</v>
+        <v>549984</v>
       </c>
       <c r="R35" t="n">
-        <v>6942503</v>
+        <v>6942510</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4243,6 +4238,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4269,32 +4269,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057538</v>
+        <v>126057596</v>
       </c>
       <c r="B36" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550041</v>
+        <v>550092</v>
       </c>
       <c r="R36" t="n">
-        <v>6942496</v>
+        <v>6942597</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4371,7 +4371,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057596</v>
+        <v>126057591</v>
       </c>
       <c r="B37" t="n">
         <v>98352</v>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550092</v>
+        <v>550020</v>
       </c>
       <c r="R37" t="n">
-        <v>6942597</v>
+        <v>6942543</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4473,32 +4473,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057591</v>
+        <v>126057538</v>
       </c>
       <c r="B38" t="n">
-        <v>98352</v>
+        <v>57656</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550020</v>
+        <v>550041</v>
       </c>
       <c r="R38" t="n">
-        <v>6942543</v>
+        <v>6942496</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4575,32 +4575,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057569</v>
+        <v>126052912</v>
       </c>
       <c r="B39" t="n">
-        <v>80080</v>
+        <v>80108</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550006</v>
+        <v>549977</v>
       </c>
       <c r="R39" t="n">
-        <v>6942630</v>
+        <v>6942554</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4672,32 +4672,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126052912</v>
+        <v>126057569</v>
       </c>
       <c r="B40" t="n">
-        <v>80108</v>
+        <v>80080</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4707,13 +4707,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549977</v>
+        <v>550006</v>
       </c>
       <c r="R40" t="n">
-        <v>6942554</v>
+        <v>6942630</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5074,48 +5074,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126052735</v>
+        <v>126057896</v>
       </c>
       <c r="B44" t="n">
-        <v>78736</v>
+        <v>80108</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549975</v>
+        <v>550007</v>
       </c>
       <c r="R44" t="n">
-        <v>6942519</v>
+        <v>6942646</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5268,48 +5268,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057896</v>
+        <v>126052735</v>
       </c>
       <c r="B46" t="n">
-        <v>80108</v>
+        <v>78736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550007</v>
+        <v>549975</v>
       </c>
       <c r="R46" t="n">
-        <v>6942646</v>
+        <v>6942519</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5568,10 +5568,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126049249</v>
+        <v>126051690</v>
       </c>
       <c r="B49" t="n">
-        <v>58025</v>
+        <v>80108</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5579,43 +5579,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>6461</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550135</v>
+        <v>550110</v>
       </c>
       <c r="R49" t="n">
-        <v>6942628</v>
+        <v>6942386</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5674,10 +5665,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126051690</v>
+        <v>126049249</v>
       </c>
       <c r="B50" t="n">
-        <v>80108</v>
+        <v>58025</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5685,34 +5676,43 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550110</v>
+        <v>550135</v>
       </c>
       <c r="R50" t="n">
-        <v>6942386</v>
+        <v>6942628</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5771,48 +5771,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126057602</v>
+        <v>126051408</v>
       </c>
       <c r="B51" t="n">
-        <v>98352</v>
+        <v>57653</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550099</v>
+        <v>550089</v>
       </c>
       <c r="R51" t="n">
-        <v>6942666</v>
+        <v>6942422</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5846,7 +5851,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5873,53 +5878,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126051408</v>
+        <v>126057602</v>
       </c>
       <c r="B52" t="n">
-        <v>57653</v>
+        <v>98352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550089</v>
+        <v>550099</v>
       </c>
       <c r="R52" t="n">
-        <v>6942422</v>
+        <v>6942666</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5980,32 +5980,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057898</v>
+        <v>126057915</v>
       </c>
       <c r="B53" t="n">
-        <v>80108</v>
+        <v>78735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>549997</v>
+        <v>550145</v>
       </c>
       <c r="R53" t="n">
-        <v>6942637</v>
+        <v>6942577</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6077,32 +6077,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057915</v>
+        <v>126057898</v>
       </c>
       <c r="B54" t="n">
-        <v>78735</v>
+        <v>80108</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550145</v>
+        <v>549997</v>
       </c>
       <c r="R54" t="n">
-        <v>6942577</v>
+        <v>6942637</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6368,53 +6368,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126050777</v>
+        <v>126057533</v>
       </c>
       <c r="B57" t="n">
-        <v>56848</v>
+        <v>57656</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550093</v>
+        <v>550026</v>
       </c>
       <c r="R57" t="n">
-        <v>6942497</v>
+        <v>6942422</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6444,6 +6439,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6470,48 +6470,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126057533</v>
+        <v>126050777</v>
       </c>
       <c r="B58" t="n">
-        <v>57656</v>
+        <v>56848</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550026</v>
+        <v>550093</v>
       </c>
       <c r="R58" t="n">
-        <v>6942422</v>
+        <v>6942497</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6541,11 +6546,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6572,37 +6572,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126048239</v>
+        <v>126051839</v>
       </c>
       <c r="B59" t="n">
-        <v>98352</v>
+        <v>56848</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>56</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6611,10 +6612,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550147</v>
+        <v>550088</v>
       </c>
       <c r="R59" t="n">
-        <v>6942635</v>
+        <v>6942377</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6673,7 +6674,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126049594</v>
+        <v>126048239</v>
       </c>
       <c r="B60" t="n">
         <v>98352</v>
@@ -6703,7 +6704,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6712,10 +6713,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550141</v>
+        <v>550147</v>
       </c>
       <c r="R60" t="n">
-        <v>6942615</v>
+        <v>6942635</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6774,38 +6775,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126051839</v>
+        <v>126049594</v>
       </c>
       <c r="B61" t="n">
-        <v>56848</v>
+        <v>98352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550088</v>
+        <v>550141</v>
       </c>
       <c r="R61" t="n">
-        <v>6942377</v>
+        <v>6942615</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7781,32 +7781,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126053048</v>
+        <v>126051112</v>
       </c>
       <c r="B71" t="n">
-        <v>78977</v>
+        <v>80108</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7816,10 +7816,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>549965</v>
+        <v>550093</v>
       </c>
       <c r="R71" t="n">
-        <v>6942583</v>
+        <v>6942497</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7852,11 +7852,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav I området</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7883,32 +7878,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126051112</v>
+        <v>126053048</v>
       </c>
       <c r="B72" t="n">
-        <v>80108</v>
+        <v>78977</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7918,10 +7913,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550093</v>
+        <v>549965</v>
       </c>
       <c r="R72" t="n">
-        <v>6942497</v>
+        <v>6942583</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7954,6 +7949,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I området</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126057549</v>
+        <v>126049570</v>
       </c>
       <c r="B73" t="n">
-        <v>91696</v>
+        <v>78977</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>549978</v>
+        <v>550135</v>
       </c>
       <c r="R73" t="n">
-        <v>6942581</v>
+        <v>6942628</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8051,6 +8051,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8077,32 +8082,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126057578</v>
+        <v>126057549</v>
       </c>
       <c r="B74" t="n">
-        <v>78735</v>
+        <v>91696</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8112,10 +8117,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550086</v>
+        <v>549978</v>
       </c>
       <c r="R74" t="n">
-        <v>6942580</v>
+        <v>6942581</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8174,10 +8179,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126049570</v>
+        <v>126057578</v>
       </c>
       <c r="B75" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8185,21 +8190,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8209,13 +8214,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550135</v>
+        <v>550086</v>
       </c>
       <c r="R75" t="n">
-        <v>6942628</v>
+        <v>6942580</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8245,11 +8250,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8276,48 +8276,52 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126057606</v>
+        <v>126051602</v>
       </c>
       <c r="B76" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550034</v>
+        <v>550089</v>
       </c>
       <c r="R76" t="n">
-        <v>6942421</v>
+        <v>6942422</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8373,10 +8377,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126057904</v>
+        <v>126057606</v>
       </c>
       <c r="B77" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8384,34 +8388,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>549997</v>
+        <v>550034</v>
       </c>
       <c r="R77" t="n">
-        <v>6942637</v>
+        <v>6942421</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8470,10 +8474,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126050913</v>
+        <v>126057904</v>
       </c>
       <c r="B78" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8481,37 +8485,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550088</v>
+        <v>549997</v>
       </c>
       <c r="R78" t="n">
-        <v>6942520</v>
+        <v>6942637</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8541,11 +8545,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8572,49 +8571,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126051602</v>
+        <v>126050913</v>
       </c>
       <c r="B79" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550089</v>
+        <v>550088</v>
       </c>
       <c r="R79" t="n">
-        <v>6942422</v>
+        <v>6942520</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8647,6 +8642,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8673,10 +8673,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126047488</v>
+        <v>126057559</v>
       </c>
       <c r="B80" t="n">
-        <v>43934</v>
+        <v>80108</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8684,42 +8684,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>101735</v>
+        <v>6461</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550158</v>
+        <v>550000</v>
       </c>
       <c r="R80" t="n">
-        <v>6942653</v>
+        <v>6942626</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8749,11 +8744,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8877,10 +8867,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126057559</v>
+        <v>126057524</v>
       </c>
       <c r="B82" t="n">
-        <v>80108</v>
+        <v>91207</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8888,21 +8878,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8912,10 +8902,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550000</v>
+        <v>550079</v>
       </c>
       <c r="R82" t="n">
-        <v>6942626</v>
+        <v>6942497</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8974,48 +8964,52 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126057524</v>
+        <v>126051270</v>
       </c>
       <c r="B83" t="n">
-        <v>91207</v>
+        <v>98352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550079</v>
+        <v>550065</v>
       </c>
       <c r="R83" t="n">
-        <v>6942497</v>
+        <v>6942463</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9071,37 +9065,38 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126051270</v>
+        <v>126047488</v>
       </c>
       <c r="B84" t="n">
-        <v>98352</v>
+        <v>43934</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>43</t>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9110,13 +9105,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550065</v>
+        <v>550158</v>
       </c>
       <c r="R84" t="n">
-        <v>6942463</v>
+        <v>6942653</v>
       </c>
       <c r="S84" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9146,6 +9141,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9172,48 +9172,52 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126057556</v>
+        <v>126052873</v>
       </c>
       <c r="B85" t="n">
-        <v>80108</v>
+        <v>98352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550074</v>
+        <v>549989</v>
       </c>
       <c r="R85" t="n">
-        <v>6942641</v>
+        <v>6942554</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9269,10 +9273,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126052154</v>
+        <v>126057531</v>
       </c>
       <c r="B86" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9280,21 +9284,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9304,13 +9308,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550021</v>
+        <v>549974</v>
       </c>
       <c r="R86" t="n">
-        <v>6942450</v>
+        <v>6942584</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9344,7 +9348,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9371,10 +9375,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126057575</v>
+        <v>126057535</v>
       </c>
       <c r="B87" t="n">
-        <v>78735</v>
+        <v>57656</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9382,21 +9386,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9406,10 +9410,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550022</v>
+        <v>550047</v>
       </c>
       <c r="R87" t="n">
-        <v>6942537</v>
+        <v>6942401</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9442,6 +9446,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9468,10 +9477,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126057531</v>
+        <v>126057575</v>
       </c>
       <c r="B88" t="n">
-        <v>57656</v>
+        <v>78735</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9479,21 +9488,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9503,10 +9512,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>549974</v>
+        <v>550022</v>
       </c>
       <c r="R88" t="n">
-        <v>6942584</v>
+        <v>6942537</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9539,11 +9548,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9570,32 +9574,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126057535</v>
+        <v>126057556</v>
       </c>
       <c r="B89" t="n">
-        <v>57656</v>
+        <v>80108</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9605,10 +9609,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550047</v>
+        <v>550074</v>
       </c>
       <c r="R89" t="n">
-        <v>6942401</v>
+        <v>6942641</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9641,11 +9645,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9672,49 +9671,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126052873</v>
+        <v>126052154</v>
       </c>
       <c r="B90" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>549989</v>
+        <v>550021</v>
       </c>
       <c r="R90" t="n">
-        <v>6942554</v>
+        <v>6942450</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9747,6 +9742,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10064,32 +10064,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126057593</v>
+        <v>126057540</v>
       </c>
       <c r="B94" t="n">
-        <v>98352</v>
+        <v>57656</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550137</v>
+        <v>550138</v>
       </c>
       <c r="R94" t="n">
-        <v>6942555</v>
+        <v>6942638</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10139,7 +10139,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10166,48 +10166,53 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126057923</v>
+        <v>126050713</v>
       </c>
       <c r="B95" t="n">
-        <v>98352</v>
+        <v>56839</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>550122</v>
+        <v>550120</v>
       </c>
       <c r="R95" t="n">
-        <v>6942671</v>
+        <v>6942506</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10237,11 +10242,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10268,32 +10268,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126057540</v>
+        <v>126057593</v>
       </c>
       <c r="B96" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10303,10 +10303,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>550138</v>
+        <v>550137</v>
       </c>
       <c r="R96" t="n">
-        <v>6942638</v>
+        <v>6942555</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall.</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10370,53 +10370,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126050713</v>
+        <v>126057923</v>
       </c>
       <c r="B97" t="n">
-        <v>56839</v>
+        <v>98352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>550120</v>
+        <v>550122</v>
       </c>
       <c r="R97" t="n">
-        <v>6942506</v>
+        <v>6942671</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10446,6 +10441,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126057934</v>
+        <v>126057564</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,34 +2194,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550127</v>
+        <v>550076</v>
       </c>
       <c r="R15" t="n">
-        <v>6942669</v>
+        <v>6942390</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2254,11 +2254,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126057536</v>
+        <v>126057934</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,34 +2291,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550113</v>
+        <v>550127</v>
       </c>
       <c r="R16" t="n">
-        <v>6942389</v>
+        <v>6942669</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2360,7 +2355,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,10 +2382,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126057564</v>
+        <v>126057536</v>
       </c>
       <c r="B17" t="n">
-        <v>78736</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2398,21 +2393,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2422,10 +2417,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550076</v>
+        <v>550113</v>
       </c>
       <c r="R17" t="n">
-        <v>6942390</v>
+        <v>6942389</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2458,6 +2453,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2785,45 +2785,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057935</v>
+        <v>126057582</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550099</v>
+        <v>550023</v>
       </c>
       <c r="R21" t="n">
-        <v>6942670</v>
+        <v>6942583</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2856,6 +2856,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>61 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,10 +2887,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057526</v>
+        <v>126057935</v>
       </c>
       <c r="B22" t="n">
-        <v>91242</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,34 +2898,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550079</v>
+        <v>550099</v>
       </c>
       <c r="R22" t="n">
-        <v>6942497</v>
+        <v>6942670</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2979,32 +2984,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057582</v>
+        <v>126057526</v>
       </c>
       <c r="B23" t="n">
-        <v>98352</v>
+        <v>91242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3014,10 +3019,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550023</v>
+        <v>550079</v>
       </c>
       <c r="R23" t="n">
-        <v>6942583</v>
+        <v>6942497</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3050,11 +3055,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>61 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -5074,32 +5074,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057896</v>
+        <v>126057930</v>
       </c>
       <c r="B44" t="n">
-        <v>80108</v>
+        <v>98352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550007</v>
+        <v>550112</v>
       </c>
       <c r="R44" t="n">
-        <v>6942646</v>
+        <v>6942664</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5145,6 +5145,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>50stycken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5171,48 +5176,52 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057568</v>
+        <v>126052332</v>
       </c>
       <c r="B45" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550093</v>
+        <v>549984</v>
       </c>
       <c r="R45" t="n">
-        <v>6942579</v>
+        <v>6942510</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5365,32 +5374,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057930</v>
+        <v>126057896</v>
       </c>
       <c r="B47" t="n">
-        <v>98352</v>
+        <v>80108</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5400,10 +5409,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550112</v>
+        <v>550007</v>
       </c>
       <c r="R47" t="n">
-        <v>6942664</v>
+        <v>6942646</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5436,11 +5445,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>50stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5467,52 +5471,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126052332</v>
+        <v>126057568</v>
       </c>
       <c r="B48" t="n">
-        <v>98373</v>
+        <v>80080</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>549984</v>
+        <v>550093</v>
       </c>
       <c r="R48" t="n">
-        <v>6942510</v>
+        <v>6942579</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5568,45 +5568,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126051690</v>
+        <v>126051408</v>
       </c>
       <c r="B49" t="n">
-        <v>80108</v>
+        <v>57653</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550110</v>
+        <v>550089</v>
       </c>
       <c r="R49" t="n">
-        <v>6942386</v>
+        <v>6942422</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5639,6 +5644,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5665,10 +5675,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126049249</v>
+        <v>126051690</v>
       </c>
       <c r="B50" t="n">
-        <v>58025</v>
+        <v>80108</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5676,43 +5686,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550135</v>
+        <v>550110</v>
       </c>
       <c r="R50" t="n">
-        <v>6942628</v>
+        <v>6942386</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5771,27 +5772,27 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126051408</v>
+        <v>126049249</v>
       </c>
       <c r="B51" t="n">
-        <v>57653</v>
+        <v>58025</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5799,10 +5800,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5811,10 +5816,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550089</v>
+        <v>550135</v>
       </c>
       <c r="R51" t="n">
-        <v>6942422</v>
+        <v>6942628</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5847,11 +5852,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6572,38 +6572,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126051839</v>
+        <v>126048239</v>
       </c>
       <c r="B59" t="n">
-        <v>56848</v>
+        <v>98352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>56</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6612,10 +6611,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550088</v>
+        <v>550147</v>
       </c>
       <c r="R59" t="n">
-        <v>6942377</v>
+        <v>6942635</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6674,7 +6673,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126048239</v>
+        <v>126049594</v>
       </c>
       <c r="B60" t="n">
         <v>98352</v>
@@ -6704,7 +6703,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6713,10 +6712,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550147</v>
+        <v>550141</v>
       </c>
       <c r="R60" t="n">
-        <v>6942635</v>
+        <v>6942615</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6775,52 +6774,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126049594</v>
+        <v>126057576</v>
       </c>
       <c r="B61" t="n">
-        <v>98352</v>
+        <v>78735</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550141</v>
+        <v>550078</v>
       </c>
       <c r="R61" t="n">
-        <v>6942615</v>
+        <v>6942401</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6876,32 +6871,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126057576</v>
+        <v>126057601</v>
       </c>
       <c r="B62" t="n">
-        <v>78735</v>
+        <v>98352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6911,10 +6906,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550078</v>
+        <v>550096</v>
       </c>
       <c r="R62" t="n">
-        <v>6942401</v>
+        <v>6942661</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6947,6 +6942,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6973,7 +6973,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126057601</v>
+        <v>126052934</v>
       </c>
       <c r="B63" t="n">
         <v>98352</v>
@@ -7001,20 +7001,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550096</v>
+        <v>549977</v>
       </c>
       <c r="R63" t="n">
-        <v>6942661</v>
+        <v>6942554</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7044,11 +7048,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7075,37 +7074,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126052934</v>
+        <v>126052802</v>
       </c>
       <c r="B64" t="n">
-        <v>98352</v>
+        <v>98373</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7114,10 +7113,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>549977</v>
+        <v>549987</v>
       </c>
       <c r="R64" t="n">
-        <v>6942554</v>
+        <v>6942530</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7176,10 +7175,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126052802</v>
+        <v>126051839</v>
       </c>
       <c r="B65" t="n">
-        <v>98373</v>
+        <v>56848</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7187,26 +7186,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>549987</v>
+        <v>550088</v>
       </c>
       <c r="R65" t="n">
-        <v>6942530</v>
+        <v>6942377</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8276,49 +8276,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126051602</v>
+        <v>126050913</v>
       </c>
       <c r="B76" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550089</v>
+        <v>550088</v>
       </c>
       <c r="R76" t="n">
-        <v>6942422</v>
+        <v>6942520</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8351,6 +8347,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8571,45 +8572,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126050913</v>
+        <v>126051602</v>
       </c>
       <c r="B79" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550088</v>
+        <v>550089</v>
       </c>
       <c r="R79" t="n">
-        <v>6942520</v>
+        <v>6942422</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8642,11 +8647,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9273,32 +9273,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126057531</v>
+        <v>126052827</v>
       </c>
       <c r="B86" t="n">
-        <v>57656</v>
+        <v>97230</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9308,13 +9308,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>549974</v>
+        <v>549987</v>
       </c>
       <c r="R86" t="n">
-        <v>6942584</v>
+        <v>6942530</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9344,11 +9344,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9375,10 +9370,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126057535</v>
+        <v>126057575</v>
       </c>
       <c r="B87" t="n">
-        <v>57656</v>
+        <v>78735</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9386,21 +9381,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9410,10 +9405,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550047</v>
+        <v>550022</v>
       </c>
       <c r="R87" t="n">
-        <v>6942401</v>
+        <v>6942537</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9446,11 +9441,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9477,32 +9467,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126057575</v>
+        <v>126057556</v>
       </c>
       <c r="B88" t="n">
-        <v>78735</v>
+        <v>80108</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9512,10 +9502,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550022</v>
+        <v>550074</v>
       </c>
       <c r="R88" t="n">
-        <v>6942537</v>
+        <v>6942641</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9574,32 +9564,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126057556</v>
+        <v>126052154</v>
       </c>
       <c r="B89" t="n">
-        <v>80108</v>
+        <v>78977</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9609,13 +9599,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550074</v>
+        <v>550021</v>
       </c>
       <c r="R89" t="n">
-        <v>6942641</v>
+        <v>6942450</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9645,6 +9635,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9671,10 +9666,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126052154</v>
+        <v>126057531</v>
       </c>
       <c r="B90" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9682,21 +9677,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9706,13 +9701,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550021</v>
+        <v>549974</v>
       </c>
       <c r="R90" t="n">
-        <v>6942450</v>
+        <v>6942584</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9746,7 +9741,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9773,32 +9768,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126052827</v>
+        <v>126057535</v>
       </c>
       <c r="B91" t="n">
-        <v>97230</v>
+        <v>57656</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9808,13 +9803,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>549987</v>
+        <v>550047</v>
       </c>
       <c r="R91" t="n">
-        <v>6942530</v>
+        <v>6942401</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9844,6 +9839,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126057564</v>
+        <v>126057934</v>
       </c>
       <c r="B15" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,34 +2194,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550076</v>
+        <v>550127</v>
       </c>
       <c r="R15" t="n">
-        <v>6942390</v>
+        <v>6942669</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2254,6 +2254,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126057934</v>
+        <v>126057536</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2291,34 +2296,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550127</v>
+        <v>550113</v>
       </c>
       <c r="R16" t="n">
-        <v>6942669</v>
+        <v>6942389</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2355,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,32 +2387,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126057536</v>
+        <v>126057597</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>98361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2417,10 +2422,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550113</v>
+        <v>550099</v>
       </c>
       <c r="R17" t="n">
-        <v>6942389</v>
+        <v>6942637</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2457,7 +2462,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,7 +2492,7 @@
         <v>126057921</v>
       </c>
       <c r="B18" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,32 +2591,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057597</v>
+        <v>126057564</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>78739</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2621,10 +2626,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550099</v>
+        <v>550076</v>
       </c>
       <c r="R19" t="n">
-        <v>6942637</v>
+        <v>6942390</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2657,11 +2662,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>8 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,7 +2691,7 @@
         <v>126057563</v>
       </c>
       <c r="B20" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>126057582</v>
       </c>
       <c r="B21" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057935</v>
+        <v>126057526</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>91245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,34 +2898,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550099</v>
+        <v>550079</v>
       </c>
       <c r="R22" t="n">
-        <v>6942670</v>
+        <v>6942497</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057526</v>
+        <v>126057935</v>
       </c>
       <c r="B23" t="n">
-        <v>91242</v>
+        <v>78980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2995,34 +2995,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550079</v>
+        <v>550099</v>
       </c>
       <c r="R23" t="n">
-        <v>6942497</v>
+        <v>6942670</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3084,7 +3084,7 @@
         <v>126057532</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126050880</v>
+        <v>126057545</v>
       </c>
       <c r="B25" t="n">
-        <v>80108</v>
+        <v>91256</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3194,21 +3194,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>1205</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3218,13 +3218,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550088</v>
+        <v>550011</v>
       </c>
       <c r="R25" t="n">
-        <v>6942520</v>
+        <v>6942535</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3280,32 +3280,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126052983</v>
+        <v>126050880</v>
       </c>
       <c r="B26" t="n">
-        <v>78735</v>
+        <v>80111</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549977</v>
+        <v>550088</v>
       </c>
       <c r="R26" t="n">
-        <v>6942554</v>
+        <v>6942520</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3377,10 +3377,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126052248</v>
+        <v>126052983</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3388,21 +3388,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550004</v>
+        <v>549977</v>
       </c>
       <c r="R27" t="n">
-        <v>6942504</v>
+        <v>6942554</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3448,11 +3448,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom området</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3479,32 +3474,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126051522</v>
+        <v>126052248</v>
       </c>
       <c r="B28" t="n">
-        <v>80108</v>
+        <v>78980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3514,10 +3509,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550089</v>
+        <v>550004</v>
       </c>
       <c r="R28" t="n">
-        <v>6942422</v>
+        <v>6942504</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3550,6 +3545,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom området</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3576,10 +3576,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057544</v>
+        <v>126051522</v>
       </c>
       <c r="B29" t="n">
-        <v>80109</v>
+        <v>80111</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3587,21 +3587,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3611,13 +3611,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550094</v>
+        <v>550089</v>
       </c>
       <c r="R29" t="n">
-        <v>6942584</v>
+        <v>6942422</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057545</v>
+        <v>126057544</v>
       </c>
       <c r="B30" t="n">
-        <v>91253</v>
+        <v>80112</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3684,21 +3684,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550011</v>
+        <v>550094</v>
       </c>
       <c r="R30" t="n">
-        <v>6942535</v>
+        <v>6942584</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3773,7 +3773,7 @@
         <v>126051074</v>
       </c>
       <c r="B31" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>126057579</v>
       </c>
       <c r="B32" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>126057937</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>126057567</v>
       </c>
       <c r="B34" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>126053984</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4269,32 +4269,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057596</v>
+        <v>126057538</v>
       </c>
       <c r="B36" t="n">
-        <v>98352</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550092</v>
+        <v>550041</v>
       </c>
       <c r="R36" t="n">
-        <v>6942597</v>
+        <v>6942496</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4371,10 +4371,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057591</v>
+        <v>126057596</v>
       </c>
       <c r="B37" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550020</v>
+        <v>550092</v>
       </c>
       <c r="R37" t="n">
-        <v>6942543</v>
+        <v>6942597</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4473,32 +4473,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057538</v>
+        <v>126057591</v>
       </c>
       <c r="B38" t="n">
-        <v>57656</v>
+        <v>98361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550041</v>
+        <v>550020</v>
       </c>
       <c r="R38" t="n">
-        <v>6942496</v>
+        <v>6942543</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4578,7 +4578,7 @@
         <v>126052912</v>
       </c>
       <c r="B39" t="n">
-        <v>80108</v>
+        <v>80111</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>126057569</v>
       </c>
       <c r="B40" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>126057592</v>
       </c>
       <c r="B41" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>126052420</v>
       </c>
       <c r="B42" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>126057600</v>
       </c>
       <c r="B43" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5074,32 +5074,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057930</v>
+        <v>126057896</v>
       </c>
       <c r="B44" t="n">
-        <v>98352</v>
+        <v>80111</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550112</v>
+        <v>550007</v>
       </c>
       <c r="R44" t="n">
-        <v>6942664</v>
+        <v>6942646</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5145,11 +5145,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>50stycken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5176,52 +5171,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126052332</v>
+        <v>126057568</v>
       </c>
       <c r="B45" t="n">
-        <v>98373</v>
+        <v>80083</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>549984</v>
+        <v>550093</v>
       </c>
       <c r="R45" t="n">
-        <v>6942510</v>
+        <v>6942579</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5277,45 +5268,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126052735</v>
+        <v>126052332</v>
       </c>
       <c r="B46" t="n">
-        <v>78736</v>
+        <v>98382</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549975</v>
+        <v>549984</v>
       </c>
       <c r="R46" t="n">
-        <v>6942519</v>
+        <v>6942510</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5374,48 +5369,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057896</v>
+        <v>126052735</v>
       </c>
       <c r="B47" t="n">
-        <v>80108</v>
+        <v>78739</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550007</v>
+        <v>549975</v>
       </c>
       <c r="R47" t="n">
-        <v>6942646</v>
+        <v>6942519</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5471,45 +5466,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057568</v>
+        <v>126057930</v>
       </c>
       <c r="B48" t="n">
-        <v>80080</v>
+        <v>98361</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550093</v>
+        <v>550112</v>
       </c>
       <c r="R48" t="n">
-        <v>6942579</v>
+        <v>6942664</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5542,6 +5537,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>50stycken</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5568,27 +5568,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126051408</v>
+        <v>126049249</v>
       </c>
       <c r="B49" t="n">
-        <v>57653</v>
+        <v>58027</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5596,10 +5596,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5608,10 +5612,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550089</v>
+        <v>550135</v>
       </c>
       <c r="R49" t="n">
-        <v>6942422</v>
+        <v>6942628</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5644,11 +5648,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5678,7 +5677,7 @@
         <v>126051690</v>
       </c>
       <c r="B50" t="n">
-        <v>80108</v>
+        <v>80111</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5772,27 +5771,27 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126049249</v>
+        <v>126051408</v>
       </c>
       <c r="B51" t="n">
-        <v>58025</v>
+        <v>57654</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5800,14 +5799,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5816,10 +5811,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550135</v>
+        <v>550089</v>
       </c>
       <c r="R51" t="n">
-        <v>6942628</v>
+        <v>6942422</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5852,6 +5847,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5881,7 +5881,7 @@
         <v>126057602</v>
       </c>
       <c r="B52" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>126057915</v>
       </c>
       <c r="B53" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>126057898</v>
       </c>
       <c r="B54" t="n">
-        <v>80108</v>
+        <v>80111</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>126057565</v>
       </c>
       <c r="B55" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>126057525</v>
       </c>
       <c r="B56" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6368,48 +6368,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126057533</v>
+        <v>126050777</v>
       </c>
       <c r="B57" t="n">
-        <v>57656</v>
+        <v>56849</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550026</v>
+        <v>550093</v>
       </c>
       <c r="R57" t="n">
-        <v>6942422</v>
+        <v>6942497</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6439,11 +6444,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6470,53 +6470,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126050777</v>
+        <v>126057533</v>
       </c>
       <c r="B58" t="n">
-        <v>56848</v>
+        <v>57657</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550093</v>
+        <v>550026</v>
       </c>
       <c r="R58" t="n">
-        <v>6942497</v>
+        <v>6942422</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6546,6 +6541,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6572,10 +6572,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126048239</v>
+        <v>126049594</v>
       </c>
       <c r="B59" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6611,10 +6611,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550147</v>
+        <v>550141</v>
       </c>
       <c r="R59" t="n">
-        <v>6942635</v>
+        <v>6942615</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6673,10 +6673,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126049594</v>
+        <v>126048239</v>
       </c>
       <c r="B60" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6712,10 +6712,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550141</v>
+        <v>550147</v>
       </c>
       <c r="R60" t="n">
-        <v>6942615</v>
+        <v>6942635</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6777,7 +6777,7 @@
         <v>126057576</v>
       </c>
       <c r="B61" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6871,48 +6871,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126057601</v>
+        <v>126051839</v>
       </c>
       <c r="B62" t="n">
-        <v>98352</v>
+        <v>56849</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550096</v>
+        <v>550088</v>
       </c>
       <c r="R62" t="n">
-        <v>6942661</v>
+        <v>6942377</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6942,11 +6947,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6973,10 +6973,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126052934</v>
+        <v>126057601</v>
       </c>
       <c r="B63" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7001,24 +7001,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>549977</v>
+        <v>550096</v>
       </c>
       <c r="R63" t="n">
-        <v>6942554</v>
+        <v>6942661</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7048,6 +7044,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7074,37 +7075,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126052802</v>
+        <v>126052934</v>
       </c>
       <c r="B64" t="n">
-        <v>98373</v>
+        <v>98361</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7113,10 +7114,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>549987</v>
+        <v>549977</v>
       </c>
       <c r="R64" t="n">
-        <v>6942530</v>
+        <v>6942554</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7175,10 +7176,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126051839</v>
+        <v>126052802</v>
       </c>
       <c r="B65" t="n">
-        <v>56848</v>
+        <v>98382</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7186,27 +7187,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550088</v>
+        <v>549987</v>
       </c>
       <c r="R65" t="n">
-        <v>6942377</v>
+        <v>6942530</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7280,7 +7280,7 @@
         <v>126057594</v>
       </c>
       <c r="B66" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>126051197</v>
       </c>
       <c r="B67" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>126051507</v>
       </c>
       <c r="B68" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>126057537</v>
       </c>
       <c r="B69" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7679,32 +7679,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126057583</v>
+        <v>126051112</v>
       </c>
       <c r="B70" t="n">
-        <v>98352</v>
+        <v>80111</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7714,13 +7714,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550098</v>
+        <v>550093</v>
       </c>
       <c r="R70" t="n">
-        <v>6942641</v>
+        <v>6942497</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7750,11 +7750,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>31 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7781,32 +7776,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126051112</v>
+        <v>126053048</v>
       </c>
       <c r="B71" t="n">
-        <v>80108</v>
+        <v>78980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7816,10 +7811,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550093</v>
+        <v>549965</v>
       </c>
       <c r="R71" t="n">
-        <v>6942497</v>
+        <v>6942583</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7852,6 +7847,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav I området</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7878,32 +7878,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126053048</v>
+        <v>126057583</v>
       </c>
       <c r="B72" t="n">
-        <v>78977</v>
+        <v>98361</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7913,13 +7913,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>549965</v>
+        <v>550098</v>
       </c>
       <c r="R72" t="n">
-        <v>6942583</v>
+        <v>6942641</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav I området</t>
+          <t>31 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7983,7 +7983,7 @@
         <v>126049570</v>
       </c>
       <c r="B73" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>126057549</v>
       </c>
       <c r="B74" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>126057578</v>
       </c>
       <c r="B75" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>126050913</v>
       </c>
       <c r="B76" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>126057606</v>
       </c>
       <c r="B77" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>126057904</v>
       </c>
       <c r="B78" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>126051602</v>
       </c>
       <c r="B79" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8673,32 +8673,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126057559</v>
+        <v>126057574</v>
       </c>
       <c r="B80" t="n">
-        <v>80108</v>
+        <v>78738</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550000</v>
+        <v>549990</v>
       </c>
       <c r="R80" t="n">
-        <v>6942626</v>
+        <v>6942590</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8770,32 +8770,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126057574</v>
+        <v>126057524</v>
       </c>
       <c r="B81" t="n">
-        <v>78735</v>
+        <v>91210</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>549990</v>
+        <v>550079</v>
       </c>
       <c r="R81" t="n">
-        <v>6942590</v>
+        <v>6942497</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8867,48 +8867,52 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126057524</v>
+        <v>126051270</v>
       </c>
       <c r="B82" t="n">
-        <v>91207</v>
+        <v>98361</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550079</v>
+        <v>550065</v>
       </c>
       <c r="R82" t="n">
-        <v>6942497</v>
+        <v>6942463</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8964,37 +8968,38 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126051270</v>
+        <v>126047488</v>
       </c>
       <c r="B83" t="n">
-        <v>98352</v>
+        <v>43935</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>43</t>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9003,13 +9008,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550065</v>
+        <v>550158</v>
       </c>
       <c r="R83" t="n">
-        <v>6942463</v>
+        <v>6942653</v>
       </c>
       <c r="S83" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9039,6 +9044,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9065,10 +9075,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126047488</v>
+        <v>126057559</v>
       </c>
       <c r="B84" t="n">
-        <v>43934</v>
+        <v>80111</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9076,42 +9086,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>101735</v>
+        <v>6461</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550158</v>
+        <v>550000</v>
       </c>
       <c r="R84" t="n">
-        <v>6942653</v>
+        <v>6942626</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9141,11 +9146,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9172,52 +9172,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126052873</v>
+        <v>126057531</v>
       </c>
       <c r="B85" t="n">
-        <v>98352</v>
+        <v>57657</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>549989</v>
+        <v>549974</v>
       </c>
       <c r="R85" t="n">
-        <v>6942554</v>
+        <v>6942584</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9247,6 +9243,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9273,32 +9274,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126052827</v>
+        <v>126057535</v>
       </c>
       <c r="B86" t="n">
-        <v>97230</v>
+        <v>57657</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9308,13 +9309,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>549987</v>
+        <v>550047</v>
       </c>
       <c r="R86" t="n">
-        <v>6942530</v>
+        <v>6942401</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9344,6 +9345,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9370,48 +9376,52 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126057575</v>
+        <v>126052873</v>
       </c>
       <c r="B87" t="n">
-        <v>78735</v>
+        <v>98361</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550022</v>
+        <v>549989</v>
       </c>
       <c r="R87" t="n">
-        <v>6942537</v>
+        <v>6942554</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9467,32 +9477,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126057556</v>
+        <v>126057575</v>
       </c>
       <c r="B88" t="n">
-        <v>80108</v>
+        <v>78738</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9502,10 +9512,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550074</v>
+        <v>550022</v>
       </c>
       <c r="R88" t="n">
-        <v>6942641</v>
+        <v>6942537</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9564,32 +9574,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126052154</v>
+        <v>126057556</v>
       </c>
       <c r="B89" t="n">
-        <v>78977</v>
+        <v>80111</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9599,13 +9609,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550021</v>
+        <v>550074</v>
       </c>
       <c r="R89" t="n">
-        <v>6942450</v>
+        <v>6942641</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9635,11 +9645,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9666,10 +9671,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126057531</v>
+        <v>126052154</v>
       </c>
       <c r="B90" t="n">
-        <v>57656</v>
+        <v>78980</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9677,21 +9682,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9701,13 +9706,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>549974</v>
+        <v>550021</v>
       </c>
       <c r="R90" t="n">
-        <v>6942584</v>
+        <v>6942450</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9741,7 +9746,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9768,32 +9773,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126057535</v>
+        <v>126052827</v>
       </c>
       <c r="B91" t="n">
-        <v>57656</v>
+        <v>97239</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9803,13 +9808,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550047</v>
+        <v>549987</v>
       </c>
       <c r="R91" t="n">
-        <v>6942401</v>
+        <v>6942530</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9839,11 +9844,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9870,10 +9870,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126057577</v>
+        <v>126057581</v>
       </c>
       <c r="B92" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9905,10 +9905,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550101</v>
+        <v>550004</v>
       </c>
       <c r="R92" t="n">
-        <v>6942551</v>
+        <v>6942625</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -9967,10 +9967,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126057581</v>
+        <v>126057540</v>
       </c>
       <c r="B93" t="n">
-        <v>78735</v>
+        <v>57657</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9978,21 +9978,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10002,10 +10002,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550004</v>
+        <v>550138</v>
       </c>
       <c r="R93" t="n">
-        <v>6942625</v>
+        <v>6942638</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10038,6 +10038,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10064,45 +10069,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126057540</v>
+        <v>126057923</v>
       </c>
       <c r="B94" t="n">
-        <v>57656</v>
+        <v>98361</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550138</v>
+        <v>550122</v>
       </c>
       <c r="R94" t="n">
-        <v>6942638</v>
+        <v>6942671</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10139,7 +10144,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall.</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10166,10 +10171,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126050713</v>
+        <v>126057577</v>
       </c>
       <c r="B95" t="n">
-        <v>56839</v>
+        <v>78738</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10177,42 +10182,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>550120</v>
+        <v>550101</v>
       </c>
       <c r="R95" t="n">
-        <v>6942506</v>
+        <v>6942551</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10268,48 +10268,53 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126057593</v>
+        <v>126050713</v>
       </c>
       <c r="B96" t="n">
-        <v>98352</v>
+        <v>56840</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>550137</v>
+        <v>550120</v>
       </c>
       <c r="R96" t="n">
-        <v>6942555</v>
+        <v>6942506</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10339,11 +10344,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>3 ex</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10370,10 +10370,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126057923</v>
+        <v>126057593</v>
       </c>
       <c r="B97" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10401,14 +10401,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>550122</v>
+        <v>550137</v>
       </c>
       <c r="R97" t="n">
-        <v>6942671</v>
+        <v>6942555</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2387,7 +2387,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126057597</v>
+        <v>126057921</v>
       </c>
       <c r="B17" t="n">
         <v>98361</v>
@@ -2418,14 +2418,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550099</v>
+        <v>550142</v>
       </c>
       <c r="R17" t="n">
-        <v>6942637</v>
+        <v>6942582</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,7 +2489,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057921</v>
+        <v>126057597</v>
       </c>
       <c r="B18" t="n">
         <v>98361</v>
@@ -2520,14 +2520,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550142</v>
+        <v>550099</v>
       </c>
       <c r="R18" t="n">
-        <v>6942582</v>
+        <v>6942637</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>30 stycken</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,32 +2785,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057582</v>
+        <v>126057526</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>91245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550023</v>
+        <v>550079</v>
       </c>
       <c r="R21" t="n">
-        <v>6942583</v>
+        <v>6942497</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2856,11 +2856,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>61 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2887,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057526</v>
+        <v>126057935</v>
       </c>
       <c r="B22" t="n">
-        <v>91245</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,34 +2893,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550079</v>
+        <v>550099</v>
       </c>
       <c r="R22" t="n">
-        <v>6942497</v>
+        <v>6942670</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2984,45 +2979,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057935</v>
+        <v>126057582</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550099</v>
+        <v>550023</v>
       </c>
       <c r="R23" t="n">
-        <v>6942670</v>
+        <v>6942583</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3055,6 +3050,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>61 ex</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4575,32 +4575,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126052912</v>
+        <v>126057592</v>
       </c>
       <c r="B39" t="n">
-        <v>80111</v>
+        <v>98361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>549977</v>
+        <v>550038</v>
       </c>
       <c r="R39" t="n">
-        <v>6942554</v>
+        <v>6942494</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4646,6 +4646,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>28 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4672,48 +4677,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126057569</v>
+        <v>126052420</v>
       </c>
       <c r="B40" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550006</v>
+        <v>549984</v>
       </c>
       <c r="R40" t="n">
-        <v>6942630</v>
+        <v>6942510</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4769,7 +4778,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126057592</v>
+        <v>126057600</v>
       </c>
       <c r="B41" t="n">
         <v>98361</v>
@@ -4804,10 +4813,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550038</v>
+        <v>550095</v>
       </c>
       <c r="R41" t="n">
-        <v>6942494</v>
+        <v>6942646</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4844,7 +4853,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>28 ex</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4871,49 +4880,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126052420</v>
+        <v>126052912</v>
       </c>
       <c r="B42" t="n">
-        <v>98361</v>
+        <v>80111</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549984</v>
+        <v>549977</v>
       </c>
       <c r="R42" t="n">
-        <v>6942510</v>
+        <v>6942554</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,32 +4977,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126057600</v>
+        <v>126057569</v>
       </c>
       <c r="B43" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5007,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550095</v>
+        <v>550006</v>
       </c>
       <c r="R43" t="n">
-        <v>6942646</v>
+        <v>6942630</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5043,11 +5048,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5074,10 +5074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057896</v>
+        <v>126052332</v>
       </c>
       <c r="B44" t="n">
-        <v>80111</v>
+        <v>98382</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5085,37 +5085,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550007</v>
+        <v>549984</v>
       </c>
       <c r="R44" t="n">
-        <v>6942646</v>
+        <v>6942510</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5171,45 +5175,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057568</v>
+        <v>126057896</v>
       </c>
       <c r="B45" t="n">
-        <v>80083</v>
+        <v>80111</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550093</v>
+        <v>550007</v>
       </c>
       <c r="R45" t="n">
-        <v>6942579</v>
+        <v>6942646</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5268,52 +5272,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126052332</v>
+        <v>126057568</v>
       </c>
       <c r="B46" t="n">
-        <v>98382</v>
+        <v>80083</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>549984</v>
+        <v>550093</v>
       </c>
       <c r="R46" t="n">
-        <v>6942510</v>
+        <v>6942579</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5369,48 +5369,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126052735</v>
+        <v>126057930</v>
       </c>
       <c r="B47" t="n">
-        <v>78739</v>
+        <v>98361</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>549975</v>
+        <v>550112</v>
       </c>
       <c r="R47" t="n">
-        <v>6942519</v>
+        <v>6942664</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5440,6 +5440,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>50stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5466,48 +5471,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057930</v>
+        <v>126052735</v>
       </c>
       <c r="B48" t="n">
-        <v>98361</v>
+        <v>78739</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550112</v>
+        <v>549975</v>
       </c>
       <c r="R48" t="n">
-        <v>6942664</v>
+        <v>6942519</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5537,11 +5542,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>50stycken</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5674,45 +5674,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126051690</v>
+        <v>126051408</v>
       </c>
       <c r="B50" t="n">
-        <v>80111</v>
+        <v>57654</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550110</v>
+        <v>550089</v>
       </c>
       <c r="R50" t="n">
-        <v>6942386</v>
+        <v>6942422</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5745,6 +5750,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5771,50 +5781,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126051408</v>
+        <v>126051690</v>
       </c>
       <c r="B51" t="n">
-        <v>57654</v>
+        <v>80111</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550089</v>
+        <v>550110</v>
       </c>
       <c r="R51" t="n">
-        <v>6942422</v>
+        <v>6942386</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5847,11 +5852,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5980,10 +5980,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057915</v>
+        <v>126057565</v>
       </c>
       <c r="B53" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5991,34 +5991,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550145</v>
+        <v>550139</v>
       </c>
       <c r="R53" t="n">
-        <v>6942577</v>
+        <v>6942641</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6077,32 +6077,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126057898</v>
+        <v>126057915</v>
       </c>
       <c r="B54" t="n">
-        <v>80111</v>
+        <v>78738</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>549997</v>
+        <v>550145</v>
       </c>
       <c r="R54" t="n">
-        <v>6942637</v>
+        <v>6942577</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6174,45 +6174,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057565</v>
+        <v>126057898</v>
       </c>
       <c r="B55" t="n">
-        <v>78739</v>
+        <v>80111</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550139</v>
+        <v>549997</v>
       </c>
       <c r="R55" t="n">
-        <v>6942641</v>
+        <v>6942637</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6572,7 +6572,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126049594</v>
+        <v>126057601</v>
       </c>
       <c r="B59" t="n">
         <v>98361</v>
@@ -6600,24 +6600,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550141</v>
+        <v>550096</v>
       </c>
       <c r="R59" t="n">
-        <v>6942615</v>
+        <v>6942661</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6647,6 +6643,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6673,7 +6674,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126048239</v>
+        <v>126052934</v>
       </c>
       <c r="B60" t="n">
         <v>98361</v>
@@ -6703,7 +6704,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6712,10 +6713,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550147</v>
+        <v>549977</v>
       </c>
       <c r="R60" t="n">
-        <v>6942635</v>
+        <v>6942554</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6774,48 +6775,52 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126057576</v>
+        <v>126049594</v>
       </c>
       <c r="B61" t="n">
-        <v>78738</v>
+        <v>98361</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550078</v>
+        <v>550141</v>
       </c>
       <c r="R61" t="n">
-        <v>6942401</v>
+        <v>6942615</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6871,38 +6876,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126051839</v>
+        <v>126048239</v>
       </c>
       <c r="B62" t="n">
-        <v>56849</v>
+        <v>98361</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>56</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6911,10 +6915,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550088</v>
+        <v>550147</v>
       </c>
       <c r="R62" t="n">
-        <v>6942377</v>
+        <v>6942635</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6973,32 +6977,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126057601</v>
+        <v>126057576</v>
       </c>
       <c r="B63" t="n">
-        <v>98361</v>
+        <v>78738</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7008,10 +7012,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550096</v>
+        <v>550078</v>
       </c>
       <c r="R63" t="n">
-        <v>6942661</v>
+        <v>6942401</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7044,11 +7048,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7075,37 +7074,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126052934</v>
+        <v>126051839</v>
       </c>
       <c r="B64" t="n">
-        <v>98361</v>
+        <v>56849</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>29</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7114,10 +7114,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>549977</v>
+        <v>550088</v>
       </c>
       <c r="R64" t="n">
-        <v>6942554</v>
+        <v>6942377</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8082,32 +8082,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126057549</v>
+        <v>126057578</v>
       </c>
       <c r="B74" t="n">
-        <v>91699</v>
+        <v>78738</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>549978</v>
+        <v>550086</v>
       </c>
       <c r="R74" t="n">
-        <v>6942581</v>
+        <v>6942580</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8179,32 +8179,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126057578</v>
+        <v>126057549</v>
       </c>
       <c r="B75" t="n">
-        <v>78738</v>
+        <v>91699</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550086</v>
+        <v>549978</v>
       </c>
       <c r="R75" t="n">
-        <v>6942580</v>
+        <v>6942581</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8673,32 +8673,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126057574</v>
+        <v>126057559</v>
       </c>
       <c r="B80" t="n">
-        <v>78738</v>
+        <v>80111</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>549990</v>
+        <v>550000</v>
       </c>
       <c r="R80" t="n">
-        <v>6942590</v>
+        <v>6942626</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126057524</v>
+        <v>126047488</v>
       </c>
       <c r="B81" t="n">
-        <v>91210</v>
+        <v>43935</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8781,37 +8781,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>101735</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550079</v>
+        <v>550158</v>
       </c>
       <c r="R81" t="n">
-        <v>6942497</v>
+        <v>6942653</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8841,6 +8846,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8867,52 +8877,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126051270</v>
+        <v>126057574</v>
       </c>
       <c r="B82" t="n">
-        <v>98361</v>
+        <v>78738</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550065</v>
+        <v>549990</v>
       </c>
       <c r="R82" t="n">
-        <v>6942463</v>
+        <v>6942590</v>
       </c>
       <c r="S82" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8968,10 +8974,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126047488</v>
+        <v>126057524</v>
       </c>
       <c r="B83" t="n">
-        <v>43935</v>
+        <v>91210</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8979,42 +8985,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>101735</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550158</v>
+        <v>550079</v>
       </c>
       <c r="R83" t="n">
-        <v>6942653</v>
+        <v>6942497</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9044,11 +9045,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9075,48 +9071,52 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126057559</v>
+        <v>126051270</v>
       </c>
       <c r="B84" t="n">
-        <v>80111</v>
+        <v>98361</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550000</v>
+        <v>550065</v>
       </c>
       <c r="R84" t="n">
-        <v>6942626</v>
+        <v>6942463</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9172,10 +9172,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126057531</v>
+        <v>126057575</v>
       </c>
       <c r="B85" t="n">
-        <v>57657</v>
+        <v>78738</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9183,21 +9183,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9207,10 +9207,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>549974</v>
+        <v>550022</v>
       </c>
       <c r="R85" t="n">
-        <v>6942584</v>
+        <v>6942537</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9243,11 +9243,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9274,32 +9269,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126057535</v>
+        <v>126057556</v>
       </c>
       <c r="B86" t="n">
-        <v>57657</v>
+        <v>80111</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9309,10 +9304,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550047</v>
+        <v>550074</v>
       </c>
       <c r="R86" t="n">
-        <v>6942401</v>
+        <v>6942641</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9345,11 +9340,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9376,49 +9366,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126052873</v>
+        <v>126052154</v>
       </c>
       <c r="B87" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>549989</v>
+        <v>550021</v>
       </c>
       <c r="R87" t="n">
-        <v>6942554</v>
+        <v>6942450</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9451,6 +9437,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9477,32 +9468,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126057575</v>
+        <v>126052827</v>
       </c>
       <c r="B88" t="n">
-        <v>78738</v>
+        <v>97239</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9512,13 +9503,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550022</v>
+        <v>549987</v>
       </c>
       <c r="R88" t="n">
-        <v>6942537</v>
+        <v>6942530</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9574,32 +9565,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126057556</v>
+        <v>126057531</v>
       </c>
       <c r="B89" t="n">
-        <v>80111</v>
+        <v>57657</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9609,10 +9600,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550074</v>
+        <v>549974</v>
       </c>
       <c r="R89" t="n">
-        <v>6942641</v>
+        <v>6942584</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9645,6 +9636,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9671,10 +9667,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126052154</v>
+        <v>126057535</v>
       </c>
       <c r="B90" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9682,21 +9678,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9706,13 +9702,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550021</v>
+        <v>550047</v>
       </c>
       <c r="R90" t="n">
-        <v>6942450</v>
+        <v>6942401</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9746,7 +9742,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9773,45 +9769,49 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126052827</v>
+        <v>126052873</v>
       </c>
       <c r="B91" t="n">
-        <v>97239</v>
+        <v>98361</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>549987</v>
+        <v>549989</v>
       </c>
       <c r="R91" t="n">
-        <v>6942530</v>
+        <v>6942554</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9870,10 +9870,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126057581</v>
+        <v>126057540</v>
       </c>
       <c r="B92" t="n">
-        <v>78738</v>
+        <v>57657</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9881,21 +9881,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9905,10 +9905,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550004</v>
+        <v>550138</v>
       </c>
       <c r="R92" t="n">
-        <v>6942625</v>
+        <v>6942638</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -9941,6 +9941,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9967,10 +9972,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126057540</v>
+        <v>126050713</v>
       </c>
       <c r="B93" t="n">
-        <v>57657</v>
+        <v>56840</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9978,16 +9983,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9996,19 +10001,24 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550138</v>
+        <v>550120</v>
       </c>
       <c r="R93" t="n">
-        <v>6942638</v>
+        <v>6942506</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10038,11 +10048,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10069,7 +10074,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126057923</v>
+        <v>126057593</v>
       </c>
       <c r="B94" t="n">
         <v>98361</v>
@@ -10100,14 +10105,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550122</v>
+        <v>550137</v>
       </c>
       <c r="R94" t="n">
-        <v>6942671</v>
+        <v>6942555</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10144,7 +10149,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10171,45 +10176,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126057577</v>
+        <v>126057923</v>
       </c>
       <c r="B95" t="n">
-        <v>78738</v>
+        <v>98361</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>550101</v>
+        <v>550122</v>
       </c>
       <c r="R95" t="n">
-        <v>6942551</v>
+        <v>6942671</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10242,6 +10247,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10268,10 +10278,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126050713</v>
+        <v>126057577</v>
       </c>
       <c r="B96" t="n">
-        <v>56840</v>
+        <v>78738</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10279,42 +10289,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>550120</v>
+        <v>550101</v>
       </c>
       <c r="R96" t="n">
-        <v>6942506</v>
+        <v>6942551</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10370,32 +10375,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126057593</v>
+        <v>126057581</v>
       </c>
       <c r="B97" t="n">
-        <v>98361</v>
+        <v>78738</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10405,10 +10410,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>550137</v>
+        <v>550004</v>
       </c>
       <c r="R97" t="n">
-        <v>6942555</v>
+        <v>6942625</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10441,11 +10446,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>3 ex</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126057934</v>
+        <v>126057536</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,34 +2194,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550127</v>
+        <v>550113</v>
       </c>
       <c r="R15" t="n">
-        <v>6942669</v>
+        <v>6942389</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126057536</v>
+        <v>126057934</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,34 +2296,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550113</v>
+        <v>550127</v>
       </c>
       <c r="R16" t="n">
-        <v>6942389</v>
+        <v>6942669</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057526</v>
+        <v>126057935</v>
       </c>
       <c r="B21" t="n">
-        <v>91245</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,34 +2796,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550079</v>
+        <v>550099</v>
       </c>
       <c r="R21" t="n">
-        <v>6942497</v>
+        <v>6942670</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126057935</v>
+        <v>126057526</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>91245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,34 +2893,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550099</v>
+        <v>550079</v>
       </c>
       <c r="R22" t="n">
-        <v>6942670</v>
+        <v>6942497</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3081,32 +3081,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126057532</v>
+        <v>126050880</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>80111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3116,13 +3116,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550020</v>
+        <v>550088</v>
       </c>
       <c r="R24" t="n">
-        <v>6942390</v>
+        <v>6942520</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,11 +3152,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3183,32 +3178,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126057545</v>
+        <v>126052983</v>
       </c>
       <c r="B25" t="n">
-        <v>91256</v>
+        <v>78738</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1205</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3218,13 +3213,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550011</v>
+        <v>549977</v>
       </c>
       <c r="R25" t="n">
-        <v>6942535</v>
+        <v>6942554</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3280,7 +3275,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126050880</v>
+        <v>126051522</v>
       </c>
       <c r="B26" t="n">
         <v>80111</v>
@@ -3315,10 +3310,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550088</v>
+        <v>550089</v>
       </c>
       <c r="R26" t="n">
-        <v>6942520</v>
+        <v>6942422</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3377,32 +3372,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126052983</v>
+        <v>126057544</v>
       </c>
       <c r="B27" t="n">
-        <v>78738</v>
+        <v>80112</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3412,13 +3407,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549977</v>
+        <v>550094</v>
       </c>
       <c r="R27" t="n">
-        <v>6942554</v>
+        <v>6942584</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3576,10 +3571,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126051522</v>
+        <v>126057545</v>
       </c>
       <c r="B29" t="n">
-        <v>80111</v>
+        <v>91256</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3587,21 +3582,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>1205</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3611,13 +3606,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550089</v>
+        <v>550011</v>
       </c>
       <c r="R29" t="n">
-        <v>6942422</v>
+        <v>6942535</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3673,32 +3668,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057544</v>
+        <v>126057532</v>
       </c>
       <c r="B30" t="n">
-        <v>80112</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3708,10 +3703,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550094</v>
+        <v>550020</v>
       </c>
       <c r="R30" t="n">
-        <v>6942584</v>
+        <v>6942390</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3744,6 +3739,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3968,10 +3968,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057937</v>
+        <v>126057567</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3979,34 +3979,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550147</v>
+        <v>550001</v>
       </c>
       <c r="R33" t="n">
-        <v>6942582</v>
+        <v>6942503</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4039,11 +4039,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4070,10 +4065,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057567</v>
+        <v>126053984</v>
       </c>
       <c r="B34" t="n">
-        <v>80083</v>
+        <v>78980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4081,21 +4076,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4105,13 +4100,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550001</v>
+        <v>549984</v>
       </c>
       <c r="R34" t="n">
-        <v>6942503</v>
+        <v>6942510</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4141,6 +4136,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4167,10 +4167,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126053984</v>
+        <v>126057538</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4178,21 +4178,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4202,13 +4202,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549984</v>
+        <v>550041</v>
       </c>
       <c r="R35" t="n">
-        <v>6942510</v>
+        <v>6942496</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav inom området</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4269,10 +4269,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057538</v>
+        <v>126057937</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4280,34 +4280,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550041</v>
+        <v>550147</v>
       </c>
       <c r="R36" t="n">
-        <v>6942496</v>
+        <v>6942582</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4575,32 +4575,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126057592</v>
+        <v>126052912</v>
       </c>
       <c r="B39" t="n">
-        <v>98361</v>
+        <v>80111</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550038</v>
+        <v>549977</v>
       </c>
       <c r="R39" t="n">
-        <v>6942494</v>
+        <v>6942554</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4646,11 +4646,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>28 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4677,52 +4672,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126052420</v>
+        <v>126057569</v>
       </c>
       <c r="B40" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>549984</v>
+        <v>550006</v>
       </c>
       <c r="R40" t="n">
-        <v>6942510</v>
+        <v>6942630</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4778,7 +4769,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126057600</v>
+        <v>126057592</v>
       </c>
       <c r="B41" t="n">
         <v>98361</v>
@@ -4813,10 +4804,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550095</v>
+        <v>550038</v>
       </c>
       <c r="R41" t="n">
-        <v>6942646</v>
+        <v>6942494</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4853,7 +4844,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>28 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4880,45 +4871,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126052912</v>
+        <v>126052420</v>
       </c>
       <c r="B42" t="n">
-        <v>80111</v>
+        <v>98361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>549977</v>
+        <v>549984</v>
       </c>
       <c r="R42" t="n">
-        <v>6942554</v>
+        <v>6942510</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4977,32 +4972,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126057569</v>
+        <v>126057600</v>
       </c>
       <c r="B43" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5012,10 +5007,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550006</v>
+        <v>550095</v>
       </c>
       <c r="R43" t="n">
-        <v>6942630</v>
+        <v>6942646</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5048,6 +5043,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5074,49 +5074,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126052332</v>
+        <v>126052735</v>
       </c>
       <c r="B44" t="n">
-        <v>98382</v>
+        <v>78739</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549984</v>
+        <v>549975</v>
       </c>
       <c r="R44" t="n">
-        <v>6942510</v>
+        <v>6942519</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5369,48 +5365,52 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126057930</v>
+        <v>126052332</v>
       </c>
       <c r="B47" t="n">
-        <v>98361</v>
+        <v>98382</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550112</v>
+        <v>549984</v>
       </c>
       <c r="R47" t="n">
-        <v>6942664</v>
+        <v>6942510</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5440,11 +5440,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>50stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5471,48 +5466,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126052735</v>
+        <v>126057930</v>
       </c>
       <c r="B48" t="n">
-        <v>78739</v>
+        <v>98361</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>549975</v>
+        <v>550112</v>
       </c>
       <c r="R48" t="n">
-        <v>6942519</v>
+        <v>6942664</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5542,6 +5537,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>50stycken</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5674,50 +5674,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126051408</v>
+        <v>126051690</v>
       </c>
       <c r="B50" t="n">
-        <v>57654</v>
+        <v>80111</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550089</v>
+        <v>550110</v>
       </c>
       <c r="R50" t="n">
-        <v>6942422</v>
+        <v>6942386</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5750,11 +5745,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5781,45 +5771,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126051690</v>
+        <v>126051408</v>
       </c>
       <c r="B51" t="n">
-        <v>80111</v>
+        <v>57654</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550110</v>
+        <v>550089</v>
       </c>
       <c r="R51" t="n">
-        <v>6942386</v>
+        <v>6942422</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5852,6 +5847,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Stora uthackade hål vid rotbasen, äldre spår. Gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6572,7 +6572,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126057601</v>
+        <v>126048239</v>
       </c>
       <c r="B59" t="n">
         <v>98361</v>
@@ -6600,20 +6600,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550096</v>
+        <v>550147</v>
       </c>
       <c r="R59" t="n">
-        <v>6942661</v>
+        <v>6942635</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6643,11 +6647,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6674,7 +6673,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126052934</v>
+        <v>126049594</v>
       </c>
       <c r="B60" t="n">
         <v>98361</v>
@@ -6704,7 +6703,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6713,10 +6712,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>549977</v>
+        <v>550141</v>
       </c>
       <c r="R60" t="n">
-        <v>6942554</v>
+        <v>6942615</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6775,52 +6774,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126049594</v>
+        <v>126057576</v>
       </c>
       <c r="B61" t="n">
-        <v>98361</v>
+        <v>78738</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550141</v>
+        <v>550078</v>
       </c>
       <c r="R61" t="n">
-        <v>6942615</v>
+        <v>6942401</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6876,37 +6871,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126048239</v>
+        <v>126051839</v>
       </c>
       <c r="B62" t="n">
-        <v>98361</v>
+        <v>56849</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>56</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6915,10 +6911,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550147</v>
+        <v>550088</v>
       </c>
       <c r="R62" t="n">
-        <v>6942635</v>
+        <v>6942377</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6977,48 +6973,52 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126057576</v>
+        <v>126052802</v>
       </c>
       <c r="B63" t="n">
-        <v>78738</v>
+        <v>98382</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550078</v>
+        <v>549987</v>
       </c>
       <c r="R63" t="n">
-        <v>6942401</v>
+        <v>6942530</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7074,53 +7074,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126051839</v>
+        <v>126057601</v>
       </c>
       <c r="B64" t="n">
-        <v>56849</v>
+        <v>98361</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550088</v>
+        <v>550096</v>
       </c>
       <c r="R64" t="n">
-        <v>6942377</v>
+        <v>6942661</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7150,6 +7145,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7176,37 +7176,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126052802</v>
+        <v>126052934</v>
       </c>
       <c r="B65" t="n">
-        <v>98382</v>
+        <v>98361</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>549987</v>
+        <v>549977</v>
       </c>
       <c r="R65" t="n">
-        <v>6942530</v>
+        <v>6942554</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8082,32 +8082,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126057578</v>
+        <v>126057549</v>
       </c>
       <c r="B74" t="n">
-        <v>78738</v>
+        <v>91699</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550086</v>
+        <v>549978</v>
       </c>
       <c r="R74" t="n">
-        <v>6942580</v>
+        <v>6942581</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8179,32 +8179,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126057549</v>
+        <v>126057578</v>
       </c>
       <c r="B75" t="n">
-        <v>91699</v>
+        <v>78738</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>549978</v>
+        <v>550086</v>
       </c>
       <c r="R75" t="n">
-        <v>6942581</v>
+        <v>6942580</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8673,10 +8673,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126057559</v>
+        <v>126047488</v>
       </c>
       <c r="B80" t="n">
-        <v>80111</v>
+        <v>43935</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8684,37 +8684,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6461</v>
+        <v>101735</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550000</v>
+        <v>550158</v>
       </c>
       <c r="R80" t="n">
-        <v>6942626</v>
+        <v>6942653</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8744,6 +8749,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8770,10 +8780,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126047488</v>
+        <v>126057559</v>
       </c>
       <c r="B81" t="n">
-        <v>43935</v>
+        <v>80111</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8781,42 +8791,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>101735</v>
+        <v>6461</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550158</v>
+        <v>550000</v>
       </c>
       <c r="R81" t="n">
-        <v>6942653</v>
+        <v>6942626</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8846,11 +8851,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Går djupt ner i hela veden. Björk</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9269,48 +9269,52 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126057556</v>
+        <v>126052873</v>
       </c>
       <c r="B86" t="n">
-        <v>80111</v>
+        <v>98361</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550074</v>
+        <v>549989</v>
       </c>
       <c r="R86" t="n">
-        <v>6942641</v>
+        <v>6942554</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9366,32 +9370,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126052154</v>
+        <v>126052827</v>
       </c>
       <c r="B87" t="n">
-        <v>78980</v>
+        <v>97239</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9401,10 +9405,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550021</v>
+        <v>549987</v>
       </c>
       <c r="R87" t="n">
-        <v>6942450</v>
+        <v>6942530</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9437,11 +9441,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9468,10 +9467,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126052827</v>
+        <v>126057556</v>
       </c>
       <c r="B88" t="n">
-        <v>97239</v>
+        <v>80111</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9479,21 +9478,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9503,13 +9502,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>549987</v>
+        <v>550074</v>
       </c>
       <c r="R88" t="n">
-        <v>6942530</v>
+        <v>6942641</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9565,10 +9564,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126057531</v>
+        <v>126052154</v>
       </c>
       <c r="B89" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9576,21 +9575,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9600,13 +9599,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>549974</v>
+        <v>550021</v>
       </c>
       <c r="R89" t="n">
-        <v>6942584</v>
+        <v>6942450</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9640,7 +9639,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9667,7 +9666,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126057535</v>
+        <v>126057531</v>
       </c>
       <c r="B90" t="n">
         <v>57657</v>
@@ -9702,10 +9701,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550047</v>
+        <v>549974</v>
       </c>
       <c r="R90" t="n">
-        <v>6942401</v>
+        <v>6942584</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9742,7 +9741,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9769,52 +9768,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126052873</v>
+        <v>126057535</v>
       </c>
       <c r="B91" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>549989</v>
+        <v>550047</v>
       </c>
       <c r="R91" t="n">
-        <v>6942554</v>
+        <v>6942401</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9844,6 +9839,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9972,10 +9972,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126050713</v>
+        <v>126057577</v>
       </c>
       <c r="B93" t="n">
-        <v>56840</v>
+        <v>78738</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9983,42 +9983,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550120</v>
+        <v>550101</v>
       </c>
       <c r="R93" t="n">
-        <v>6942506</v>
+        <v>6942551</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10074,32 +10069,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126057593</v>
+        <v>126057581</v>
       </c>
       <c r="B94" t="n">
-        <v>98361</v>
+        <v>78738</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10109,10 +10104,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550137</v>
+        <v>550004</v>
       </c>
       <c r="R94" t="n">
-        <v>6942555</v>
+        <v>6942625</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10145,11 +10140,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>3 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10176,48 +10166,53 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126057923</v>
+        <v>126050713</v>
       </c>
       <c r="B95" t="n">
-        <v>98361</v>
+        <v>56840</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>550122</v>
+        <v>550120</v>
       </c>
       <c r="R95" t="n">
-        <v>6942671</v>
+        <v>6942506</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10247,11 +10242,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10278,32 +10268,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126057577</v>
+        <v>126057593</v>
       </c>
       <c r="B96" t="n">
-        <v>78738</v>
+        <v>98361</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10313,10 +10303,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>550101</v>
+        <v>550137</v>
       </c>
       <c r="R96" t="n">
-        <v>6942551</v>
+        <v>6942555</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10349,6 +10339,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10375,45 +10370,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126057581</v>
+        <v>126057923</v>
       </c>
       <c r="B97" t="n">
-        <v>78738</v>
+        <v>98361</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>550004</v>
+        <v>550122</v>
       </c>
       <c r="R97" t="n">
-        <v>6942625</v>
+        <v>6942671</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10446,6 +10441,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -5074,48 +5074,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126052735</v>
+        <v>126057896</v>
       </c>
       <c r="B44" t="n">
-        <v>78739</v>
+        <v>80111</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>549975</v>
+        <v>550007</v>
       </c>
       <c r="R44" t="n">
-        <v>6942519</v>
+        <v>6942646</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5171,45 +5171,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057896</v>
+        <v>126057568</v>
       </c>
       <c r="B45" t="n">
-        <v>80111</v>
+        <v>80083</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550007</v>
+        <v>550093</v>
       </c>
       <c r="R45" t="n">
-        <v>6942646</v>
+        <v>6942579</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5268,45 +5268,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057568</v>
+        <v>126057930</v>
       </c>
       <c r="B46" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550093</v>
+        <v>550112</v>
       </c>
       <c r="R46" t="n">
-        <v>6942579</v>
+        <v>6942664</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5339,6 +5339,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>50stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5466,48 +5471,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126057930</v>
+        <v>126052735</v>
       </c>
       <c r="B48" t="n">
-        <v>98361</v>
+        <v>78739</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550112</v>
+        <v>549975</v>
       </c>
       <c r="R48" t="n">
-        <v>6942664</v>
+        <v>6942519</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5537,11 +5542,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>50stycken</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -9269,52 +9269,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126052873</v>
+        <v>126057556</v>
       </c>
       <c r="B86" t="n">
-        <v>98361</v>
+        <v>80111</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>549989</v>
+        <v>550074</v>
       </c>
       <c r="R86" t="n">
-        <v>6942554</v>
+        <v>6942641</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9370,32 +9366,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126052827</v>
+        <v>126052154</v>
       </c>
       <c r="B87" t="n">
-        <v>97239</v>
+        <v>78980</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9405,10 +9401,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>549987</v>
+        <v>550021</v>
       </c>
       <c r="R87" t="n">
-        <v>6942530</v>
+        <v>6942450</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9441,6 +9437,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9467,32 +9468,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126057556</v>
+        <v>126057531</v>
       </c>
       <c r="B88" t="n">
-        <v>80111</v>
+        <v>57657</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9502,10 +9503,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550074</v>
+        <v>549974</v>
       </c>
       <c r="R88" t="n">
-        <v>6942641</v>
+        <v>6942584</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9538,6 +9539,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9564,10 +9570,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126052154</v>
+        <v>126057535</v>
       </c>
       <c r="B89" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9575,21 +9581,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9599,13 +9605,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550021</v>
+        <v>550047</v>
       </c>
       <c r="R89" t="n">
-        <v>6942450</v>
+        <v>6942401</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9639,7 +9645,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9666,48 +9672,52 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126057531</v>
+        <v>126052873</v>
       </c>
       <c r="B90" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>549974</v>
+        <v>549989</v>
       </c>
       <c r="R90" t="n">
-        <v>6942584</v>
+        <v>6942554</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9737,11 +9747,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9768,32 +9773,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126057535</v>
+        <v>126052827</v>
       </c>
       <c r="B91" t="n">
-        <v>57657</v>
+        <v>97239</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9803,13 +9808,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550047</v>
+        <v>549987</v>
       </c>
       <c r="R91" t="n">
-        <v>6942401</v>
+        <v>6942530</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9839,11 +9844,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9870,10 +9870,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126057540</v>
+        <v>126057577</v>
       </c>
       <c r="B92" t="n">
-        <v>57657</v>
+        <v>78738</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9881,21 +9881,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9905,10 +9905,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550138</v>
+        <v>550101</v>
       </c>
       <c r="R92" t="n">
-        <v>6942638</v>
+        <v>6942551</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -9941,11 +9941,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9972,7 +9967,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126057577</v>
+        <v>126057581</v>
       </c>
       <c r="B93" t="n">
         <v>78738</v>
@@ -10007,10 +10002,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550101</v>
+        <v>550004</v>
       </c>
       <c r="R93" t="n">
-        <v>6942551</v>
+        <v>6942625</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10069,10 +10064,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126057581</v>
+        <v>126057540</v>
       </c>
       <c r="B94" t="n">
-        <v>78738</v>
+        <v>57657</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10080,21 +10075,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10104,10 +10099,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550004</v>
+        <v>550138</v>
       </c>
       <c r="R94" t="n">
-        <v>6942625</v>
+        <v>6942638</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10140,6 +10135,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -5074,48 +5074,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126057896</v>
+        <v>126052735</v>
       </c>
       <c r="B44" t="n">
-        <v>80111</v>
+        <v>78739</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550007</v>
+        <v>549975</v>
       </c>
       <c r="R44" t="n">
-        <v>6942646</v>
+        <v>6942519</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5171,45 +5171,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126057568</v>
+        <v>126057896</v>
       </c>
       <c r="B45" t="n">
-        <v>80083</v>
+        <v>80111</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550093</v>
+        <v>550007</v>
       </c>
       <c r="R45" t="n">
-        <v>6942579</v>
+        <v>6942646</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5268,45 +5268,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126057930</v>
+        <v>126057568</v>
       </c>
       <c r="B46" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550112</v>
+        <v>550093</v>
       </c>
       <c r="R46" t="n">
-        <v>6942664</v>
+        <v>6942579</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5339,11 +5339,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>50stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5471,48 +5466,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126052735</v>
+        <v>126057930</v>
       </c>
       <c r="B48" t="n">
-        <v>78739</v>
+        <v>98361</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>549975</v>
+        <v>550112</v>
       </c>
       <c r="R48" t="n">
-        <v>6942519</v>
+        <v>6942664</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5542,6 +5537,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>50stycken</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5980,45 +5980,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057565</v>
+        <v>126057898</v>
       </c>
       <c r="B53" t="n">
-        <v>78739</v>
+        <v>80111</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550139</v>
+        <v>549997</v>
       </c>
       <c r="R53" t="n">
-        <v>6942641</v>
+        <v>6942637</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6174,45 +6174,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057898</v>
+        <v>126057565</v>
       </c>
       <c r="B55" t="n">
-        <v>80111</v>
+        <v>78739</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>549997</v>
+        <v>550139</v>
       </c>
       <c r="R55" t="n">
-        <v>6942637</v>
+        <v>6942641</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7980,32 +7980,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126049570</v>
+        <v>126057549</v>
       </c>
       <c r="B73" t="n">
-        <v>78980</v>
+        <v>91699</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550135</v>
+        <v>549978</v>
       </c>
       <c r="R73" t="n">
-        <v>6942628</v>
+        <v>6942581</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8051,11 +8051,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8082,32 +8077,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126057549</v>
+        <v>126049570</v>
       </c>
       <c r="B74" t="n">
-        <v>91699</v>
+        <v>78980</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8117,13 +8112,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>549978</v>
+        <v>550135</v>
       </c>
       <c r="R74" t="n">
-        <v>6942581</v>
+        <v>6942628</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8153,6 +8148,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9269,48 +9269,52 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126057556</v>
+        <v>126052873</v>
       </c>
       <c r="B86" t="n">
-        <v>80111</v>
+        <v>98361</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550074</v>
+        <v>549989</v>
       </c>
       <c r="R86" t="n">
-        <v>6942641</v>
+        <v>6942554</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9366,32 +9370,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126052154</v>
+        <v>126052827</v>
       </c>
       <c r="B87" t="n">
-        <v>78980</v>
+        <v>97239</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9401,10 +9405,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550021</v>
+        <v>549987</v>
       </c>
       <c r="R87" t="n">
-        <v>6942450</v>
+        <v>6942530</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9437,11 +9441,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9468,32 +9467,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126057531</v>
+        <v>126057556</v>
       </c>
       <c r="B88" t="n">
-        <v>57657</v>
+        <v>80111</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9503,10 +9502,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>549974</v>
+        <v>550074</v>
       </c>
       <c r="R88" t="n">
-        <v>6942584</v>
+        <v>6942641</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9539,11 +9538,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9570,10 +9564,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126057535</v>
+        <v>126052154</v>
       </c>
       <c r="B89" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9581,21 +9575,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9605,13 +9599,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550047</v>
+        <v>550021</v>
       </c>
       <c r="R89" t="n">
-        <v>6942401</v>
+        <v>6942450</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9645,7 +9639,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9672,52 +9666,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126052873</v>
+        <v>126057531</v>
       </c>
       <c r="B90" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>549989</v>
+        <v>549974</v>
       </c>
       <c r="R90" t="n">
-        <v>6942554</v>
+        <v>6942584</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9747,6 +9737,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9773,32 +9768,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126052827</v>
+        <v>126057535</v>
       </c>
       <c r="B91" t="n">
-        <v>97239</v>
+        <v>57657</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9808,13 +9803,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>549987</v>
+        <v>550047</v>
       </c>
       <c r="R91" t="n">
-        <v>6942530</v>
+        <v>6942401</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9844,6 +9839,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -2183,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126057536</v>
+        <v>126057934</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,34 +2194,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550113</v>
+        <v>550127</v>
       </c>
       <c r="R15" t="n">
-        <v>6942389</v>
+        <v>6942669</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Rikligt med garnlav i området</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126057934</v>
+        <v>126057536</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,34 +2296,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550127</v>
+        <v>550113</v>
       </c>
       <c r="R16" t="n">
-        <v>6942669</v>
+        <v>6942389</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,45 +2387,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126057921</v>
+        <v>126057564</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>78739</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550142</v>
+        <v>550076</v>
       </c>
       <c r="R17" t="n">
-        <v>6942582</v>
+        <v>6942390</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2458,11 +2458,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,7 +2484,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126057597</v>
+        <v>126057921</v>
       </c>
       <c r="B18" t="n">
         <v>98361</v>
@@ -2520,14 +2515,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550099</v>
+        <v>550142</v>
       </c>
       <c r="R18" t="n">
-        <v>6942637</v>
+        <v>6942582</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2564,7 +2559,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,32 +2586,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126057564</v>
+        <v>126057597</v>
       </c>
       <c r="B19" t="n">
-        <v>78739</v>
+        <v>98361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550076</v>
+        <v>550099</v>
       </c>
       <c r="R19" t="n">
-        <v>6942390</v>
+        <v>6942637</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2662,6 +2657,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -5980,45 +5980,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126057898</v>
+        <v>126057565</v>
       </c>
       <c r="B53" t="n">
-        <v>80111</v>
+        <v>78739</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>549997</v>
+        <v>550139</v>
       </c>
       <c r="R53" t="n">
-        <v>6942637</v>
+        <v>6942641</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6174,45 +6174,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126057565</v>
+        <v>126057898</v>
       </c>
       <c r="B55" t="n">
-        <v>78739</v>
+        <v>80111</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550139</v>
+        <v>549997</v>
       </c>
       <c r="R55" t="n">
-        <v>6942641</v>
+        <v>6942637</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6774,32 +6774,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126057576</v>
+        <v>126057601</v>
       </c>
       <c r="B61" t="n">
-        <v>78738</v>
+        <v>98361</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550078</v>
+        <v>550096</v>
       </c>
       <c r="R61" t="n">
-        <v>6942401</v>
+        <v>6942661</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6845,6 +6845,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6871,38 +6876,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126051839</v>
+        <v>126052934</v>
       </c>
       <c r="B62" t="n">
-        <v>56849</v>
+        <v>98361</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6911,10 +6915,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550088</v>
+        <v>549977</v>
       </c>
       <c r="R62" t="n">
-        <v>6942377</v>
+        <v>6942554</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7074,32 +7078,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126057601</v>
+        <v>126057576</v>
       </c>
       <c r="B64" t="n">
-        <v>98361</v>
+        <v>78738</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7109,10 +7113,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550096</v>
+        <v>550078</v>
       </c>
       <c r="R64" t="n">
-        <v>6942661</v>
+        <v>6942401</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7145,11 +7149,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7176,37 +7175,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126052934</v>
+        <v>126051839</v>
       </c>
       <c r="B65" t="n">
-        <v>98361</v>
+        <v>56849</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>29</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>549977</v>
+        <v>550088</v>
       </c>
       <c r="R65" t="n">
-        <v>6942554</v>
+        <v>6942377</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9870,10 +9870,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126057577</v>
+        <v>126057540</v>
       </c>
       <c r="B92" t="n">
-        <v>78738</v>
+        <v>57657</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9881,21 +9881,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9905,10 +9905,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550101</v>
+        <v>550138</v>
       </c>
       <c r="R92" t="n">
-        <v>6942551</v>
+        <v>6942638</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -9941,6 +9941,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9967,7 +9972,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126057581</v>
+        <v>126057577</v>
       </c>
       <c r="B93" t="n">
         <v>78738</v>
@@ -10002,10 +10007,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550004</v>
+        <v>550101</v>
       </c>
       <c r="R93" t="n">
-        <v>6942625</v>
+        <v>6942551</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10064,10 +10069,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126057540</v>
+        <v>126057581</v>
       </c>
       <c r="B94" t="n">
-        <v>57657</v>
+        <v>78738</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10075,21 +10080,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10099,10 +10104,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550138</v>
+        <v>550004</v>
       </c>
       <c r="R94" t="n">
-        <v>6942638</v>
+        <v>6942625</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10135,11 +10140,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -5774,7 +5774,7 @@
         <v>126051408</v>
       </c>
       <c r="B51" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -5774,7 +5774,7 @@
         <v>126051408</v>
       </c>
       <c r="B51" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -5774,7 +5774,7 @@
         <v>126051408</v>
       </c>
       <c r="B51" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -5774,7 +5774,7 @@
         <v>126051408</v>
       </c>
       <c r="B51" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -5774,7 +5774,7 @@
         <v>126051408</v>
       </c>
       <c r="B51" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 27652-2025 artfynd.xlsx
+++ b/artfynd/A 27652-2025 artfynd.xlsx
@@ -5774,7 +5774,7 @@
         <v>126051408</v>
       </c>
       <c r="B51" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
